--- a/data/macro/China/China PMI.xlsx
+++ b/data/macro/China/China PMI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\macro\China\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data/macro/China/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF71E575-3E63-40C3-9402-6CF02606DFC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDA48D33-F23E-A04D-AB4B-20FAE145924F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4C7AFA9F-A9F7-4D4A-8224-91102ADA8910}"/>
+    <workbookView xWindow="22160" yWindow="600" windowWidth="29040" windowHeight="15720" xr2:uid="{4C7AFA9F-A9F7-4D4A-8224-91102ADA8910}"/>
   </bookViews>
   <sheets>
     <sheet name="CPMINDX" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="13">
   <si>
     <t>Release Date</t>
   </si>
@@ -76,22 +76,22 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="177" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="178" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="166" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="167" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Aptos Narrow"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -99,30 +99,30 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Verdana"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Verdana"/>
+      <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="12"/>
-      <color theme="10"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -144,45 +144,45 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -514,5926 +514,5969 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8641136A-8358-754A-BFC1-48B8F9996351}">
-  <dimension ref="A1:G257"/>
-  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G259"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.81640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.36328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.6328125" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.54296875" style="10"/>
-    <col min="5" max="7" width="11.6328125" style="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="11.54296875" style="3"/>
+    <col min="1" max="1" width="10.83203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5" style="11"/>
+    <col min="5" max="7" width="11.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="11.5" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="4">
+      <c r="A2" s="7">
         <v>38353</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="7">
         <v>38384</v>
       </c>
-      <c r="C2" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="9">
+      <c r="C2" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="10">
         <v>54.7</v>
       </c>
-      <c r="F2" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" s="9" t="s">
+      <c r="F2" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="10" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="4">
+      <c r="A3" s="7">
         <v>38384</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="7">
         <v>38412</v>
       </c>
-      <c r="C3" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="9">
+      <c r="C3" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="10">
         <v>54.5</v>
       </c>
-      <c r="F3" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G3" s="9">
+      <c r="F3" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="10">
         <v>54.7</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="4">
+      <c r="A4" s="7">
         <v>38412</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="7">
         <v>38443</v>
       </c>
-      <c r="C4" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="9">
+      <c r="C4" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="10">
         <v>57.9</v>
       </c>
-      <c r="F4" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G4" s="9">
+      <c r="F4" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="10">
         <v>54.5</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="4">
+      <c r="A5" s="7">
         <v>38443</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="7">
         <v>38473</v>
       </c>
-      <c r="C5" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="9">
+      <c r="C5" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="10">
         <v>56.7</v>
       </c>
-      <c r="F5" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G5" s="9">
+      <c r="F5" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G5" s="10">
         <v>57.9</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="4">
+      <c r="A6" s="7">
         <v>38473</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="7">
         <v>38504</v>
       </c>
-      <c r="C6" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="9">
+      <c r="C6" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="10">
         <v>52.9</v>
       </c>
-      <c r="F6" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G6" s="9">
+      <c r="F6" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G6" s="10">
         <v>56.7</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="4">
+      <c r="A7" s="7">
         <v>38504</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="7">
         <v>38534</v>
       </c>
-      <c r="C7" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="9">
+      <c r="C7" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="10">
         <v>51.7</v>
       </c>
-      <c r="F7" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G7" s="9">
+      <c r="F7" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G7" s="10">
         <v>52.9</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" s="4">
+      <c r="A8" s="7">
         <v>38534</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="7">
         <v>38565</v>
       </c>
-      <c r="C8" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="9">
+      <c r="C8" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="10">
         <v>51.1</v>
       </c>
-      <c r="F8" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G8" s="9">
+      <c r="F8" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G8" s="10">
         <v>51.7</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="4">
+      <c r="A9" s="7">
         <v>38565</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="7">
         <v>38596</v>
       </c>
-      <c r="C9" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="9">
+      <c r="C9" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="10">
         <v>52.6</v>
       </c>
-      <c r="F9" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G9" s="9">
+      <c r="F9" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G9" s="10">
         <v>51.1</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="4">
+      <c r="A10" s="7">
         <v>38596</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="7">
         <v>38626</v>
       </c>
-      <c r="C10" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="9">
+      <c r="C10" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="10">
         <v>55.1</v>
       </c>
-      <c r="F10" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="9">
+      <c r="F10" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G10" s="10">
         <v>52.6</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="4">
+      <c r="A11" s="7">
         <v>38626</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11" s="7">
         <v>38657</v>
       </c>
-      <c r="C11" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" s="9">
+      <c r="C11" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="10">
         <v>54.1</v>
       </c>
-      <c r="F11" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G11" s="9">
+      <c r="F11" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G11" s="10">
         <v>55.1</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="4">
+      <c r="A12" s="7">
         <v>38657</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12" s="7">
         <v>38687</v>
       </c>
-      <c r="C12" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="9">
+      <c r="C12" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="10">
         <v>54.1</v>
       </c>
-      <c r="F12" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G12" s="9">
+      <c r="F12" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G12" s="10">
         <v>54.1</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" s="4">
+      <c r="A13" s="7">
         <v>38687</v>
       </c>
-      <c r="B13" s="4">
+      <c r="B13" s="7">
         <v>38718</v>
       </c>
-      <c r="C13" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="9">
+      <c r="C13" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="10">
         <v>54.3</v>
       </c>
-      <c r="F13" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G13" s="9">
+      <c r="F13" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G13" s="10">
         <v>54.1</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" s="4">
+      <c r="A14" s="7">
         <v>38718</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14" s="7">
         <v>38749</v>
       </c>
-      <c r="C14" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" s="9">
+      <c r="C14" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="10">
         <v>52.1</v>
       </c>
-      <c r="F14" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G14" s="9">
+      <c r="F14" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="10">
         <v>54.3</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" s="4">
+      <c r="A15" s="7">
         <v>38749</v>
       </c>
-      <c r="B15" s="4">
+      <c r="B15" s="7">
         <v>38777</v>
       </c>
-      <c r="C15" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E15" s="9">
+      <c r="C15" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="10">
         <v>52.1</v>
       </c>
-      <c r="F15" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G15" s="9">
+      <c r="F15" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G15" s="10">
         <v>52.1</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" s="4">
+      <c r="A16" s="7">
         <v>38777</v>
       </c>
-      <c r="B16" s="4">
+      <c r="B16" s="7">
         <v>38808</v>
       </c>
-      <c r="C16" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" s="9">
+      <c r="C16" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="10">
         <v>55.3</v>
       </c>
-      <c r="F16" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G16" s="9">
+      <c r="F16" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G16" s="10">
         <v>52.1</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="4">
+      <c r="A17" s="7">
         <v>38808</v>
       </c>
-      <c r="B17" s="4">
+      <c r="B17" s="7">
         <v>38838</v>
       </c>
-      <c r="C17" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E17" s="9">
+      <c r="C17" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" s="10">
         <v>58.1</v>
       </c>
-      <c r="F17" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G17" s="9">
+      <c r="F17" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G17" s="10">
         <v>55.3</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="4">
+      <c r="A18" s="7">
         <v>38838</v>
       </c>
-      <c r="B18" s="4">
+      <c r="B18" s="7">
         <v>38869</v>
       </c>
-      <c r="C18" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E18" s="9">
+      <c r="C18" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="10">
         <v>54.8</v>
       </c>
-      <c r="F18" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G18" s="9">
+      <c r="F18" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G18" s="10">
         <v>58.1</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="4">
+      <c r="A19" s="7">
         <v>38869</v>
       </c>
-      <c r="B19" s="4">
+      <c r="B19" s="7">
         <v>38899</v>
       </c>
-      <c r="C19" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E19" s="9">
+      <c r="C19" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" s="10">
         <v>54.1</v>
       </c>
-      <c r="F19" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G19" s="9">
+      <c r="F19" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G19" s="10">
         <v>54.8</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="4">
+      <c r="A20" s="7">
         <v>38899</v>
       </c>
-      <c r="B20" s="4">
+      <c r="B20" s="7">
         <v>38930</v>
       </c>
-      <c r="C20" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E20" s="9">
+      <c r="C20" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" s="10">
         <v>52.4</v>
       </c>
-      <c r="F20" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G20" s="9">
+      <c r="F20" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G20" s="10">
         <v>54.1</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="4">
+      <c r="A21" s="7">
         <v>38930</v>
       </c>
-      <c r="B21" s="4">
+      <c r="B21" s="7">
         <v>38961</v>
       </c>
-      <c r="C21" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E21" s="9">
+      <c r="C21" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" s="10">
         <v>53.1</v>
       </c>
-      <c r="F21" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G21" s="9">
+      <c r="F21" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G21" s="10">
         <v>52.4</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22" s="4">
+      <c r="A22" s="7">
         <v>38961</v>
       </c>
-      <c r="B22" s="4">
+      <c r="B22" s="7">
         <v>38991</v>
       </c>
-      <c r="C22" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E22" s="9">
+      <c r="C22" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" s="10">
         <v>57</v>
       </c>
-      <c r="F22" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G22" s="9">
+      <c r="F22" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="10">
         <v>53.1</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23" s="4">
+      <c r="A23" s="7">
         <v>38991</v>
       </c>
-      <c r="B23" s="4">
+      <c r="B23" s="7">
         <v>39022</v>
       </c>
-      <c r="C23" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E23" s="9">
+      <c r="C23" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" s="10">
         <v>54.7</v>
       </c>
-      <c r="F23" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G23" s="9">
+      <c r="F23" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G23" s="10">
         <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24" s="4">
+      <c r="A24" s="7">
         <v>39022</v>
       </c>
-      <c r="B24" s="4">
+      <c r="B24" s="7">
         <v>39052</v>
       </c>
-      <c r="C24" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E24" s="9">
+      <c r="C24" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" s="10">
         <v>55.3</v>
       </c>
-      <c r="F24" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G24" s="9">
+      <c r="F24" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G24" s="10">
         <v>54.7</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25" s="4">
+      <c r="A25" s="7">
         <v>39052</v>
       </c>
-      <c r="B25" s="4">
+      <c r="B25" s="7">
         <v>39083</v>
       </c>
-      <c r="C25" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E25" s="9">
+      <c r="C25" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" s="10">
         <v>54.8</v>
       </c>
-      <c r="F25" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G25" s="9">
+      <c r="F25" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G25" s="10">
         <v>55.3</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A26" s="4">
+      <c r="A26" s="7">
         <v>39083</v>
       </c>
-      <c r="B26" s="4">
+      <c r="B26" s="7">
         <v>39114</v>
       </c>
-      <c r="C26" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E26" s="9">
+      <c r="C26" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" s="10">
         <v>55.1</v>
       </c>
-      <c r="F26" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G26" s="9">
+      <c r="F26" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G26" s="10">
         <v>54.8</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A27" s="4">
+      <c r="A27" s="7">
         <v>39114</v>
       </c>
-      <c r="B27" s="4">
+      <c r="B27" s="7">
         <v>39142</v>
       </c>
-      <c r="C27" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E27" s="9">
+      <c r="C27" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" s="10">
         <v>53.1</v>
       </c>
-      <c r="F27" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G27" s="9">
+      <c r="F27" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G27" s="10">
         <v>55.1</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A28" s="4">
+      <c r="A28" s="7">
         <v>39142</v>
       </c>
-      <c r="B28" s="4">
+      <c r="B28" s="7">
         <v>39173</v>
       </c>
-      <c r="C28" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E28" s="9">
+      <c r="C28" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" s="10">
         <v>56.1</v>
       </c>
-      <c r="F28" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G28" s="9">
+      <c r="F28" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G28" s="10">
         <v>53.1</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A29" s="4">
+      <c r="A29" s="7">
         <v>39173</v>
       </c>
-      <c r="B29" s="4">
+      <c r="B29" s="7">
         <v>39203</v>
       </c>
-      <c r="C29" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E29" s="9">
+      <c r="C29" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" s="10">
         <v>58.6</v>
       </c>
-      <c r="F29" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G29" s="9">
+      <c r="F29" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G29" s="10">
         <v>56.1</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A30" s="4">
+      <c r="A30" s="7">
         <v>39203</v>
       </c>
-      <c r="B30" s="4">
+      <c r="B30" s="7">
         <v>39234</v>
       </c>
-      <c r="C30" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E30" s="9">
+      <c r="C30" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" s="10">
         <v>55.7</v>
       </c>
-      <c r="F30" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G30" s="9">
+      <c r="F30" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G30" s="10">
         <v>58.6</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A31" s="4">
+      <c r="A31" s="7">
         <v>39234</v>
       </c>
-      <c r="B31" s="4">
+      <c r="B31" s="7">
         <v>39264</v>
       </c>
-      <c r="C31" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E31" s="9">
+      <c r="C31" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E31" s="10">
         <v>54.5</v>
       </c>
-      <c r="F31" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G31" s="9">
+      <c r="F31" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G31" s="10">
         <v>55.7</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A32" s="4">
+      <c r="A32" s="7">
         <v>39264</v>
       </c>
-      <c r="B32" s="4">
+      <c r="B32" s="7">
         <v>39295</v>
       </c>
-      <c r="C32" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E32" s="9">
+      <c r="C32" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E32" s="10">
         <v>53.3</v>
       </c>
-      <c r="F32" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G32" s="9">
+      <c r="F32" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G32" s="10">
         <v>54.5</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A33" s="4">
+      <c r="A33" s="7">
         <v>39295</v>
       </c>
-      <c r="B33" s="4">
+      <c r="B33" s="7">
         <v>39326</v>
       </c>
-      <c r="C33" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E33" s="9">
+      <c r="C33" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" s="10">
         <v>54</v>
       </c>
-      <c r="F33" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G33" s="9">
+      <c r="F33" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G33" s="10">
         <v>53.3</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A34" s="4">
+      <c r="A34" s="7">
         <v>39326</v>
       </c>
-      <c r="B34" s="4">
+      <c r="B34" s="7">
         <v>39356</v>
       </c>
-      <c r="C34" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E34" s="9">
+      <c r="C34" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" s="10">
         <v>56.1</v>
       </c>
-      <c r="F34" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G34" s="9">
+      <c r="F34" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G34" s="10">
         <v>54</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A35" s="4">
+      <c r="A35" s="7">
         <v>39356</v>
       </c>
-      <c r="B35" s="4">
+      <c r="B35" s="7">
         <v>39387</v>
       </c>
-      <c r="C35" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E35" s="9">
+      <c r="C35" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" s="10">
         <v>53.2</v>
       </c>
-      <c r="F35" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G35" s="9">
+      <c r="F35" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G35" s="10">
         <v>56.1</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A36" s="4">
+      <c r="A36" s="7">
         <v>39387</v>
       </c>
-      <c r="B36" s="4">
+      <c r="B36" s="7">
         <v>39417</v>
       </c>
-      <c r="C36" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E36" s="9">
+      <c r="C36" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" s="10">
         <v>55.4</v>
       </c>
-      <c r="F36" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G36" s="9">
+      <c r="F36" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G36" s="10">
         <v>53.2</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A37" s="4">
+      <c r="A37" s="7">
         <v>39417</v>
       </c>
-      <c r="B37" s="4">
+      <c r="B37" s="7">
         <v>39448</v>
       </c>
-      <c r="C37" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E37" s="9">
+      <c r="C37" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E37" s="10">
         <v>55.3</v>
       </c>
-      <c r="F37" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G37" s="9">
+      <c r="F37" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G37" s="10">
         <v>55.4</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A38" s="4">
+      <c r="A38" s="7">
         <v>39448</v>
       </c>
-      <c r="B38" s="4">
+      <c r="B38" s="7">
         <v>39479</v>
       </c>
-      <c r="C38" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E38" s="9">
+      <c r="C38" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E38" s="10">
         <v>53</v>
       </c>
-      <c r="F38" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G38" s="9">
+      <c r="F38" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G38" s="10">
         <v>55.3</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A39" s="4">
+      <c r="A39" s="7">
         <v>39479</v>
       </c>
-      <c r="B39" s="4">
+      <c r="B39" s="7">
         <v>39508</v>
       </c>
-      <c r="C39" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E39" s="9">
+      <c r="C39" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E39" s="10">
         <v>53.4</v>
       </c>
-      <c r="F39" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G39" s="9">
+      <c r="F39" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G39" s="10">
         <v>53</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A40" s="4">
+      <c r="A40" s="7">
         <v>39508</v>
       </c>
-      <c r="B40" s="4">
+      <c r="B40" s="7">
         <v>39539</v>
       </c>
-      <c r="C40" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E40" s="9">
+      <c r="C40" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E40" s="10">
         <v>58.4</v>
       </c>
-      <c r="F40" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G40" s="9">
+      <c r="F40" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G40" s="10">
         <v>53.4</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A41" s="4">
+      <c r="A41" s="7">
         <v>39539</v>
       </c>
-      <c r="B41" s="4">
+      <c r="B41" s="7">
         <v>39569</v>
       </c>
-      <c r="C41" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E41" s="9">
+      <c r="C41" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E41" s="10">
         <v>59.2</v>
       </c>
-      <c r="F41" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G41" s="9">
+      <c r="F41" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G41" s="10">
         <v>58.4</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A42" s="4">
+      <c r="A42" s="7">
         <v>39569</v>
       </c>
-      <c r="B42" s="4">
+      <c r="B42" s="7">
         <v>39600</v>
       </c>
-      <c r="C42" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E42" s="9">
+      <c r="C42" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" s="10">
         <v>53.3</v>
       </c>
-      <c r="F42" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G42" s="9">
+      <c r="F42" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G42" s="10">
         <v>59.2</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A43" s="4">
+      <c r="A43" s="7">
         <v>39600</v>
       </c>
-      <c r="B43" s="4">
+      <c r="B43" s="7">
         <v>39630</v>
       </c>
-      <c r="C43" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E43" s="9">
+      <c r="C43" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E43" s="10">
         <v>52</v>
       </c>
-      <c r="F43" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G43" s="9">
+      <c r="F43" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G43" s="10">
         <v>53.3</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A44" s="4">
+      <c r="A44" s="7">
         <v>39630</v>
       </c>
-      <c r="B44" s="4">
+      <c r="B44" s="7">
         <v>39661</v>
       </c>
-      <c r="C44" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E44" s="9">
+      <c r="C44" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E44" s="10">
         <v>48.4</v>
       </c>
-      <c r="F44" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G44" s="9">
+      <c r="F44" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G44" s="10">
         <v>52</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A45" s="4">
+      <c r="A45" s="7">
         <v>39661</v>
       </c>
-      <c r="B45" s="4">
+      <c r="B45" s="7">
         <v>39692</v>
       </c>
-      <c r="C45" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E45" s="9">
+      <c r="C45" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E45" s="10">
         <v>48.4</v>
       </c>
-      <c r="F45" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G45" s="9">
+      <c r="F45" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G45" s="10">
         <v>48.4</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A46" s="4">
+      <c r="A46" s="7">
         <v>39692</v>
       </c>
-      <c r="B46" s="4">
+      <c r="B46" s="7">
         <v>39722</v>
       </c>
-      <c r="C46" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E46" s="9">
+      <c r="C46" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E46" s="10">
         <v>51.2</v>
       </c>
-      <c r="F46" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G46" s="9">
+      <c r="F46" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G46" s="10">
         <v>48.4</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A47" s="4">
+      <c r="A47" s="7">
         <v>39722</v>
       </c>
-      <c r="B47" s="4">
+      <c r="B47" s="7">
         <v>39753</v>
       </c>
-      <c r="C47" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E47" s="9">
+      <c r="C47" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E47" s="10">
         <v>44.6</v>
       </c>
-      <c r="F47" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G47" s="9">
+      <c r="F47" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G47" s="10">
         <v>51.2</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A48" s="4">
+      <c r="A48" s="7">
         <v>39753</v>
       </c>
-      <c r="B48" s="4">
+      <c r="B48" s="7">
         <v>39783</v>
       </c>
-      <c r="C48" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E48" s="9">
+      <c r="C48" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E48" s="10">
         <v>38.799999999999997</v>
       </c>
-      <c r="F48" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G48" s="9">
+      <c r="F48" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G48" s="10">
         <v>44.6</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A49" s="4">
+      <c r="A49" s="7">
         <v>39783</v>
       </c>
-      <c r="B49" s="4">
+      <c r="B49" s="7">
         <v>39814</v>
       </c>
-      <c r="C49" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E49" s="9">
+      <c r="C49" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E49" s="10">
         <v>41.2</v>
       </c>
-      <c r="F49" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G49" s="9">
+      <c r="F49" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G49" s="10">
         <v>38.799999999999997</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A50" s="4">
+      <c r="A50" s="7">
         <v>39814</v>
       </c>
-      <c r="B50" s="4">
+      <c r="B50" s="7">
         <v>39845</v>
       </c>
-      <c r="C50" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E50" s="9">
+      <c r="C50" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E50" s="10">
         <v>45.3</v>
       </c>
-      <c r="F50" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G50" s="9">
+      <c r="F50" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G50" s="10">
         <v>41.2</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A51" s="4">
+      <c r="A51" s="7">
         <v>39845</v>
       </c>
-      <c r="B51" s="4">
+      <c r="B51" s="7">
         <v>39873</v>
       </c>
-      <c r="C51" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E51" s="9">
+      <c r="C51" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E51" s="10">
         <v>49</v>
       </c>
-      <c r="F51" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G51" s="9">
+      <c r="F51" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G51" s="10">
         <v>45.3</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A52" s="4">
+      <c r="A52" s="7">
         <v>39873</v>
       </c>
-      <c r="B52" s="4">
+      <c r="B52" s="7">
         <v>39904</v>
       </c>
-      <c r="C52" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E52" s="9">
+      <c r="C52" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D52" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E52" s="10">
         <v>52.4</v>
       </c>
-      <c r="F52" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G52" s="9">
+      <c r="F52" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G52" s="10">
         <v>49</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A53" s="4">
+      <c r="A53" s="7">
         <v>39904</v>
       </c>
-      <c r="B53" s="4">
+      <c r="B53" s="7">
         <v>39934</v>
       </c>
-      <c r="C53" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D53" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E53" s="9">
+      <c r="C53" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D53" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E53" s="10">
         <v>53.5</v>
       </c>
-      <c r="F53" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G53" s="9">
+      <c r="F53" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G53" s="10">
         <v>52.4</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A54" s="4">
+      <c r="A54" s="7">
         <v>39934</v>
       </c>
-      <c r="B54" s="4">
+      <c r="B54" s="7">
         <v>39965</v>
       </c>
-      <c r="C54" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D54" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E54" s="9">
+      <c r="C54" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D54" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E54" s="10">
         <v>53.1</v>
       </c>
-      <c r="F54" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G54" s="9">
+      <c r="F54" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G54" s="10">
         <v>53.5</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A55" s="4">
+      <c r="A55" s="7">
         <v>39965</v>
       </c>
-      <c r="B55" s="4">
+      <c r="B55" s="7">
         <v>39995</v>
       </c>
-      <c r="C55" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D55" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E55" s="9">
+      <c r="C55" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E55" s="10">
         <v>53.2</v>
       </c>
-      <c r="F55" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G55" s="9">
+      <c r="F55" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G55" s="10">
         <v>53.1</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A56" s="4">
+      <c r="A56" s="7">
         <v>39995</v>
       </c>
-      <c r="B56" s="4">
+      <c r="B56" s="7">
         <v>40026</v>
       </c>
-      <c r="C56" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D56" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E56" s="9">
+      <c r="C56" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D56" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E56" s="10">
         <v>53.3</v>
       </c>
-      <c r="F56" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G56" s="9">
+      <c r="F56" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G56" s="10">
         <v>53.2</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A57" s="4">
+      <c r="A57" s="7">
         <v>40026</v>
       </c>
-      <c r="B57" s="4">
+      <c r="B57" s="7">
         <v>40057</v>
       </c>
-      <c r="C57" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D57" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E57" s="9">
+      <c r="C57" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E57" s="10">
         <v>54</v>
       </c>
-      <c r="F57" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G57" s="9">
+      <c r="F57" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G57" s="10">
         <v>53.3</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A58" s="4">
+      <c r="A58" s="7">
         <v>40057</v>
       </c>
-      <c r="B58" s="4">
+      <c r="B58" s="7">
         <v>40087</v>
       </c>
-      <c r="C58" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D58" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E58" s="9">
+      <c r="C58" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E58" s="10">
         <v>54.3</v>
       </c>
-      <c r="F58" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G58" s="9">
+      <c r="F58" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G58" s="10">
         <v>54</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A59" s="4">
+      <c r="A59" s="7">
         <v>40087</v>
       </c>
-      <c r="B59" s="4">
+      <c r="B59" s="7">
         <v>40118</v>
       </c>
-      <c r="C59" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D59" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E59" s="9">
+      <c r="C59" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D59" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E59" s="10">
         <v>55.2</v>
       </c>
-      <c r="F59" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G59" s="9">
+      <c r="F59" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G59" s="10">
         <v>54.3</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A60" s="4">
+      <c r="A60" s="7">
         <v>40118</v>
       </c>
-      <c r="B60" s="4">
+      <c r="B60" s="7">
         <v>40148</v>
       </c>
-      <c r="C60" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D60" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E60" s="9">
+      <c r="C60" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D60" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E60" s="10">
         <v>55.2</v>
       </c>
-      <c r="F60" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G60" s="9">
+      <c r="F60" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G60" s="10">
         <v>55.2</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A61" s="4">
+      <c r="A61" s="7">
         <v>40148</v>
       </c>
-      <c r="B61" s="4">
+      <c r="B61" s="7">
         <v>40179</v>
       </c>
-      <c r="C61" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E61" s="9">
+      <c r="C61" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E61" s="10">
         <v>56.6</v>
       </c>
-      <c r="F61" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G61" s="9">
+      <c r="F61" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G61" s="10">
         <v>55.2</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A62" s="4">
+      <c r="A62" s="7">
         <v>40179</v>
       </c>
-      <c r="B62" s="4">
+      <c r="B62" s="7">
         <v>40210</v>
       </c>
-      <c r="C62" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D62" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E62" s="9">
+      <c r="C62" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D62" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E62" s="10">
         <v>55.8</v>
       </c>
-      <c r="F62" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G62" s="9">
+      <c r="F62" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G62" s="10">
         <v>56.6</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A63" s="4">
+      <c r="A63" s="7">
         <v>40210</v>
       </c>
-      <c r="B63" s="4">
+      <c r="B63" s="7">
         <v>40238</v>
       </c>
-      <c r="C63" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D63" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E63" s="9">
+      <c r="C63" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D63" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E63" s="10">
         <v>52</v>
       </c>
-      <c r="F63" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G63" s="9">
+      <c r="F63" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G63" s="10">
         <v>55.8</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A64" s="4">
+      <c r="A64" s="7">
         <v>40238</v>
       </c>
-      <c r="B64" s="4">
+      <c r="B64" s="7">
         <v>40269</v>
       </c>
-      <c r="C64" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D64" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E64" s="9">
+      <c r="C64" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D64" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E64" s="10">
         <v>55.1</v>
       </c>
-      <c r="F64" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G64" s="9">
+      <c r="F64" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G64" s="10">
         <v>52</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A65" s="4">
+      <c r="A65" s="7">
         <v>40269</v>
       </c>
-      <c r="B65" s="4">
+      <c r="B65" s="7">
         <v>40299</v>
       </c>
-      <c r="C65" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D65" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E65" s="9">
+      <c r="C65" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D65" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E65" s="10">
         <v>55.7</v>
       </c>
-      <c r="F65" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G65" s="9">
+      <c r="F65" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G65" s="10">
         <v>55.1</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A66" s="4">
+      <c r="A66" s="7">
         <v>40299</v>
       </c>
-      <c r="B66" s="4">
+      <c r="B66" s="7">
         <v>40330</v>
       </c>
-      <c r="C66" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D66" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E66" s="9">
+      <c r="C66" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D66" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E66" s="10">
         <v>53.9</v>
       </c>
-      <c r="F66" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G66" s="9">
+      <c r="F66" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G66" s="10">
         <v>55.7</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A67" s="4">
+      <c r="A67" s="7">
         <v>40330</v>
       </c>
-      <c r="B67" s="4">
+      <c r="B67" s="7">
         <v>40360</v>
       </c>
-      <c r="C67" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D67" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E67" s="9">
+      <c r="C67" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D67" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E67" s="10">
         <v>52.1</v>
       </c>
-      <c r="F67" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G67" s="9">
+      <c r="F67" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G67" s="10">
         <v>53.9</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A68" s="4">
+      <c r="A68" s="7">
         <v>40360</v>
       </c>
-      <c r="B68" s="4">
+      <c r="B68" s="7">
         <v>40391</v>
       </c>
-      <c r="C68" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D68" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E68" s="9">
+      <c r="C68" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D68" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E68" s="10">
         <v>51.2</v>
       </c>
-      <c r="F68" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G68" s="9">
+      <c r="F68" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G68" s="10">
         <v>52.1</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A69" s="4">
+      <c r="A69" s="7">
         <v>40391</v>
       </c>
-      <c r="B69" s="4">
+      <c r="B69" s="7">
         <v>40422</v>
       </c>
-      <c r="C69" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D69" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E69" s="9">
+      <c r="C69" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D69" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E69" s="10">
         <v>51.7</v>
       </c>
-      <c r="F69" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G69" s="9">
+      <c r="F69" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G69" s="10">
         <v>51.2</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A70" s="4">
+      <c r="A70" s="7">
         <v>40422</v>
       </c>
-      <c r="B70" s="4">
+      <c r="B70" s="7">
         <v>40452</v>
       </c>
-      <c r="C70" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D70" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E70" s="9">
+      <c r="C70" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D70" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E70" s="10">
         <v>53.8</v>
       </c>
-      <c r="F70" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G70" s="9">
+      <c r="F70" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G70" s="10">
         <v>51.7</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A71" s="4">
+      <c r="A71" s="7">
         <v>40452</v>
       </c>
-      <c r="B71" s="4">
+      <c r="B71" s="7">
         <v>40483</v>
       </c>
-      <c r="C71" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D71" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E71" s="9">
+      <c r="C71" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D71" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E71" s="10">
         <v>54.7</v>
       </c>
-      <c r="F71" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G71" s="9">
+      <c r="F71" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G71" s="10">
         <v>53.8</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A72" s="4">
+      <c r="A72" s="7">
         <v>40483</v>
       </c>
-      <c r="B72" s="4">
+      <c r="B72" s="7">
         <v>40513</v>
       </c>
-      <c r="C72" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D72" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E72" s="9">
+      <c r="C72" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D72" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E72" s="10">
         <v>55.2</v>
       </c>
-      <c r="F72" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G72" s="9">
+      <c r="F72" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G72" s="10">
         <v>54.7</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A73" s="4">
+      <c r="A73" s="7">
         <v>40513</v>
       </c>
-      <c r="B73" s="4">
+      <c r="B73" s="7">
         <v>40544</v>
       </c>
-      <c r="C73" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D73" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E73" s="9">
+      <c r="C73" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D73" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E73" s="10">
         <v>53.9</v>
       </c>
-      <c r="F73" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G73" s="9">
+      <c r="F73" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G73" s="10">
         <v>55.2</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A74" s="4">
+      <c r="A74" s="7">
         <v>40544</v>
       </c>
-      <c r="B74" s="4">
+      <c r="B74" s="7">
         <v>40575</v>
       </c>
-      <c r="C74" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D74" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E74" s="9">
+      <c r="C74" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D74" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E74" s="10">
         <v>52.9</v>
       </c>
-      <c r="F74" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G74" s="9">
+      <c r="F74" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G74" s="10">
         <v>53.9</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A75" s="4">
+      <c r="A75" s="7">
         <v>40575</v>
       </c>
-      <c r="B75" s="4">
+      <c r="B75" s="7">
         <v>40603</v>
       </c>
-      <c r="C75" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D75" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E75" s="9">
+      <c r="C75" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D75" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E75" s="10">
         <v>52.2</v>
       </c>
-      <c r="F75" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G75" s="9">
+      <c r="F75" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G75" s="10">
         <v>52.9</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A76" s="4">
+      <c r="A76" s="7">
         <v>40603</v>
       </c>
-      <c r="B76" s="4">
+      <c r="B76" s="7">
         <v>40634</v>
       </c>
-      <c r="C76" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D76" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E76" s="9">
+      <c r="C76" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D76" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E76" s="10">
         <v>53.4</v>
       </c>
-      <c r="F76" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G76" s="9">
+      <c r="F76" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G76" s="10">
         <v>52.2</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A77" s="4">
+      <c r="A77" s="7">
         <v>40634</v>
       </c>
-      <c r="B77" s="4">
+      <c r="B77" s="7">
         <v>40664</v>
       </c>
-      <c r="C77" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D77" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E77" s="9">
+      <c r="C77" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D77" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E77" s="10">
         <v>52.9</v>
       </c>
-      <c r="F77" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G77" s="9">
+      <c r="F77" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G77" s="10">
         <v>53.4</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A78" s="4">
+      <c r="A78" s="7">
         <v>40664</v>
       </c>
-      <c r="B78" s="4">
+      <c r="B78" s="7">
         <v>40695</v>
       </c>
-      <c r="C78" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D78" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E78" s="9">
+      <c r="C78" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D78" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E78" s="10">
         <v>52</v>
       </c>
-      <c r="F78" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G78" s="9">
+      <c r="F78" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G78" s="10">
         <v>52.9</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A79" s="4">
+      <c r="A79" s="7">
         <v>40695</v>
       </c>
-      <c r="B79" s="4">
+      <c r="B79" s="7">
         <v>40725</v>
       </c>
-      <c r="C79" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D79" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E79" s="9">
+      <c r="C79" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D79" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E79" s="10">
         <v>50.9</v>
       </c>
-      <c r="F79" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G79" s="9">
+      <c r="F79" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G79" s="10">
         <v>52</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A80" s="4">
+      <c r="A80" s="7">
         <v>40725</v>
       </c>
-      <c r="B80" s="4">
+      <c r="B80" s="7">
         <v>40756</v>
       </c>
-      <c r="C80" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D80" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E80" s="9">
+      <c r="C80" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D80" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E80" s="10">
         <v>50.7</v>
       </c>
-      <c r="F80" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G80" s="9">
+      <c r="F80" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G80" s="10">
         <v>50.9</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A81" s="4">
+      <c r="A81" s="7">
         <v>40756</v>
       </c>
-      <c r="B81" s="4">
+      <c r="B81" s="7">
         <v>40787</v>
       </c>
-      <c r="C81" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D81" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E81" s="9">
+      <c r="C81" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D81" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E81" s="10">
         <v>50.9</v>
       </c>
-      <c r="F81" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G81" s="9">
+      <c r="F81" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G81" s="10">
         <v>50.7</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A82" s="4">
+      <c r="A82" s="7">
         <v>40787</v>
       </c>
-      <c r="B82" s="4">
+      <c r="B82" s="7">
         <v>40817</v>
       </c>
-      <c r="C82" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D82" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E82" s="9">
+      <c r="C82" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D82" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E82" s="10">
         <v>51.2</v>
       </c>
-      <c r="F82" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G82" s="9">
+      <c r="F82" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G82" s="10">
         <v>50.9</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A83" s="4">
+      <c r="A83" s="7">
         <v>40817</v>
       </c>
-      <c r="B83" s="4">
+      <c r="B83" s="7">
         <v>40848</v>
       </c>
-      <c r="C83" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D83" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E83" s="9">
+      <c r="C83" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D83" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E83" s="10">
         <v>50.4</v>
       </c>
-      <c r="F83" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G83" s="9">
+      <c r="F83" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G83" s="10">
         <v>51.2</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A84" s="4">
+      <c r="A84" s="7">
         <v>40848</v>
       </c>
-      <c r="B84" s="4">
+      <c r="B84" s="7">
         <v>40878</v>
       </c>
-      <c r="C84" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D84" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E84" s="9">
+      <c r="C84" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D84" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E84" s="10">
         <v>49</v>
       </c>
-      <c r="F84" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G84" s="9">
+      <c r="F84" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G84" s="10">
         <v>50.4</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A85" s="4">
+      <c r="A85" s="7">
         <v>40878</v>
       </c>
-      <c r="B85" s="4">
+      <c r="B85" s="7">
         <v>40909</v>
       </c>
-      <c r="C85" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D85" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E85" s="9">
+      <c r="C85" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D85" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E85" s="10">
         <v>50.3</v>
       </c>
-      <c r="F85" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G85" s="9">
+      <c r="F85" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G85" s="10">
         <v>49</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A86" s="4">
+      <c r="A86" s="7">
         <v>40909</v>
       </c>
-      <c r="B86" s="4">
+      <c r="B86" s="7">
         <v>40940</v>
       </c>
-      <c r="C86" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D86" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E86" s="9">
+      <c r="C86" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D86" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E86" s="10">
         <v>50.5</v>
       </c>
-      <c r="F86" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G86" s="9">
+      <c r="F86" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G86" s="10">
         <v>50.3</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A87" s="4">
+      <c r="A87" s="7">
         <v>40940</v>
       </c>
-      <c r="B87" s="4">
+      <c r="B87" s="7">
         <v>40969</v>
       </c>
-      <c r="C87" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D87" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E87" s="9">
+      <c r="C87" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D87" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E87" s="10">
         <v>51</v>
       </c>
-      <c r="F87" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G87" s="9">
+      <c r="F87" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G87" s="10">
         <v>50.5</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A88" s="4">
+      <c r="A88" s="7">
         <v>40969</v>
       </c>
-      <c r="B88" s="4">
+      <c r="B88" s="7">
         <v>41000</v>
       </c>
-      <c r="C88" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D88" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E88" s="9">
+      <c r="C88" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D88" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E88" s="10">
         <v>53.1</v>
       </c>
-      <c r="F88" s="9">
+      <c r="F88" s="10">
         <v>51</v>
       </c>
-      <c r="G88" s="9">
+      <c r="G88" s="10">
         <v>51</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A89" s="4">
+      <c r="A89" s="7">
         <v>41000</v>
       </c>
-      <c r="B89" s="4">
+      <c r="B89" s="7">
         <v>41030</v>
       </c>
-      <c r="C89" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D89" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E89" s="9">
+      <c r="C89" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D89" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E89" s="10">
         <v>53.3</v>
       </c>
-      <c r="F89" s="9">
+      <c r="F89" s="10">
         <v>53.6</v>
       </c>
-      <c r="G89" s="9">
+      <c r="G89" s="10">
         <v>53.1</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A90" s="4">
+      <c r="A90" s="7">
         <v>41030</v>
       </c>
-      <c r="B90" s="4">
+      <c r="B90" s="7">
         <v>41061</v>
       </c>
-      <c r="C90" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D90" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E90" s="9">
+      <c r="C90" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D90" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E90" s="10">
         <v>50.4</v>
       </c>
-      <c r="F90" s="9">
+      <c r="F90" s="10">
         <v>52.2</v>
       </c>
-      <c r="G90" s="9">
+      <c r="G90" s="10">
         <v>53.3</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A91" s="4">
+      <c r="A91" s="7">
         <v>41061</v>
       </c>
-      <c r="B91" s="4">
+      <c r="B91" s="7">
         <v>41091</v>
       </c>
-      <c r="C91" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D91" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E91" s="9">
+      <c r="C91" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D91" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E91" s="10">
         <v>50.2</v>
       </c>
-      <c r="F91" s="9">
+      <c r="F91" s="10">
         <v>49.8</v>
       </c>
-      <c r="G91" s="9">
+      <c r="G91" s="10">
         <v>50.4</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A92" s="4">
+      <c r="A92" s="7">
         <v>41091</v>
       </c>
-      <c r="B92" s="4">
+      <c r="B92" s="7">
         <v>41122</v>
       </c>
-      <c r="C92" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D92" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E92" s="9">
+      <c r="C92" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D92" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E92" s="10">
         <v>50.1</v>
       </c>
-      <c r="F92" s="9">
+      <c r="F92" s="10">
         <v>50.3</v>
       </c>
-      <c r="G92" s="9">
+      <c r="G92" s="10">
         <v>50.2</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A93" s="4">
+      <c r="A93" s="7">
         <v>41122</v>
       </c>
-      <c r="B93" s="4">
+      <c r="B93" s="7">
         <v>41153</v>
       </c>
-      <c r="C93" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D93" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E93" s="9">
+      <c r="C93" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D93" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E93" s="10">
         <v>49.2</v>
       </c>
-      <c r="F93" s="9">
+      <c r="F93" s="10">
         <v>50</v>
       </c>
-      <c r="G93" s="9">
+      <c r="G93" s="10">
         <v>50.1</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A94" s="4">
+      <c r="A94" s="7">
         <v>41153</v>
       </c>
-      <c r="B94" s="4">
+      <c r="B94" s="7">
         <v>41183</v>
       </c>
-      <c r="C94" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D94" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E94" s="9">
+      <c r="C94" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D94" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E94" s="10">
         <v>49.8</v>
       </c>
-      <c r="F94" s="9">
+      <c r="F94" s="10">
         <v>49.8</v>
       </c>
-      <c r="G94" s="9">
+      <c r="G94" s="10">
         <v>49.2</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A95" s="4">
+      <c r="A95" s="7">
         <v>41183</v>
       </c>
-      <c r="B95" s="4">
+      <c r="B95" s="7">
         <v>41214</v>
       </c>
-      <c r="C95" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D95" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E95" s="9">
+      <c r="C95" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D95" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E95" s="10">
         <v>50.2</v>
       </c>
-      <c r="F95" s="9">
+      <c r="F95" s="10">
         <v>50.3</v>
       </c>
-      <c r="G95" s="9">
+      <c r="G95" s="10">
         <v>49.8</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A96" s="4">
+      <c r="A96" s="7">
         <v>41214</v>
       </c>
-      <c r="B96" s="4">
+      <c r="B96" s="7">
         <v>41244</v>
       </c>
-      <c r="C96" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D96" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E96" s="9">
+      <c r="C96" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D96" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E96" s="10">
         <v>50.6</v>
       </c>
-      <c r="F96" s="9">
+      <c r="F96" s="10">
         <v>50.6</v>
       </c>
-      <c r="G96" s="9">
+      <c r="G96" s="10">
         <v>50.2</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A97" s="4">
+      <c r="A97" s="7">
         <v>41244</v>
       </c>
-      <c r="B97" s="4">
+      <c r="B97" s="7">
         <v>41275</v>
       </c>
-      <c r="C97" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D97" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E97" s="9">
+      <c r="C97" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D97" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E97" s="10">
         <v>50.6</v>
       </c>
-      <c r="F97" s="9">
+      <c r="F97" s="10">
         <v>51</v>
       </c>
-      <c r="G97" s="9">
+      <c r="G97" s="10">
         <v>50.6</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A98" s="4">
+      <c r="A98" s="7">
         <v>41275</v>
       </c>
-      <c r="B98" s="4">
+      <c r="B98" s="7">
         <v>41306</v>
       </c>
-      <c r="C98" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D98" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E98" s="9">
+      <c r="C98" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D98" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E98" s="10">
         <v>50.4</v>
       </c>
-      <c r="F98" s="9">
+      <c r="F98" s="10">
         <v>50.9</v>
       </c>
-      <c r="G98" s="9">
+      <c r="G98" s="10">
         <v>50.6</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A99" s="4">
+      <c r="A99" s="7">
         <v>41306</v>
       </c>
-      <c r="B99" s="4">
+      <c r="B99" s="7">
         <v>41334</v>
       </c>
-      <c r="C99" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D99" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E99" s="9">
+      <c r="C99" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D99" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E99" s="10">
         <v>50.1</v>
       </c>
-      <c r="F99" s="9">
+      <c r="F99" s="10">
         <v>50.2</v>
       </c>
-      <c r="G99" s="9">
+      <c r="G99" s="10">
         <v>50.4</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A100" s="4">
+      <c r="A100" s="7">
         <v>41334</v>
       </c>
-      <c r="B100" s="4">
+      <c r="B100" s="7">
         <v>41365</v>
       </c>
-      <c r="C100" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D100" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E100" s="9">
+      <c r="C100" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D100" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E100" s="10">
         <v>50.9</v>
       </c>
-      <c r="F100" s="9">
+      <c r="F100" s="10">
         <v>52</v>
       </c>
-      <c r="G100" s="9">
+      <c r="G100" s="10">
         <v>50.1</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A101" s="4">
+      <c r="A101" s="7">
         <v>41365</v>
       </c>
-      <c r="B101" s="4">
+      <c r="B101" s="7">
         <v>41395</v>
       </c>
-      <c r="C101" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D101" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E101" s="9">
+      <c r="C101" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D101" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E101" s="10">
         <v>50.6</v>
       </c>
-      <c r="F101" s="9">
+      <c r="F101" s="10">
         <v>51</v>
       </c>
-      <c r="G101" s="9">
+      <c r="G101" s="10">
         <v>50.9</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A102" s="4">
+      <c r="A102" s="7">
         <v>41395</v>
       </c>
-      <c r="B102" s="4">
+      <c r="B102" s="7">
         <v>41426</v>
       </c>
-      <c r="C102" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D102" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E102" s="9">
+      <c r="C102" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D102" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E102" s="10">
         <v>50.8</v>
       </c>
-      <c r="F102" s="9">
+      <c r="F102" s="10">
         <v>50.1</v>
       </c>
-      <c r="G102" s="9">
+      <c r="G102" s="10">
         <v>50.6</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A103" s="4">
+      <c r="A103" s="7">
         <v>41426</v>
       </c>
-      <c r="B103" s="4">
+      <c r="B103" s="7">
         <v>41456</v>
       </c>
-      <c r="C103" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D103" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E103" s="9">
+      <c r="C103" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D103" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E103" s="10">
         <v>50.1</v>
       </c>
-      <c r="F103" s="9">
+      <c r="F103" s="10">
         <v>50</v>
       </c>
-      <c r="G103" s="9">
+      <c r="G103" s="10">
         <v>50.8</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A104" s="4">
+      <c r="A104" s="7">
         <v>41456</v>
       </c>
-      <c r="B104" s="4">
+      <c r="B104" s="7">
         <v>41487</v>
       </c>
-      <c r="C104" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D104" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E104" s="9">
+      <c r="C104" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D104" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E104" s="10">
         <v>50.3</v>
       </c>
-      <c r="F104" s="9">
+      <c r="F104" s="10">
         <v>49.9</v>
       </c>
-      <c r="G104" s="9">
+      <c r="G104" s="10">
         <v>50.1</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A105" s="4">
+      <c r="A105" s="7">
         <v>41487</v>
       </c>
-      <c r="B105" s="4">
+      <c r="B105" s="7">
         <v>41518</v>
       </c>
-      <c r="C105" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D105" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E105" s="9">
+      <c r="C105" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D105" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E105" s="10">
         <v>51</v>
       </c>
-      <c r="F105" s="9">
+      <c r="F105" s="10">
         <v>50.6</v>
       </c>
-      <c r="G105" s="9">
+      <c r="G105" s="10">
         <v>50.3</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A106" s="4">
+      <c r="A106" s="7">
         <v>41518</v>
       </c>
-      <c r="B106" s="4">
+      <c r="B106" s="7">
         <v>41548</v>
       </c>
-      <c r="C106" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D106" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E106" s="9">
+      <c r="C106" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D106" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E106" s="10">
         <v>51.1</v>
       </c>
-      <c r="F106" s="9">
+      <c r="F106" s="10">
         <v>51.5</v>
       </c>
-      <c r="G106" s="9">
+      <c r="G106" s="10">
         <v>51</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A107" s="4">
+      <c r="A107" s="7">
         <v>41548</v>
       </c>
-      <c r="B107" s="4">
+      <c r="B107" s="7">
         <v>41579</v>
       </c>
-      <c r="C107" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D107" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E107" s="9">
+      <c r="C107" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D107" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E107" s="10">
         <v>51.4</v>
       </c>
-      <c r="F107" s="9">
+      <c r="F107" s="10">
         <v>51.2</v>
       </c>
-      <c r="G107" s="9">
+      <c r="G107" s="10">
         <v>51.1</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A108" s="4">
+      <c r="A108" s="7">
         <v>41579</v>
       </c>
-      <c r="B108" s="4">
+      <c r="B108" s="7">
         <v>41609</v>
       </c>
-      <c r="C108" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D108" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E108" s="9">
+      <c r="C108" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D108" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E108" s="10">
         <v>51.4</v>
       </c>
-      <c r="F108" s="9">
+      <c r="F108" s="10">
         <v>51.1</v>
       </c>
-      <c r="G108" s="9">
+      <c r="G108" s="10">
         <v>51.4</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A109" s="4">
+      <c r="A109" s="7">
         <v>41609</v>
       </c>
-      <c r="B109" s="4">
+      <c r="B109" s="7">
         <v>41640</v>
       </c>
-      <c r="C109" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D109" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E109" s="9">
+      <c r="C109" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D109" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E109" s="10">
         <v>51</v>
       </c>
-      <c r="F109" s="9">
+      <c r="F109" s="10">
         <v>51.2</v>
       </c>
-      <c r="G109" s="9">
+      <c r="G109" s="10">
         <v>51.4</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A110" s="4">
+      <c r="A110" s="7">
         <v>41640</v>
       </c>
-      <c r="B110" s="4">
+      <c r="B110" s="7">
         <v>41671</v>
       </c>
-      <c r="C110" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D110" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E110" s="9">
+      <c r="C110" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D110" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E110" s="10">
         <v>50.5</v>
       </c>
-      <c r="F110" s="9">
+      <c r="F110" s="10">
         <v>50.5</v>
       </c>
-      <c r="G110" s="9">
+      <c r="G110" s="10">
         <v>51</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A111" s="4">
+      <c r="A111" s="7">
         <v>41671</v>
       </c>
-      <c r="B111" s="4">
+      <c r="B111" s="7">
         <v>41699</v>
       </c>
-      <c r="C111" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D111" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E111" s="9">
+      <c r="C111" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D111" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E111" s="10">
         <v>50.2</v>
       </c>
-      <c r="F111" s="9">
+      <c r="F111" s="10">
         <v>50.1</v>
       </c>
-      <c r="G111" s="9">
+      <c r="G111" s="10">
         <v>50.5</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A112" s="4">
+      <c r="A112" s="7">
         <v>41699</v>
       </c>
-      <c r="B112" s="4">
+      <c r="B112" s="7">
         <v>41730</v>
       </c>
-      <c r="C112" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D112" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E112" s="9">
+      <c r="C112" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D112" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E112" s="10">
         <v>50.3</v>
       </c>
-      <c r="F112" s="9">
+      <c r="F112" s="10">
         <v>50.3</v>
       </c>
-      <c r="G112" s="9">
+      <c r="G112" s="10">
         <v>50.2</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A113" s="4">
+      <c r="A113" s="7">
         <v>41730</v>
       </c>
-      <c r="B113" s="4">
+      <c r="B113" s="7">
         <v>41760</v>
       </c>
-      <c r="C113" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D113" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E113" s="9">
+      <c r="C113" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D113" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E113" s="10">
         <v>50.4</v>
       </c>
-      <c r="F113" s="9">
+      <c r="F113" s="10">
         <v>50.5</v>
       </c>
-      <c r="G113" s="9">
+      <c r="G113" s="10">
         <v>50.3</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A114" s="4">
+      <c r="A114" s="7">
         <v>41760</v>
       </c>
-      <c r="B114" s="4">
+      <c r="B114" s="7">
         <v>41791</v>
       </c>
-      <c r="C114" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D114" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E114" s="9">
+      <c r="C114" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D114" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E114" s="10">
         <v>50.8</v>
       </c>
-      <c r="F114" s="9">
+      <c r="F114" s="10">
         <v>50.6</v>
       </c>
-      <c r="G114" s="9">
+      <c r="G114" s="10">
         <v>50.4</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A115" s="4">
+      <c r="A115" s="7">
         <v>41791</v>
       </c>
-      <c r="B115" s="4">
+      <c r="B115" s="7">
         <v>41821</v>
       </c>
-      <c r="C115" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D115" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E115" s="9">
+      <c r="C115" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D115" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E115" s="10">
         <v>51</v>
       </c>
-      <c r="F115" s="9">
+      <c r="F115" s="10">
         <v>51</v>
       </c>
-      <c r="G115" s="9">
+      <c r="G115" s="10">
         <v>50.8</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A116" s="4">
+      <c r="A116" s="7">
         <v>41821</v>
       </c>
-      <c r="B116" s="4">
+      <c r="B116" s="7">
         <v>41852</v>
       </c>
-      <c r="C116" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D116" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E116" s="9">
+      <c r="C116" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D116" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E116" s="10">
         <v>51.7</v>
       </c>
-      <c r="F116" s="9">
+      <c r="F116" s="10">
         <v>51.4</v>
       </c>
-      <c r="G116" s="9">
+      <c r="G116" s="10">
         <v>51</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A117" s="4">
+      <c r="A117" s="7">
         <v>41852</v>
       </c>
-      <c r="B117" s="4">
+      <c r="B117" s="7">
         <v>41883</v>
       </c>
-      <c r="C117" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D117" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E117" s="9">
+      <c r="C117" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D117" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E117" s="10">
         <v>51.1</v>
       </c>
-      <c r="F117" s="9">
+      <c r="F117" s="10">
         <v>51.2</v>
       </c>
-      <c r="G117" s="9">
+      <c r="G117" s="10">
         <v>51.7</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A118" s="4">
+      <c r="A118" s="7">
         <v>41883</v>
       </c>
-      <c r="B118" s="4">
+      <c r="B118" s="7">
         <v>41913</v>
       </c>
-      <c r="C118" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D118" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E118" s="9">
+      <c r="C118" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D118" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E118" s="10">
         <v>51.1</v>
       </c>
-      <c r="F118" s="9">
+      <c r="F118" s="10">
         <v>51</v>
       </c>
-      <c r="G118" s="9">
+      <c r="G118" s="10">
         <v>51.1</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A119" s="4">
+      <c r="A119" s="7">
         <v>41913</v>
       </c>
-      <c r="B119" s="4">
+      <c r="B119" s="7">
         <v>41944</v>
       </c>
-      <c r="C119" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D119" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E119" s="9">
+      <c r="C119" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D119" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E119" s="10">
         <v>50.8</v>
       </c>
-      <c r="F119" s="9">
+      <c r="F119" s="10">
         <v>51.2</v>
       </c>
-      <c r="G119" s="9">
+      <c r="G119" s="10">
         <v>51.1</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A120" s="4">
+      <c r="A120" s="7">
         <v>41944</v>
       </c>
-      <c r="B120" s="4">
+      <c r="B120" s="7">
         <v>41974</v>
       </c>
-      <c r="C120" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D120" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E120" s="9">
+      <c r="C120" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D120" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E120" s="10">
         <v>50.3</v>
       </c>
-      <c r="F120" s="9">
+      <c r="F120" s="10">
         <v>50.5</v>
       </c>
-      <c r="G120" s="9">
+      <c r="G120" s="10">
         <v>50.8</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A121" s="4">
+      <c r="A121" s="7">
         <v>41974</v>
       </c>
-      <c r="B121" s="4">
+      <c r="B121" s="7">
         <v>42005</v>
       </c>
-      <c r="C121" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D121" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E121" s="9">
+      <c r="C121" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D121" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E121" s="10">
         <v>50.1</v>
       </c>
-      <c r="F121" s="9">
+      <c r="F121" s="10">
         <v>50.1</v>
       </c>
-      <c r="G121" s="9">
+      <c r="G121" s="10">
         <v>50.3</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A122" s="4">
+      <c r="A122" s="7">
         <v>42005</v>
       </c>
-      <c r="B122" s="4">
+      <c r="B122" s="7">
         <v>42036</v>
       </c>
-      <c r="C122" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D122" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E122" s="9">
+      <c r="C122" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D122" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E122" s="10">
         <v>49.8</v>
       </c>
-      <c r="F122" s="9">
+      <c r="F122" s="10">
         <v>50.2</v>
       </c>
-      <c r="G122" s="9">
+      <c r="G122" s="10">
         <v>50.1</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A123" s="4">
+      <c r="A123" s="7">
         <v>42036</v>
       </c>
-      <c r="B123" s="4">
+      <c r="B123" s="7">
         <v>42064</v>
       </c>
-      <c r="C123" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D123" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E123" s="9">
+      <c r="C123" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D123" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E123" s="10">
         <v>49.9</v>
       </c>
-      <c r="F123" s="9">
+      <c r="F123" s="10">
         <v>49.7</v>
       </c>
-      <c r="G123" s="9">
+      <c r="G123" s="10">
         <v>49.8</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A124" s="4">
+      <c r="A124" s="7">
         <v>42064</v>
       </c>
-      <c r="B124" s="4">
+      <c r="B124" s="7">
         <v>42095</v>
       </c>
-      <c r="C124" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D124" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E124" s="9">
+      <c r="C124" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D124" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E124" s="10">
         <v>50.1</v>
       </c>
-      <c r="F124" s="9">
+      <c r="F124" s="10">
         <v>49.7</v>
       </c>
-      <c r="G124" s="9">
+      <c r="G124" s="10">
         <v>49.9</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A125" s="4">
+      <c r="A125" s="7">
         <v>42095</v>
       </c>
-      <c r="B125" s="4">
+      <c r="B125" s="7">
         <v>42125</v>
       </c>
-      <c r="C125" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D125" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E125" s="9">
+      <c r="C125" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D125" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E125" s="10">
         <v>50.1</v>
       </c>
-      <c r="F125" s="9">
+      <c r="F125" s="10">
         <v>50</v>
       </c>
-      <c r="G125" s="9">
+      <c r="G125" s="10">
         <v>50.1</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A126" s="4">
+      <c r="A126" s="7">
         <v>42125</v>
       </c>
-      <c r="B126" s="4">
+      <c r="B126" s="7">
         <v>42156</v>
       </c>
-      <c r="C126" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D126" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E126" s="9">
+      <c r="C126" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D126" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E126" s="10">
         <v>50.2</v>
       </c>
-      <c r="F126" s="9">
+      <c r="F126" s="10">
         <v>50.2</v>
       </c>
-      <c r="G126" s="9">
+      <c r="G126" s="10">
         <v>50.1</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A127" s="4">
+      <c r="A127" s="7">
         <v>42156</v>
       </c>
-      <c r="B127" s="4">
+      <c r="B127" s="7">
         <v>42186</v>
       </c>
-      <c r="C127" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D127" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E127" s="9">
+      <c r="C127" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D127" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E127" s="10">
         <v>50.2</v>
       </c>
-      <c r="F127" s="9">
+      <c r="F127" s="10">
         <v>50.3</v>
       </c>
-      <c r="G127" s="9">
+      <c r="G127" s="10">
         <v>50.2</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A128" s="4">
+      <c r="A128" s="7">
         <v>42186</v>
       </c>
-      <c r="B128" s="4">
+      <c r="B128" s="7">
         <v>42217</v>
       </c>
-      <c r="C128" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D128" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E128" s="9">
+      <c r="C128" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D128" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E128" s="10">
         <v>50</v>
       </c>
-      <c r="F128" s="9">
+      <c r="F128" s="10">
         <v>50.2</v>
       </c>
-      <c r="G128" s="9">
+      <c r="G128" s="10">
         <v>50.2</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A129" s="4">
+      <c r="A129" s="7">
         <v>42217</v>
       </c>
-      <c r="B129" s="4">
+      <c r="B129" s="7">
         <v>42248</v>
       </c>
-      <c r="C129" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D129" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E129" s="9">
+      <c r="C129" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D129" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E129" s="10">
         <v>49.7</v>
       </c>
-      <c r="F129" s="9">
+      <c r="F129" s="10">
         <v>49.7</v>
       </c>
-      <c r="G129" s="9">
+      <c r="G129" s="10">
         <v>50</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A130" s="4">
+      <c r="A130" s="7">
         <v>42248</v>
       </c>
-      <c r="B130" s="4">
+      <c r="B130" s="7">
         <v>42278</v>
       </c>
-      <c r="C130" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D130" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E130" s="9">
+      <c r="C130" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D130" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E130" s="10">
         <v>49.8</v>
       </c>
-      <c r="F130" s="9">
+      <c r="F130" s="10">
         <v>49.6</v>
       </c>
-      <c r="G130" s="9">
+      <c r="G130" s="10">
         <v>49.7</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A131" s="4">
+      <c r="A131" s="7">
         <v>42278</v>
       </c>
-      <c r="B131" s="4">
+      <c r="B131" s="7">
         <v>42309</v>
       </c>
-      <c r="C131" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D131" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E131" s="9">
+      <c r="C131" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D131" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E131" s="10">
         <v>49.8</v>
       </c>
-      <c r="F131" s="9">
+      <c r="F131" s="10">
         <v>50</v>
       </c>
-      <c r="G131" s="9">
+      <c r="G131" s="10">
         <v>49.8</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A132" s="4">
+      <c r="A132" s="7">
         <v>42309</v>
       </c>
-      <c r="B132" s="4">
+      <c r="B132" s="7">
         <v>42339</v>
       </c>
-      <c r="C132" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D132" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E132" s="9">
+      <c r="C132" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D132" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E132" s="10">
         <v>49.6</v>
       </c>
-      <c r="F132" s="9">
+      <c r="F132" s="10">
         <v>49.8</v>
       </c>
-      <c r="G132" s="9">
+      <c r="G132" s="10">
         <v>49.8</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A133" s="4">
+      <c r="A133" s="7">
         <v>42339</v>
       </c>
-      <c r="B133" s="4">
+      <c r="B133" s="7">
         <v>42370</v>
       </c>
-      <c r="C133" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D133" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E133" s="9">
+      <c r="C133" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D133" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E133" s="10">
         <v>49.7</v>
       </c>
-      <c r="F133" s="9">
+      <c r="F133" s="10">
         <v>49.7</v>
       </c>
-      <c r="G133" s="9">
+      <c r="G133" s="10">
         <v>49.6</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A134" s="4">
+      <c r="A134" s="7">
         <v>42370</v>
       </c>
-      <c r="B134" s="4">
+      <c r="B134" s="7">
         <v>42401</v>
       </c>
-      <c r="C134" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D134" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E134" s="9">
+      <c r="C134" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D134" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E134" s="10">
         <v>49.4</v>
       </c>
-      <c r="F134" s="9">
+      <c r="F134" s="10">
         <v>49.6</v>
       </c>
-      <c r="G134" s="9">
+      <c r="G134" s="10">
         <v>49.7</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A135" s="4">
+      <c r="A135" s="7">
         <v>42401</v>
       </c>
-      <c r="B135" s="4">
+      <c r="B135" s="7">
         <v>42430</v>
       </c>
-      <c r="C135" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D135" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E135" s="9">
+      <c r="C135" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D135" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E135" s="10">
         <v>49</v>
       </c>
-      <c r="F135" s="9">
+      <c r="F135" s="10">
         <v>49.3</v>
       </c>
-      <c r="G135" s="9">
+      <c r="G135" s="10">
         <v>49.4</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A136" s="4">
+      <c r="A136" s="7">
         <v>42430</v>
       </c>
-      <c r="B136" s="4">
+      <c r="B136" s="7">
         <v>42461</v>
       </c>
-      <c r="C136" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D136" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E136" s="9">
+      <c r="C136" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D136" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E136" s="10">
         <v>50.2</v>
       </c>
-      <c r="F136" s="9">
+      <c r="F136" s="10">
         <v>49.3</v>
       </c>
-      <c r="G136" s="9">
+      <c r="G136" s="10">
         <v>49</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A137" s="4">
+      <c r="A137" s="7">
         <v>42461</v>
       </c>
-      <c r="B137" s="4">
+      <c r="B137" s="7">
         <v>42491</v>
       </c>
-      <c r="C137" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D137" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E137" s="9">
+      <c r="C137" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D137" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E137" s="10">
         <v>50.1</v>
       </c>
-      <c r="F137" s="9">
+      <c r="F137" s="10">
         <v>50.4</v>
       </c>
-      <c r="G137" s="9">
+      <c r="G137" s="10">
         <v>50.2</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A138" s="4">
+      <c r="A138" s="7">
         <v>42491</v>
       </c>
-      <c r="B138" s="4">
+      <c r="B138" s="7">
         <v>42522</v>
       </c>
-      <c r="C138" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D138" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E138" s="9">
+      <c r="C138" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D138" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E138" s="10">
         <v>50.1</v>
       </c>
-      <c r="F138" s="9">
+      <c r="F138" s="10">
         <v>50</v>
       </c>
-      <c r="G138" s="9">
+      <c r="G138" s="10">
         <v>50.1</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A139" s="4">
+      <c r="A139" s="7">
         <v>42522</v>
       </c>
-      <c r="B139" s="4">
+      <c r="B139" s="7">
         <v>42552</v>
       </c>
-      <c r="C139" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D139" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E139" s="9">
+      <c r="C139" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D139" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E139" s="10">
         <v>50</v>
       </c>
-      <c r="F139" s="9">
+      <c r="F139" s="10">
         <v>50</v>
       </c>
-      <c r="G139" s="9">
+      <c r="G139" s="10">
         <v>50.1</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A140" s="4">
+      <c r="A140" s="7">
         <v>42552</v>
       </c>
-      <c r="B140" s="4">
+      <c r="B140" s="7">
         <v>42583</v>
       </c>
-      <c r="C140" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D140" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E140" s="9">
+      <c r="C140" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D140" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E140" s="10">
         <v>49.9</v>
       </c>
-      <c r="F140" s="9">
+      <c r="F140" s="10">
         <v>50</v>
       </c>
-      <c r="G140" s="9">
+      <c r="G140" s="10">
         <v>50</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A141" s="4">
+      <c r="A141" s="7">
         <v>42583</v>
       </c>
-      <c r="B141" s="4">
+      <c r="B141" s="7">
         <v>42614</v>
       </c>
-      <c r="C141" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D141" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E141" s="9">
+      <c r="C141" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D141" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E141" s="10">
         <v>50.4</v>
       </c>
-      <c r="F141" s="9">
+      <c r="F141" s="10">
         <v>49.9</v>
       </c>
-      <c r="G141" s="9">
+      <c r="G141" s="10">
         <v>49.9</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A142" s="4">
+      <c r="A142" s="7">
         <v>42614</v>
       </c>
-      <c r="B142" s="4">
+      <c r="B142" s="7">
         <v>42644</v>
       </c>
-      <c r="C142" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D142" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E142" s="9">
+      <c r="C142" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D142" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E142" s="10">
         <v>50.4</v>
       </c>
-      <c r="F142" s="9">
+      <c r="F142" s="10">
         <v>50.4</v>
       </c>
-      <c r="G142" s="9">
+      <c r="G142" s="10">
         <v>50.4</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A143" s="4">
+      <c r="A143" s="7">
         <v>42644</v>
       </c>
-      <c r="B143" s="4">
+      <c r="B143" s="7">
         <v>42675</v>
       </c>
-      <c r="C143" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D143" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E143" s="9">
+      <c r="C143" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D143" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E143" s="10">
         <v>51.2</v>
       </c>
-      <c r="F143" s="9">
+      <c r="F143" s="10">
         <v>50.4</v>
       </c>
-      <c r="G143" s="9">
+      <c r="G143" s="10">
         <v>50.4</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A144" s="4">
+      <c r="A144" s="7">
         <v>42675</v>
       </c>
-      <c r="B144" s="4">
+      <c r="B144" s="7">
         <v>42705</v>
       </c>
-      <c r="C144" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D144" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E144" s="9">
+      <c r="C144" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D144" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E144" s="10">
         <v>51.7</v>
       </c>
-      <c r="F144" s="9">
+      <c r="F144" s="10">
         <v>51</v>
       </c>
-      <c r="G144" s="9">
+      <c r="G144" s="10">
         <v>51.2</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A145" s="4">
+      <c r="A145" s="7">
         <v>42705</v>
       </c>
-      <c r="B145" s="4">
+      <c r="B145" s="7">
         <v>42736</v>
       </c>
-      <c r="C145" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D145" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E145" s="9">
+      <c r="C145" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D145" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E145" s="10">
         <v>51.4</v>
       </c>
-      <c r="F145" s="9">
+      <c r="F145" s="10">
         <v>51.5</v>
       </c>
-      <c r="G145" s="9">
+      <c r="G145" s="10">
         <v>51.7</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A146" s="4">
+      <c r="A146" s="7">
         <v>42736</v>
       </c>
-      <c r="B146" s="4">
+      <c r="B146" s="7">
         <v>42767</v>
       </c>
-      <c r="C146" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D146" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E146" s="9">
+      <c r="C146" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D146" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E146" s="10">
         <v>51.3</v>
       </c>
-      <c r="F146" s="9">
+      <c r="F146" s="10">
         <v>51.2</v>
       </c>
-      <c r="G146" s="9">
+      <c r="G146" s="10">
         <v>51.4</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A147" s="4">
+      <c r="A147" s="7">
         <v>42767</v>
       </c>
-      <c r="B147" s="4">
+      <c r="B147" s="7">
         <v>42795</v>
       </c>
-      <c r="C147" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D147" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E147" s="9">
+      <c r="C147" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D147" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E147" s="10">
         <v>51.6</v>
       </c>
-      <c r="F147" s="9">
+      <c r="F147" s="10">
         <v>51.1</v>
       </c>
-      <c r="G147" s="9">
+      <c r="G147" s="10">
         <v>51.3</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A148" s="4">
+      <c r="A148" s="7">
         <v>42795</v>
       </c>
-      <c r="B148" s="4">
+      <c r="B148" s="7">
         <v>42825</v>
       </c>
-      <c r="C148" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D148" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E148" s="9">
+      <c r="C148" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D148" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E148" s="10">
         <v>51.8</v>
       </c>
-      <c r="F148" s="9">
+      <c r="F148" s="10">
         <v>51.6</v>
       </c>
-      <c r="G148" s="9">
+      <c r="G148" s="10">
         <v>51.6</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A149" s="4">
+      <c r="A149" s="7">
         <v>42826</v>
       </c>
-      <c r="B149" s="4">
+      <c r="B149" s="7">
         <v>42855</v>
       </c>
-      <c r="C149" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D149" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E149" s="9">
+      <c r="C149" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D149" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E149" s="10">
         <v>51.2</v>
       </c>
-      <c r="F149" s="9">
+      <c r="F149" s="10">
         <v>51.6</v>
       </c>
-      <c r="G149" s="9">
+      <c r="G149" s="10">
         <v>51.8</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A150" s="4">
+      <c r="A150" s="7">
         <v>42856</v>
       </c>
-      <c r="B150" s="4">
+      <c r="B150" s="7">
         <v>42886</v>
       </c>
-      <c r="C150" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D150" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E150" s="9">
+      <c r="C150" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D150" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E150" s="10">
         <v>51.2</v>
       </c>
-      <c r="F150" s="9">
+      <c r="F150" s="10">
         <v>51</v>
       </c>
-      <c r="G150" s="9">
+      <c r="G150" s="10">
         <v>51.2</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A151" s="4">
+      <c r="A151" s="7">
         <v>42887</v>
       </c>
-      <c r="B151" s="4">
+      <c r="B151" s="7">
         <v>42916</v>
       </c>
-      <c r="C151" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D151" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E151" s="9">
+      <c r="C151" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D151" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E151" s="10">
         <v>51.7</v>
       </c>
-      <c r="F151" s="9">
+      <c r="F151" s="10">
         <v>51</v>
       </c>
-      <c r="G151" s="9">
+      <c r="G151" s="10">
         <v>51.2</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A152" s="4">
+      <c r="A152" s="7">
         <v>42917</v>
       </c>
-      <c r="B152" s="4">
+      <c r="B152" s="7">
         <v>42947</v>
       </c>
-      <c r="C152" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D152" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E152" s="9">
+      <c r="C152" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D152" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E152" s="10">
         <v>51.4</v>
       </c>
-      <c r="F152" s="9">
+      <c r="F152" s="10">
         <v>51.6</v>
       </c>
-      <c r="G152" s="9">
+      <c r="G152" s="10">
         <v>51.7</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A153" s="4">
+      <c r="A153" s="7">
         <v>42948</v>
       </c>
-      <c r="B153" s="4">
+      <c r="B153" s="7">
         <v>42978</v>
       </c>
-      <c r="C153" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D153" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E153" s="9">
+      <c r="C153" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D153" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E153" s="10">
         <v>51.7</v>
       </c>
-      <c r="F153" s="9">
+      <c r="F153" s="10">
         <v>51.3</v>
       </c>
-      <c r="G153" s="9">
+      <c r="G153" s="10">
         <v>51.4</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A154" s="4">
+      <c r="A154" s="7">
         <v>42979</v>
       </c>
-      <c r="B154" s="4">
+      <c r="B154" s="7">
         <v>43008</v>
       </c>
-      <c r="C154" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D154" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E154" s="9">
+      <c r="C154" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D154" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E154" s="10">
         <v>52.4</v>
       </c>
-      <c r="F154" s="9">
+      <c r="F154" s="10">
         <v>51.5</v>
       </c>
-      <c r="G154" s="9">
+      <c r="G154" s="10">
         <v>51.7</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A155" s="4">
+      <c r="A155" s="7">
         <v>43009</v>
       </c>
-      <c r="B155" s="4">
+      <c r="B155" s="7">
         <v>43039</v>
       </c>
-      <c r="C155" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D155" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E155" s="9">
+      <c r="C155" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D155" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E155" s="10">
         <v>51.6</v>
       </c>
-      <c r="F155" s="9">
+      <c r="F155" s="10">
         <v>52</v>
       </c>
-      <c r="G155" s="9">
+      <c r="G155" s="10">
         <v>52.4</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A156" s="4">
+      <c r="A156" s="7">
         <v>43040</v>
       </c>
-      <c r="B156" s="4">
+      <c r="B156" s="7">
         <v>43069</v>
       </c>
-      <c r="C156" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D156" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E156" s="9">
+      <c r="C156" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D156" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E156" s="10">
         <v>51.8</v>
       </c>
-      <c r="F156" s="9">
+      <c r="F156" s="10">
         <v>51.4</v>
       </c>
-      <c r="G156" s="9">
+      <c r="G156" s="10">
         <v>51.6</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A157" s="4">
+      <c r="A157" s="7">
         <v>43070</v>
       </c>
-      <c r="B157" s="4">
+      <c r="B157" s="7">
         <v>43100</v>
       </c>
-      <c r="C157" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D157" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E157" s="9">
+      <c r="C157" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D157" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E157" s="10">
         <v>51.6</v>
       </c>
-      <c r="F157" s="9">
+      <c r="F157" s="10">
         <v>51.6</v>
       </c>
-      <c r="G157" s="9">
+      <c r="G157" s="10">
         <v>51.8</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A158" s="4">
+      <c r="A158" s="7">
         <v>43101</v>
       </c>
-      <c r="B158" s="4">
+      <c r="B158" s="7">
         <v>43131</v>
       </c>
-      <c r="C158" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D158" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E158" s="9">
+      <c r="C158" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D158" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E158" s="10">
         <v>51.3</v>
       </c>
-      <c r="F158" s="9">
+      <c r="F158" s="10">
         <v>51.5</v>
       </c>
-      <c r="G158" s="9">
+      <c r="G158" s="10">
         <v>51.6</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A159" s="4">
+      <c r="A159" s="7">
         <v>43132</v>
       </c>
-      <c r="B159" s="4">
+      <c r="B159" s="7">
         <v>43159</v>
       </c>
-      <c r="C159" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D159" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E159" s="9">
+      <c r="C159" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D159" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E159" s="10">
         <v>50.3</v>
       </c>
-      <c r="F159" s="9">
+      <c r="F159" s="10">
         <v>51.4</v>
       </c>
-      <c r="G159" s="9">
+      <c r="G159" s="10">
         <v>51.3</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A160" s="4">
+      <c r="A160" s="7">
         <v>43160</v>
       </c>
-      <c r="B160" s="4">
+      <c r="B160" s="7">
         <v>43190</v>
       </c>
-      <c r="C160" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D160" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E160" s="9">
+      <c r="C160" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D160" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E160" s="10">
         <v>51.5</v>
       </c>
-      <c r="F160" s="9">
+      <c r="F160" s="10">
         <v>50.5</v>
       </c>
-      <c r="G160" s="9">
+      <c r="G160" s="10">
         <v>50.3</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A161" s="4">
+      <c r="A161" s="7">
         <v>43191</v>
       </c>
-      <c r="B161" s="4">
+      <c r="B161" s="7">
         <v>43220</v>
       </c>
-      <c r="C161" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D161" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E161" s="9">
+      <c r="C161" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D161" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E161" s="10">
         <v>51.4</v>
       </c>
-      <c r="F161" s="9">
+      <c r="F161" s="10">
         <v>51.3</v>
       </c>
-      <c r="G161" s="9">
+      <c r="G161" s="10">
         <v>51.5</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A162" s="4">
+      <c r="A162" s="7">
         <v>43221</v>
       </c>
-      <c r="B162" s="4">
+      <c r="B162" s="7">
         <v>43251</v>
       </c>
-      <c r="C162" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D162" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E162" s="9">
+      <c r="C162" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D162" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E162" s="10">
         <v>51.9</v>
       </c>
-      <c r="F162" s="9">
+      <c r="F162" s="10">
         <v>51.4</v>
       </c>
-      <c r="G162" s="9">
+      <c r="G162" s="10">
         <v>51.4</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A163" s="4">
+      <c r="A163" s="7">
         <v>43252</v>
       </c>
-      <c r="B163" s="4">
+      <c r="B163" s="7">
         <v>43281</v>
       </c>
-      <c r="C163" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D163" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E163" s="9">
+      <c r="C163" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D163" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E163" s="10">
         <v>51.5</v>
       </c>
-      <c r="F163" s="9">
+      <c r="F163" s="10">
         <v>51.6</v>
       </c>
-      <c r="G163" s="9">
+      <c r="G163" s="10">
         <v>51.9</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A164" s="4">
+      <c r="A164" s="7">
         <v>43282</v>
       </c>
-      <c r="B164" s="4">
+      <c r="B164" s="7">
         <v>43312</v>
       </c>
-      <c r="C164" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D164" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E164" s="9">
+      <c r="C164" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D164" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E164" s="10">
         <v>51.2</v>
       </c>
-      <c r="F164" s="9">
+      <c r="F164" s="10">
         <v>51.4</v>
       </c>
-      <c r="G164" s="9">
+      <c r="G164" s="10">
         <v>51.5</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A165" s="4">
+      <c r="A165" s="7">
         <v>43313</v>
       </c>
-      <c r="B165" s="4">
+      <c r="B165" s="7">
         <v>43343</v>
       </c>
-      <c r="C165" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D165" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E165" s="9">
+      <c r="C165" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D165" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E165" s="10">
         <v>51.3</v>
       </c>
-      <c r="F165" s="9">
+      <c r="F165" s="10">
         <v>51</v>
       </c>
-      <c r="G165" s="9">
+      <c r="G165" s="10">
         <v>51.2</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A166" s="4">
+      <c r="A166" s="7">
         <v>43344</v>
       </c>
-      <c r="B166" s="4">
+      <c r="B166" s="7">
         <v>43373</v>
       </c>
-      <c r="C166" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D166" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E166" s="9">
+      <c r="C166" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D166" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E166" s="10">
         <v>50.8</v>
       </c>
-      <c r="F166" s="9">
+      <c r="F166" s="10">
         <v>51.2</v>
       </c>
-      <c r="G166" s="9">
+      <c r="G166" s="10">
         <v>51.3</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A167" s="4">
+      <c r="A167" s="7">
         <v>43374</v>
       </c>
-      <c r="B167" s="4">
+      <c r="B167" s="7">
         <v>43404</v>
       </c>
-      <c r="C167" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D167" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E167" s="9">
+      <c r="C167" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D167" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E167" s="10">
         <v>50.2</v>
       </c>
-      <c r="F167" s="9">
+      <c r="F167" s="10">
         <v>50.6</v>
       </c>
-      <c r="G167" s="9">
+      <c r="G167" s="10">
         <v>50.8</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A168" s="4">
+      <c r="A168" s="7">
         <v>43405</v>
       </c>
-      <c r="B168" s="4">
+      <c r="B168" s="7">
         <v>43434</v>
       </c>
-      <c r="C168" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D168" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E168" s="9">
+      <c r="C168" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D168" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E168" s="10">
         <v>50</v>
       </c>
-      <c r="F168" s="9">
+      <c r="F168" s="10">
         <v>50.2</v>
       </c>
-      <c r="G168" s="9">
+      <c r="G168" s="10">
         <v>50.2</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A169" s="4">
+      <c r="A169" s="7">
         <v>43435</v>
       </c>
-      <c r="B169" s="4">
+      <c r="B169" s="7">
         <v>43465</v>
       </c>
-      <c r="C169" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D169" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E169" s="9">
+      <c r="C169" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D169" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E169" s="10">
         <v>49.4</v>
       </c>
-      <c r="F169" s="9">
+      <c r="F169" s="10">
         <v>50</v>
       </c>
-      <c r="G169" s="9">
+      <c r="G169" s="10">
         <v>50</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A170" s="4">
+      <c r="A170" s="7">
         <v>43466</v>
       </c>
-      <c r="B170" s="4">
+      <c r="B170" s="7">
         <v>43496</v>
       </c>
-      <c r="C170" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D170" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E170" s="9">
+      <c r="C170" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D170" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E170" s="10">
         <v>49.5</v>
       </c>
-      <c r="F170" s="9">
+      <c r="F170" s="10">
         <v>49.3</v>
       </c>
-      <c r="G170" s="9">
+      <c r="G170" s="10">
         <v>49.4</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A171" s="4">
+      <c r="A171" s="7">
         <v>43497</v>
       </c>
-      <c r="B171" s="4">
+      <c r="B171" s="7">
         <v>43524</v>
       </c>
-      <c r="C171" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D171" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E171" s="9">
+      <c r="C171" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D171" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E171" s="10">
         <v>49.2</v>
       </c>
-      <c r="F171" s="9">
+      <c r="F171" s="10">
         <v>49.5</v>
       </c>
-      <c r="G171" s="9">
+      <c r="G171" s="10">
         <v>49.5</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A172" s="4">
+      <c r="A172" s="7">
         <v>43525</v>
       </c>
-      <c r="B172" s="4">
+      <c r="B172" s="7">
         <v>43555</v>
       </c>
-      <c r="C172" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D172" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E172" s="9">
+      <c r="C172" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D172" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E172" s="10">
         <v>50.5</v>
       </c>
-      <c r="F172" s="9">
+      <c r="F172" s="10">
         <v>49.5</v>
       </c>
-      <c r="G172" s="9">
+      <c r="G172" s="10">
         <v>49.2</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A173" s="4">
+      <c r="A173" s="7">
         <v>43556</v>
       </c>
-      <c r="B173" s="4">
+      <c r="B173" s="7">
         <v>43585</v>
       </c>
-      <c r="C173" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D173" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E173" s="9">
+      <c r="C173" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D173" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E173" s="10">
         <v>50.1</v>
       </c>
-      <c r="F173" s="9">
+      <c r="F173" s="10">
         <v>50.7</v>
       </c>
-      <c r="G173" s="9">
+      <c r="G173" s="10">
         <v>50.5</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A174" s="4">
+      <c r="A174" s="7">
         <v>43586</v>
       </c>
-      <c r="B174" s="4">
+      <c r="B174" s="7">
         <v>43616</v>
       </c>
-      <c r="C174" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D174" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E174" s="9">
+      <c r="C174" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D174" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E174" s="10">
         <v>49.4</v>
       </c>
-      <c r="F174" s="9">
+      <c r="F174" s="10">
         <v>49.9</v>
       </c>
-      <c r="G174" s="9">
+      <c r="G174" s="10">
         <v>50.1</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A175" s="4">
+      <c r="A175" s="7">
         <v>43617</v>
       </c>
-      <c r="B175" s="4">
+      <c r="B175" s="7">
         <v>43646</v>
       </c>
-      <c r="C175" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D175" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E175" s="9">
+      <c r="C175" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D175" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E175" s="10">
         <v>49.4</v>
       </c>
-      <c r="F175" s="9">
+      <c r="F175" s="10">
         <v>49.5</v>
       </c>
-      <c r="G175" s="9">
+      <c r="G175" s="10">
         <v>49.4</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A176" s="4">
+      <c r="A176" s="7">
         <v>43647</v>
       </c>
-      <c r="B176" s="4">
+      <c r="B176" s="7">
         <v>43677</v>
       </c>
-      <c r="C176" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D176" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E176" s="9">
+      <c r="C176" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D176" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E176" s="10">
         <v>49.7</v>
       </c>
-      <c r="F176" s="9">
+      <c r="F176" s="10">
         <v>49.6</v>
       </c>
-      <c r="G176" s="9">
+      <c r="G176" s="10">
         <v>49.4</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A177" s="4">
+      <c r="A177" s="7">
         <v>43678</v>
       </c>
-      <c r="B177" s="4">
+      <c r="B177" s="7">
         <v>43708</v>
       </c>
-      <c r="C177" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D177" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E177" s="9">
+      <c r="C177" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D177" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E177" s="10">
         <v>49.5</v>
       </c>
-      <c r="F177" s="9">
+      <c r="F177" s="10">
         <v>49.7</v>
       </c>
-      <c r="G177" s="9">
+      <c r="G177" s="10">
         <v>49.7</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A178" s="4">
+      <c r="A178" s="7">
         <v>43709</v>
       </c>
-      <c r="B178" s="4">
+      <c r="B178" s="7">
         <v>43738</v>
       </c>
-      <c r="C178" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D178" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E178" s="9">
+      <c r="C178" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D178" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E178" s="10">
         <v>49.8</v>
       </c>
-      <c r="F178" s="9">
+      <c r="F178" s="10">
         <v>49.5</v>
       </c>
-      <c r="G178" s="9">
+      <c r="G178" s="10">
         <v>49.5</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A179" s="4">
+      <c r="A179" s="7">
         <v>43739</v>
       </c>
-      <c r="B179" s="4">
+      <c r="B179" s="7">
         <v>43769</v>
       </c>
-      <c r="C179" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D179" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E179" s="9">
+      <c r="C179" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D179" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E179" s="10">
         <v>49.3</v>
       </c>
-      <c r="F179" s="9">
+      <c r="F179" s="10">
         <v>49.9</v>
       </c>
-      <c r="G179" s="9">
+      <c r="G179" s="10">
         <v>49.8</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A180" s="4">
+      <c r="A180" s="7">
         <v>43770</v>
       </c>
-      <c r="B180" s="4">
+      <c r="B180" s="7">
         <v>43799</v>
       </c>
-      <c r="C180" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D180" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E180" s="9">
+      <c r="C180" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D180" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E180" s="10">
         <v>50.2</v>
       </c>
-      <c r="F180" s="9">
+      <c r="F180" s="10">
         <v>49.5</v>
       </c>
-      <c r="G180" s="9">
+      <c r="G180" s="10">
         <v>49.3</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A181" s="4">
+      <c r="A181" s="7">
         <v>43800</v>
       </c>
-      <c r="B181" s="4">
+      <c r="B181" s="7">
         <v>43830</v>
       </c>
-      <c r="C181" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D181" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E181" s="9">
+      <c r="C181" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D181" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E181" s="10">
         <v>50.2</v>
       </c>
-      <c r="F181" s="9">
+      <c r="F181" s="10">
         <v>50.1</v>
       </c>
-      <c r="G181" s="9">
+      <c r="G181" s="10">
         <v>50.2</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A182" s="4">
+      <c r="A182" s="7">
         <v>43831</v>
       </c>
-      <c r="B182" s="4">
+      <c r="B182" s="7">
         <v>43861</v>
       </c>
-      <c r="C182" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D182" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E182" s="9">
+      <c r="C182" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D182" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E182" s="10">
         <v>50</v>
       </c>
-      <c r="F182" s="9">
+      <c r="F182" s="10">
         <v>50</v>
       </c>
-      <c r="G182" s="9">
+      <c r="G182" s="10">
         <v>50.2</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A183" s="4">
+      <c r="A183" s="7">
         <v>43862</v>
       </c>
-      <c r="B183" s="4">
+      <c r="B183" s="7">
         <v>43890</v>
       </c>
-      <c r="C183" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D183" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E183" s="9">
+      <c r="C183" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D183" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E183" s="10">
         <v>35.700000000000003</v>
       </c>
-      <c r="F183" s="9">
+      <c r="F183" s="10">
         <v>46</v>
       </c>
-      <c r="G183" s="9">
+      <c r="G183" s="10">
         <v>50</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A184" s="4">
+      <c r="A184" s="7">
         <v>43891</v>
       </c>
-      <c r="B184" s="4">
+      <c r="B184" s="7">
         <v>43921</v>
       </c>
-      <c r="C184" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D184" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E184" s="9">
+      <c r="C184" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D184" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E184" s="10">
         <v>52</v>
       </c>
-      <c r="F184" s="9">
+      <c r="F184" s="10">
         <v>45</v>
       </c>
-      <c r="G184" s="9">
+      <c r="G184" s="10">
         <v>35.700000000000003</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A185" s="4">
+      <c r="A185" s="7">
         <v>43922</v>
       </c>
-      <c r="B185" s="4">
+      <c r="B185" s="7">
         <v>43951</v>
       </c>
-      <c r="C185" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D185" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E185" s="9">
+      <c r="C185" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D185" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E185" s="10">
         <v>50.8</v>
       </c>
-      <c r="F185" s="9">
+      <c r="F185" s="10">
         <v>51</v>
       </c>
-      <c r="G185" s="9">
+      <c r="G185" s="10">
         <v>52</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A186" s="4">
+      <c r="A186" s="7">
         <v>43952</v>
       </c>
-      <c r="B186" s="4">
+      <c r="B186" s="7">
         <v>43982</v>
       </c>
-      <c r="C186" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D186" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E186" s="9">
+      <c r="C186" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D186" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E186" s="10">
         <v>50.6</v>
       </c>
-      <c r="F186" s="9">
+      <c r="F186" s="10">
         <v>51</v>
       </c>
-      <c r="G186" s="9">
+      <c r="G186" s="10">
         <v>50.8</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A187" s="4">
+      <c r="A187" s="7">
         <v>43983</v>
       </c>
-      <c r="B187" s="4">
+      <c r="B187" s="7">
         <v>44012</v>
       </c>
-      <c r="C187" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D187" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E187" s="9">
+      <c r="C187" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D187" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E187" s="10">
         <v>50.9</v>
       </c>
-      <c r="F187" s="9">
+      <c r="F187" s="10">
         <v>50.4</v>
       </c>
-      <c r="G187" s="9">
+      <c r="G187" s="10">
         <v>50.6</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A188" s="4">
+      <c r="A188" s="7">
         <v>44013</v>
       </c>
-      <c r="B188" s="4">
+      <c r="B188" s="7">
         <v>44043</v>
       </c>
-      <c r="C188" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D188" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E188" s="9">
+      <c r="C188" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D188" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E188" s="10">
         <v>51.1</v>
       </c>
-      <c r="F188" s="9">
+      <c r="F188" s="10">
         <v>50.7</v>
       </c>
-      <c r="G188" s="9">
+      <c r="G188" s="10">
         <v>50.9</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A189" s="4">
+      <c r="A189" s="7">
         <v>44044</v>
       </c>
-      <c r="B189" s="4">
+      <c r="B189" s="7">
         <v>44074</v>
       </c>
-      <c r="C189" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D189" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E189" s="9">
+      <c r="C189" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D189" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E189" s="10">
         <v>51</v>
       </c>
-      <c r="F189" s="9">
+      <c r="F189" s="10">
         <v>51.2</v>
       </c>
-      <c r="G189" s="9">
+      <c r="G189" s="10">
         <v>51.1</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A190" s="4">
+      <c r="A190" s="7">
         <v>44075</v>
       </c>
-      <c r="B190" s="4">
+      <c r="B190" s="7">
         <v>44104</v>
       </c>
-      <c r="C190" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D190" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E190" s="9">
+      <c r="C190" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D190" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E190" s="10">
         <v>51.5</v>
       </c>
-      <c r="F190" s="9">
+      <c r="F190" s="10">
         <v>51.2</v>
       </c>
-      <c r="G190" s="9">
+      <c r="G190" s="10">
         <v>51</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A191" s="4">
+      <c r="A191" s="7">
         <v>44105</v>
       </c>
-      <c r="B191" s="4">
+      <c r="B191" s="7">
         <v>44135</v>
       </c>
-      <c r="C191" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D191" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E191" s="9">
+      <c r="C191" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D191" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E191" s="10">
         <v>51.4</v>
       </c>
-      <c r="F191" s="9">
+      <c r="F191" s="10">
         <v>51.3</v>
       </c>
-      <c r="G191" s="9">
+      <c r="G191" s="10">
         <v>51.5</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A192" s="4">
+      <c r="A192" s="7">
         <v>44136</v>
       </c>
-      <c r="B192" s="4">
+      <c r="B192" s="7">
         <v>44165</v>
       </c>
-      <c r="C192" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D192" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E192" s="9">
+      <c r="C192" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D192" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E192" s="10">
         <v>52.1</v>
       </c>
-      <c r="F192" s="9">
+      <c r="F192" s="10">
         <v>51.5</v>
       </c>
-      <c r="G192" s="9">
+      <c r="G192" s="10">
         <v>51.4</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A193" s="4">
+      <c r="A193" s="7">
         <v>44166</v>
       </c>
-      <c r="B193" s="4">
+      <c r="B193" s="7">
         <v>44196</v>
       </c>
-      <c r="C193" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D193" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E193" s="9">
+      <c r="C193" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D193" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E193" s="10">
         <v>51.9</v>
       </c>
-      <c r="F193" s="9">
+      <c r="F193" s="10">
         <v>52</v>
       </c>
-      <c r="G193" s="9">
+      <c r="G193" s="10">
         <v>52.1</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A194" s="4">
+      <c r="A194" s="7">
         <v>44197</v>
       </c>
-      <c r="B194" s="4">
+      <c r="B194" s="7">
         <v>44227</v>
       </c>
-      <c r="C194" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D194" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E194" s="9">
+      <c r="C194" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D194" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E194" s="10">
         <v>51.3</v>
       </c>
-      <c r="F194" s="9">
+      <c r="F194" s="10">
         <v>51.6</v>
       </c>
-      <c r="G194" s="9">
+      <c r="G194" s="10">
         <v>51.9</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A195" s="4">
+      <c r="A195" s="7">
         <v>44228</v>
       </c>
-      <c r="B195" s="4">
+      <c r="B195" s="7">
         <v>44255</v>
       </c>
-      <c r="C195" s="7">
+      <c r="C195" s="8">
         <v>0.625</v>
       </c>
-      <c r="D195" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E195" s="9">
+      <c r="D195" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E195" s="10">
         <v>50.6</v>
       </c>
-      <c r="F195" s="9">
+      <c r="F195" s="10">
         <v>51.1</v>
       </c>
-      <c r="G195" s="9">
+      <c r="G195" s="10">
         <v>51.3</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A196" s="4">
+      <c r="A196" s="7">
         <v>44256</v>
       </c>
-      <c r="B196" s="4">
+      <c r="B196" s="7">
         <v>44286</v>
       </c>
-      <c r="C196" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D196" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E196" s="9">
+      <c r="C196" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D196" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E196" s="10">
         <v>51.9</v>
       </c>
-      <c r="F196" s="9">
+      <c r="F196" s="10">
         <v>51</v>
       </c>
-      <c r="G196" s="9">
+      <c r="G196" s="10">
         <v>50.6</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A197" s="4">
+      <c r="A197" s="7">
         <v>44287</v>
       </c>
-      <c r="B197" s="4">
+      <c r="B197" s="7">
         <v>44316</v>
       </c>
-      <c r="C197" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D197" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E197" s="9">
+      <c r="C197" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D197" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E197" s="10">
         <v>51.1</v>
       </c>
-      <c r="F197" s="9">
+      <c r="F197" s="10">
         <v>51.7</v>
       </c>
-      <c r="G197" s="9">
+      <c r="G197" s="10">
         <v>51.9</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A198" s="4">
+      <c r="A198" s="7">
         <v>44317</v>
       </c>
-      <c r="B198" s="4">
+      <c r="B198" s="7">
         <v>44347</v>
       </c>
-      <c r="C198" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D198" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E198" s="9">
+      <c r="C198" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D198" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E198" s="10">
         <v>51</v>
       </c>
-      <c r="F198" s="9">
+      <c r="F198" s="10">
         <v>51.1</v>
       </c>
-      <c r="G198" s="9">
+      <c r="G198" s="10">
         <v>51.1</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A199" s="4">
+      <c r="A199" s="7">
         <v>44348</v>
       </c>
-      <c r="B199" s="4">
+      <c r="B199" s="7">
         <v>44377</v>
       </c>
-      <c r="C199" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D199" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E199" s="9">
+      <c r="C199" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D199" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E199" s="10">
         <v>50.9</v>
       </c>
-      <c r="F199" s="9">
+      <c r="F199" s="10">
         <v>50.8</v>
       </c>
-      <c r="G199" s="9">
+      <c r="G199" s="10">
         <v>51</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A200" s="4">
+      <c r="A200" s="7">
         <v>44378</v>
       </c>
-      <c r="B200" s="4">
+      <c r="B200" s="7">
         <v>44408</v>
       </c>
-      <c r="C200" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D200" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E200" s="9">
+      <c r="C200" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D200" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E200" s="10">
         <v>50.4</v>
       </c>
-      <c r="F200" s="9">
+      <c r="F200" s="10">
         <v>50.8</v>
       </c>
-      <c r="G200" s="9">
+      <c r="G200" s="10">
         <v>50.9</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A201" s="4">
+      <c r="A201" s="7">
         <v>44409</v>
       </c>
-      <c r="B201" s="4">
+      <c r="B201" s="7">
         <v>44439</v>
       </c>
-      <c r="C201" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D201" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E201" s="9">
+      <c r="C201" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D201" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E201" s="10">
         <v>50.1</v>
       </c>
-      <c r="F201" s="9">
+      <c r="F201" s="10">
         <v>50.2</v>
       </c>
-      <c r="G201" s="9">
+      <c r="G201" s="10">
         <v>50.4</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A202" s="4">
+      <c r="A202" s="7">
         <v>44440</v>
       </c>
-      <c r="B202" s="4">
+      <c r="B202" s="7">
         <v>44469</v>
       </c>
-      <c r="C202" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D202" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E202" s="9">
+      <c r="C202" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D202" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E202" s="10">
         <v>49.6</v>
       </c>
-      <c r="F202" s="9">
+      <c r="F202" s="10">
         <v>50.1</v>
       </c>
-      <c r="G202" s="9">
+      <c r="G202" s="10">
         <v>50.1</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A203" s="4">
+      <c r="A203" s="7">
         <v>44470</v>
       </c>
-      <c r="B203" s="4">
+      <c r="B203" s="7">
         <v>44500</v>
       </c>
-      <c r="C203" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D203" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E203" s="9">
+      <c r="C203" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D203" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E203" s="10">
         <v>49.2</v>
       </c>
-      <c r="F203" s="9">
+      <c r="F203" s="10">
         <v>49.7</v>
       </c>
-      <c r="G203" s="9">
+      <c r="G203" s="10">
         <v>49.6</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A204" s="4">
+      <c r="A204" s="7">
         <v>44501</v>
       </c>
-      <c r="B204" s="4">
+      <c r="B204" s="7">
         <v>44530</v>
       </c>
-      <c r="C204" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D204" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E204" s="9">
+      <c r="C204" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D204" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E204" s="10">
         <v>50.1</v>
       </c>
-      <c r="F204" s="9">
+      <c r="F204" s="10">
         <v>49.6</v>
       </c>
-      <c r="G204" s="9">
+      <c r="G204" s="10">
         <v>49.2</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A205" s="4">
+      <c r="A205" s="7">
         <v>44531</v>
       </c>
-      <c r="B205" s="4">
+      <c r="B205" s="7">
         <v>44561</v>
       </c>
-      <c r="C205" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D205" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E205" s="9">
+      <c r="C205" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D205" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E205" s="10">
         <v>50.3</v>
       </c>
-      <c r="F205" s="9">
+      <c r="F205" s="10">
         <v>50</v>
       </c>
-      <c r="G205" s="9">
+      <c r="G205" s="10">
         <v>50.1</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A206" s="4">
+      <c r="A206" s="7">
         <v>44562</v>
       </c>
-      <c r="B206" s="4">
+      <c r="B206" s="7">
         <v>44591</v>
       </c>
-      <c r="C206" s="7">
+      <c r="C206" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D206" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E206" s="9">
+      <c r="D206" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E206" s="10">
         <v>50.1</v>
       </c>
-      <c r="F206" s="9">
+      <c r="F206" s="10">
         <v>50</v>
       </c>
-      <c r="G206" s="9">
+      <c r="G206" s="10">
         <v>50.3</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A207" s="4">
+      <c r="A207" s="7">
         <v>44593</v>
       </c>
-      <c r="B207" s="4">
+      <c r="B207" s="7">
         <v>44621</v>
       </c>
-      <c r="C207" s="7">
+      <c r="C207" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D207" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E207" s="9">
+      <c r="D207" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E207" s="10">
         <v>50.2</v>
       </c>
-      <c r="F207" s="9">
+      <c r="F207" s="10">
         <v>49.9</v>
       </c>
-      <c r="G207" s="9">
+      <c r="G207" s="10">
         <v>50.1</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A208" s="4">
+      <c r="A208" s="7">
         <v>44621</v>
       </c>
-      <c r="B208" s="4">
+      <c r="B208" s="7">
         <v>44651</v>
       </c>
-      <c r="C208" s="7">
+      <c r="C208" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D208" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E208" s="9">
+      <c r="D208" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E208" s="10">
         <v>49.5</v>
       </c>
-      <c r="F208" s="9">
+      <c r="F208" s="10">
         <v>49.9</v>
       </c>
-      <c r="G208" s="9">
+      <c r="G208" s="10">
         <v>50.2</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A209" s="4">
+      <c r="A209" s="7">
         <v>44652</v>
       </c>
-      <c r="B209" s="4">
+      <c r="B209" s="7">
         <v>44681</v>
       </c>
-      <c r="C209" s="7">
+      <c r="C209" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D209" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E209" s="9">
+      <c r="D209" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E209" s="10">
         <v>47.4</v>
       </c>
-      <c r="F209" s="9">
+      <c r="F209" s="10">
         <v>48</v>
       </c>
-      <c r="G209" s="9">
+      <c r="G209" s="10">
         <v>49.5</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A210" s="4">
+      <c r="A210" s="7">
         <v>44682</v>
       </c>
-      <c r="B210" s="4">
+      <c r="B210" s="7">
         <v>44712</v>
       </c>
-      <c r="C210" s="7">
+      <c r="C210" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D210" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E210" s="9">
+      <c r="D210" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E210" s="10">
         <v>49.6</v>
       </c>
-      <c r="F210" s="9">
+      <c r="F210" s="10">
         <v>48</v>
       </c>
-      <c r="G210" s="9">
+      <c r="G210" s="10">
         <v>47.4</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A211" s="4">
+      <c r="A211" s="7">
         <v>44713</v>
       </c>
-      <c r="B211" s="4">
+      <c r="B211" s="7">
         <v>44742</v>
       </c>
-      <c r="C211" s="7">
+      <c r="C211" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D211" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E211" s="9">
+      <c r="D211" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E211" s="10">
         <v>50.2</v>
       </c>
-      <c r="F211" s="9">
+      <c r="F211" s="10">
         <v>50.5</v>
       </c>
-      <c r="G211" s="9">
+      <c r="G211" s="10">
         <v>49.6</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A212" s="4">
+      <c r="A212" s="7">
         <v>44743</v>
       </c>
-      <c r="B212" s="4">
+      <c r="B212" s="7">
         <v>44773</v>
       </c>
-      <c r="C212" s="7">
+      <c r="C212" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D212" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E212" s="9">
+      <c r="D212" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E212" s="10">
         <v>49</v>
       </c>
-      <c r="F212" s="9">
+      <c r="F212" s="10">
         <v>50.4</v>
       </c>
-      <c r="G212" s="9">
+      <c r="G212" s="10">
         <v>50.2</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A213" s="4">
+      <c r="A213" s="7">
         <v>44774</v>
       </c>
-      <c r="B213" s="4">
+      <c r="B213" s="7">
         <v>44804</v>
       </c>
-      <c r="C213" s="7">
+      <c r="C213" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D213" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E213" s="9">
+      <c r="D213" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E213" s="10">
         <v>49.4</v>
       </c>
-      <c r="F213" s="9">
+      <c r="F213" s="10">
         <v>49.2</v>
       </c>
-      <c r="G213" s="9">
+      <c r="G213" s="10">
         <v>49</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A214" s="4">
+      <c r="A214" s="7">
         <v>44805</v>
       </c>
-      <c r="B214" s="4">
+      <c r="B214" s="7">
         <v>44834</v>
       </c>
-      <c r="C214" s="7">
+      <c r="C214" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D214" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E214" s="9">
+      <c r="D214" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E214" s="10">
         <v>50.1</v>
       </c>
-      <c r="F214" s="9">
+      <c r="F214" s="10">
         <v>49.6</v>
       </c>
-      <c r="G214" s="9">
+      <c r="G214" s="10">
         <v>49.4</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A215" s="4">
+      <c r="A215" s="7">
         <v>44835</v>
       </c>
-      <c r="B215" s="4">
+      <c r="B215" s="7">
         <v>44865</v>
       </c>
-      <c r="C215" s="7">
+      <c r="C215" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D215" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E215" s="9">
+      <c r="D215" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E215" s="10">
         <v>49.2</v>
       </c>
-      <c r="F215" s="9">
+      <c r="F215" s="10">
         <v>50</v>
       </c>
-      <c r="G215" s="9">
+      <c r="G215" s="10">
         <v>50.1</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A216" s="4">
+      <c r="A216" s="7">
         <v>44866</v>
       </c>
-      <c r="B216" s="4">
+      <c r="B216" s="7">
         <v>44895</v>
       </c>
-      <c r="C216" s="7">
+      <c r="C216" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D216" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E216" s="9">
+      <c r="D216" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E216" s="10">
         <v>48</v>
       </c>
-      <c r="F216" s="9">
+      <c r="F216" s="10">
         <v>49</v>
       </c>
-      <c r="G216" s="9">
+      <c r="G216" s="10">
         <v>49.2</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A217" s="4">
+      <c r="A217" s="7">
         <v>44896</v>
       </c>
-      <c r="B217" s="4">
+      <c r="B217" s="7">
         <v>44926</v>
       </c>
-      <c r="C217" s="7">
+      <c r="C217" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D217" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E217" s="9">
+      <c r="D217" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E217" s="10">
         <v>47</v>
       </c>
-      <c r="F217" s="9">
+      <c r="F217" s="10">
         <v>48</v>
       </c>
-      <c r="G217" s="9">
+      <c r="G217" s="10">
         <v>48</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A218" s="4">
+      <c r="A218" s="7">
         <v>44927</v>
       </c>
-      <c r="B218" s="4">
+      <c r="B218" s="7">
         <v>44957</v>
       </c>
-      <c r="C218" s="7">
+      <c r="C218" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D218" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E218" s="9">
+      <c r="D218" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E218" s="10">
         <v>50.1</v>
       </c>
-      <c r="F218" s="9">
+      <c r="F218" s="10">
         <v>49.8</v>
       </c>
-      <c r="G218" s="9">
+      <c r="G218" s="10">
         <v>47</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A219" s="4">
+      <c r="A219" s="7">
         <v>44958</v>
       </c>
-      <c r="B219" s="4">
+      <c r="B219" s="7">
         <v>44986</v>
       </c>
-      <c r="C219" s="7">
+      <c r="C219" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D219" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E219" s="9">
+      <c r="D219" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E219" s="10">
         <v>52.6</v>
       </c>
-      <c r="F219" s="9">
+      <c r="F219" s="10">
         <v>50.5</v>
       </c>
-      <c r="G219" s="9">
+      <c r="G219" s="10">
         <v>50.1</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A220" s="4">
+      <c r="A220" s="7">
         <v>44986</v>
       </c>
-      <c r="B220" s="4">
+      <c r="B220" s="7">
         <v>45016</v>
       </c>
-      <c r="C220" s="7">
+      <c r="C220" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D220" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E220" s="9">
+      <c r="D220" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E220" s="10">
         <v>51.9</v>
       </c>
-      <c r="F220" s="9">
+      <c r="F220" s="10">
         <v>51.5</v>
       </c>
-      <c r="G220" s="9">
+      <c r="G220" s="10">
         <v>52.6</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A221" s="4">
+      <c r="A221" s="7">
         <v>45017</v>
       </c>
-      <c r="B221" s="4">
+      <c r="B221" s="7">
         <v>45046</v>
       </c>
-      <c r="C221" s="7">
+      <c r="C221" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D221" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E221" s="9">
+      <c r="D221" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E221" s="10">
         <v>49.2</v>
       </c>
-      <c r="F221" s="9">
+      <c r="F221" s="10">
         <v>51.4</v>
       </c>
-      <c r="G221" s="9">
+      <c r="G221" s="10">
         <v>51.9</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A222" s="4">
+      <c r="A222" s="7">
         <v>45047</v>
       </c>
-      <c r="B222" s="4">
+      <c r="B222" s="7">
         <v>45077</v>
       </c>
-      <c r="C222" s="7">
+      <c r="C222" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D222" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E222" s="9">
+      <c r="D222" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E222" s="10">
         <v>48.8</v>
       </c>
-      <c r="F222" s="9">
+      <c r="F222" s="10">
         <v>51.4</v>
       </c>
-      <c r="G222" s="9">
+      <c r="G222" s="10">
         <v>49.2</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A223" s="4">
+      <c r="A223" s="7">
         <v>45078</v>
       </c>
-      <c r="B223" s="4">
+      <c r="B223" s="7">
         <v>45107</v>
       </c>
-      <c r="C223" s="7">
+      <c r="C223" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D223" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E223" s="9">
+      <c r="D223" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E223" s="10">
         <v>49</v>
       </c>
-      <c r="F223" s="9">
+      <c r="F223" s="10">
         <v>49</v>
       </c>
-      <c r="G223" s="9">
+      <c r="G223" s="10">
         <v>48.8</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A224" s="4">
+      <c r="A224" s="7">
         <v>45108</v>
       </c>
-      <c r="B224" s="4">
+      <c r="B224" s="7">
         <v>45138</v>
       </c>
-      <c r="C224" s="7">
+      <c r="C224" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D224" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E224" s="9">
+      <c r="D224" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E224" s="10">
         <v>49.3</v>
       </c>
-      <c r="F224" s="9">
+      <c r="F224" s="10">
         <v>49.2</v>
       </c>
-      <c r="G224" s="9">
+      <c r="G224" s="10">
         <v>49</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A225" s="4">
+      <c r="A225" s="7">
         <v>45139</v>
       </c>
-      <c r="B225" s="4">
+      <c r="B225" s="7">
         <v>45169</v>
       </c>
-      <c r="C225" s="7">
+      <c r="C225" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D225" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E225" s="9">
+      <c r="D225" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E225" s="10">
         <v>49.7</v>
       </c>
-      <c r="F225" s="9">
+      <c r="F225" s="10">
         <v>49.4</v>
       </c>
-      <c r="G225" s="9">
+      <c r="G225" s="10">
         <v>49.3</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A226" s="4">
+      <c r="A226" s="7">
         <v>45170</v>
       </c>
-      <c r="B226" s="4">
+      <c r="B226" s="7">
         <v>45199</v>
       </c>
-      <c r="C226" s="7">
+      <c r="C226" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D226" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E226" s="9">
+      <c r="D226" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E226" s="10">
         <v>50.2</v>
       </c>
-      <c r="F226" s="9">
+      <c r="F226" s="10">
         <v>50.2</v>
       </c>
-      <c r="G226" s="9">
+      <c r="G226" s="10">
         <v>49.7</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A227" s="4">
+      <c r="A227" s="7">
         <v>45200</v>
       </c>
-      <c r="B227" s="4">
+      <c r="B227" s="7">
         <v>45230</v>
       </c>
-      <c r="C227" s="7">
+      <c r="C227" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D227" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E227" s="9">
+      <c r="D227" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E227" s="10">
         <v>49.5</v>
       </c>
-      <c r="F227" s="9">
+      <c r="F227" s="10">
         <v>50.2</v>
       </c>
-      <c r="G227" s="9">
+      <c r="G227" s="10">
         <v>50.2</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A228" s="4">
+      <c r="A228" s="7">
         <v>45231</v>
       </c>
-      <c r="B228" s="4">
+      <c r="B228" s="7">
         <v>45260</v>
       </c>
-      <c r="C228" s="7">
+      <c r="C228" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D228" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E228" s="9">
+      <c r="D228" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E228" s="10">
         <v>49.4</v>
       </c>
-      <c r="F228" s="9">
+      <c r="F228" s="10">
         <v>49.7</v>
       </c>
-      <c r="G228" s="9">
+      <c r="G228" s="10">
         <v>49.5</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A229" s="4">
+      <c r="A229" s="7">
         <v>45261</v>
       </c>
-      <c r="B229" s="4">
+      <c r="B229" s="7">
         <v>45291</v>
       </c>
-      <c r="C229" s="7">
+      <c r="C229" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D229" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E229" s="9">
+      <c r="D229" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E229" s="10">
         <v>49</v>
       </c>
-      <c r="F229" s="9">
+      <c r="F229" s="10">
         <v>49.5</v>
       </c>
-      <c r="G229" s="9">
+      <c r="G229" s="10">
         <v>49.4</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A230" s="4">
+      <c r="A230" s="7">
         <v>45292</v>
       </c>
-      <c r="B230" s="4">
+      <c r="B230" s="7">
         <v>45322</v>
       </c>
-      <c r="C230" s="7">
+      <c r="C230" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D230" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E230" s="9">
+      <c r="D230" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E230" s="10">
         <v>49.2</v>
       </c>
-      <c r="F230" s="9">
+      <c r="F230" s="10">
         <v>49.2</v>
       </c>
-      <c r="G230" s="9">
+      <c r="G230" s="10">
         <v>49</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A231" s="4">
+      <c r="A231" s="7">
         <v>45323</v>
       </c>
-      <c r="B231" s="4">
+      <c r="B231" s="7">
         <v>45352</v>
       </c>
-      <c r="C231" s="7">
+      <c r="C231" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D231" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E231" s="9">
+      <c r="D231" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E231" s="10">
         <v>49.1</v>
       </c>
-      <c r="F231" s="9">
+      <c r="F231" s="10">
         <v>49.1</v>
       </c>
-      <c r="G231" s="9">
+      <c r="G231" s="10">
         <v>49.2</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A232" s="4">
+      <c r="A232" s="7">
         <v>45352</v>
       </c>
-      <c r="B232" s="4">
+      <c r="B232" s="7">
         <v>45382</v>
       </c>
-      <c r="C232" s="7">
+      <c r="C232" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D232" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E232" s="9">
+      <c r="D232" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E232" s="10">
         <v>50.8</v>
       </c>
-      <c r="F232" s="9">
+      <c r="F232" s="10">
         <v>50.1</v>
       </c>
-      <c r="G232" s="9">
+      <c r="G232" s="10">
         <v>49.1</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A233" s="4">
+      <c r="A233" s="7">
         <v>45383</v>
       </c>
-      <c r="B233" s="4">
+      <c r="B233" s="7">
         <v>45412</v>
       </c>
-      <c r="C233" s="7">
+      <c r="C233" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D233" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E233" s="9">
+      <c r="D233" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E233" s="10">
         <v>50.4</v>
       </c>
-      <c r="F233" s="9">
+      <c r="F233" s="10">
         <v>50.3</v>
       </c>
-      <c r="G233" s="9">
+      <c r="G233" s="10">
         <v>50.8</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A234" s="4">
+      <c r="A234" s="7">
         <v>45413</v>
       </c>
-      <c r="B234" s="4">
+      <c r="B234" s="7">
         <v>45443</v>
       </c>
-      <c r="C234" s="7">
+      <c r="C234" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D234" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E234" s="9">
+      <c r="D234" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E234" s="10">
         <v>49.5</v>
       </c>
-      <c r="F234" s="9">
+      <c r="F234" s="10">
         <v>50.5</v>
       </c>
-      <c r="G234" s="9">
+      <c r="G234" s="10">
         <v>50.4</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A235" s="4">
+      <c r="A235" s="7">
         <v>45444</v>
       </c>
-      <c r="B235" s="4">
+      <c r="B235" s="7">
         <v>45473</v>
       </c>
-      <c r="C235" s="7">
+      <c r="C235" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D235" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E235" s="9">
+      <c r="D235" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E235" s="10">
         <v>49.5</v>
       </c>
-      <c r="F235" s="9">
+      <c r="F235" s="10">
         <v>49.5</v>
       </c>
-      <c r="G235" s="9">
+      <c r="G235" s="10">
         <v>49.5</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A236" s="4">
+      <c r="A236" s="7">
         <v>45474</v>
       </c>
-      <c r="B236" s="4">
+      <c r="B236" s="7">
         <v>45504</v>
       </c>
-      <c r="C236" s="7">
+      <c r="C236" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D236" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E236" s="9">
+      <c r="D236" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E236" s="10">
         <v>49.4</v>
       </c>
-      <c r="F236" s="9">
+      <c r="F236" s="10">
         <v>49.4</v>
       </c>
-      <c r="G236" s="9">
+      <c r="G236" s="10">
         <v>49.5</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A237" s="4">
+      <c r="A237" s="7">
         <v>45505</v>
       </c>
-      <c r="B237" s="4">
+      <c r="B237" s="7">
         <v>45535</v>
       </c>
-      <c r="C237" s="7">
+      <c r="C237" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D237" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E237" s="9">
+      <c r="D237" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E237" s="10">
         <v>49.1</v>
       </c>
-      <c r="F237" s="9">
+      <c r="F237" s="10">
         <v>49.5</v>
       </c>
-      <c r="G237" s="9">
+      <c r="G237" s="10">
         <v>49.4</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A238" s="4">
+      <c r="A238" s="7">
         <v>45536</v>
       </c>
-      <c r="B238" s="4">
+      <c r="B238" s="7">
         <v>45565</v>
       </c>
-      <c r="C238" s="7">
+      <c r="C238" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D238" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E238" s="9">
+      <c r="D238" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E238" s="10">
         <v>49.8</v>
       </c>
-      <c r="F238" s="9">
+      <c r="F238" s="10">
         <v>49.4</v>
       </c>
-      <c r="G238" s="9">
+      <c r="G238" s="10">
         <v>49.1</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A239" s="4">
+      <c r="A239" s="7">
         <v>45566</v>
       </c>
-      <c r="B239" s="4">
+      <c r="B239" s="7">
         <v>45596</v>
       </c>
-      <c r="C239" s="7">
+      <c r="C239" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D239" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E239" s="9">
+      <c r="D239" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E239" s="10">
         <v>50.1</v>
       </c>
-      <c r="F239" s="9">
+      <c r="F239" s="10">
         <v>49.8</v>
       </c>
-      <c r="G239" s="9">
+      <c r="G239" s="10">
         <v>49.8</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A240" s="4">
+      <c r="A240" s="7">
         <v>45597</v>
       </c>
-      <c r="B240" s="4">
+      <c r="B240" s="7">
         <v>45626</v>
       </c>
-      <c r="C240" s="7">
+      <c r="C240" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D240" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E240" s="9">
+      <c r="D240" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E240" s="10">
         <v>50.3</v>
       </c>
-      <c r="F240" s="9">
+      <c r="F240" s="10">
         <v>50.2</v>
       </c>
-      <c r="G240" s="9">
+      <c r="G240" s="10">
         <v>50.1</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A241" s="4">
+      <c r="A241" s="7">
         <v>45627</v>
       </c>
-      <c r="B241" s="4">
+      <c r="B241" s="7">
         <v>45657</v>
       </c>
-      <c r="C241" s="7">
+      <c r="C241" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D241" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E241" s="9">
+      <c r="D241" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E241" s="10">
         <v>50.1</v>
       </c>
-      <c r="F241" s="9">
+      <c r="F241" s="10">
         <v>50.3</v>
       </c>
-      <c r="G241" s="9">
+      <c r="G241" s="10">
         <v>50.3</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A242" s="4">
+      <c r="A242" s="7">
         <v>45658</v>
       </c>
-      <c r="B242" s="4">
+      <c r="B242" s="7">
         <v>45684</v>
       </c>
-      <c r="C242" s="7">
+      <c r="C242" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D242" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E242" s="9">
+      <c r="D242" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E242" s="10">
         <v>49.1</v>
       </c>
-      <c r="F242" s="9">
+      <c r="F242" s="10">
         <v>50.1</v>
       </c>
-      <c r="G242" s="9">
+      <c r="G242" s="10">
         <v>50.1</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A243" s="4">
+      <c r="A243" s="7">
         <v>45689</v>
       </c>
-      <c r="B243" s="4">
+      <c r="B243" s="7">
         <v>45717</v>
       </c>
-      <c r="C243" s="7">
+      <c r="C243" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D243" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E243" s="9">
+      <c r="D243" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E243" s="10">
         <v>50.2</v>
       </c>
-      <c r="F243" s="9">
+      <c r="F243" s="10">
         <v>50</v>
       </c>
-      <c r="G243" s="9">
+      <c r="G243" s="10">
         <v>49.1</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A244" s="4">
+      <c r="A244" s="7">
         <v>45717</v>
       </c>
-      <c r="B244" s="4">
+      <c r="B244" s="7">
         <v>45747</v>
       </c>
-      <c r="C244" s="7">
+      <c r="C244" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D244" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E244" s="9">
+      <c r="D244" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E244" s="10">
         <v>50.5</v>
       </c>
-      <c r="F244" s="9">
+      <c r="F244" s="10">
         <v>50.4</v>
       </c>
-      <c r="G244" s="9">
+      <c r="G244" s="10">
         <v>50.2</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A245" s="4">
+      <c r="A245" s="7">
         <v>45748</v>
       </c>
-      <c r="B245" s="4">
+      <c r="B245" s="7">
         <v>45777</v>
       </c>
-      <c r="C245" s="7">
+      <c r="C245" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D245" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E245" s="9">
+      <c r="D245" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E245" s="10">
         <v>49</v>
       </c>
-      <c r="F245" s="9">
+      <c r="F245" s="10">
         <v>49.7</v>
       </c>
-      <c r="G245" s="9">
+      <c r="G245" s="10">
         <v>50.5</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A246" s="4">
+      <c r="A246" s="7">
         <v>45778</v>
       </c>
-      <c r="B246" s="4">
+      <c r="B246" s="7">
         <v>45808</v>
       </c>
-      <c r="C246" s="7">
+      <c r="C246" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D246" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E246" s="9">
+      <c r="D246" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E246" s="10">
         <v>49.5</v>
       </c>
-      <c r="F246" s="9">
+      <c r="F246" s="10">
         <v>49.5</v>
       </c>
-      <c r="G246" s="9">
+      <c r="G246" s="10">
         <v>49</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A247" s="4">
+      <c r="A247" s="7">
         <v>45809</v>
       </c>
-      <c r="B247" s="4">
+      <c r="B247" s="7">
         <v>45838</v>
       </c>
-      <c r="C247" s="7">
+      <c r="C247" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D247" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E247" s="9">
+      <c r="D247" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E247" s="10">
         <v>49.7</v>
       </c>
-      <c r="F247" s="9">
+      <c r="F247" s="10">
         <v>49.6</v>
       </c>
-      <c r="G247" s="9">
+      <c r="G247" s="10">
         <v>49.5</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A248" s="4">
+      <c r="A248" s="7">
         <v>45839</v>
       </c>
-      <c r="B248" s="4">
+      <c r="B248" s="7">
         <v>45869</v>
       </c>
-      <c r="C248" s="7">
+      <c r="C248" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D248" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E248" s="9">
+      <c r="D248" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E248" s="10">
         <v>49.3</v>
       </c>
-      <c r="F248" s="9">
+      <c r="F248" s="10">
         <v>49.7</v>
       </c>
-      <c r="G248" s="9">
+      <c r="G248" s="10">
         <v>49.7</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A249" s="4">
+      <c r="A249" s="7">
         <v>45870</v>
       </c>
-      <c r="B249" s="4">
+      <c r="B249" s="7">
         <v>45900</v>
       </c>
-      <c r="C249" s="7">
+      <c r="C249" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D249" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E249" s="9">
+      <c r="D249" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E249" s="10">
         <v>49.4</v>
       </c>
-      <c r="F249" s="9">
+      <c r="F249" s="10">
         <v>49.5</v>
       </c>
-      <c r="G249" s="9">
+      <c r="G249" s="10">
         <v>49.3</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A250" s="4">
+      <c r="A250" s="7">
         <v>45901</v>
       </c>
-      <c r="B250" s="4">
+      <c r="B250" s="7">
         <v>45930</v>
       </c>
-      <c r="C250" s="7">
+      <c r="C250" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D250" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E250" s="9">
+      <c r="D250" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E250" s="10">
         <v>49.8</v>
       </c>
-      <c r="F250" s="9">
+      <c r="F250" s="10">
         <v>49.6</v>
       </c>
-      <c r="G250" s="9">
+      <c r="G250" s="10">
         <v>49.4</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A251" s="4">
+      <c r="A251" s="7">
         <v>45931</v>
       </c>
-      <c r="B251" s="4">
+      <c r="B251" s="7">
         <v>45961</v>
       </c>
-      <c r="C251" s="7">
+      <c r="C251" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D251" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E251" s="9">
+      <c r="D251" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E251" s="10">
         <v>49</v>
       </c>
-      <c r="F251" s="9">
+      <c r="F251" s="10">
         <v>49.6</v>
       </c>
-      <c r="G251" s="9">
+      <c r="G251" s="10">
         <v>49.8</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A252" s="4">
+      <c r="A252" s="7">
         <v>45962</v>
       </c>
-      <c r="B252" s="4">
+      <c r="B252" s="7">
         <v>45991</v>
       </c>
-      <c r="C252" s="7">
+      <c r="C252" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D252" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E252" s="9">
+      <c r="D252" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E252" s="10">
         <v>49.2</v>
       </c>
-      <c r="F252" s="9">
+      <c r="F252" s="10">
         <v>49.2</v>
       </c>
-      <c r="G252" s="9">
+      <c r="G252" s="10">
         <v>49</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A253" s="4">
+      <c r="A253" s="7">
         <v>45992</v>
       </c>
-      <c r="B253" s="4">
+      <c r="B253" s="7">
         <v>46022</v>
       </c>
-      <c r="C253" s="7">
+      <c r="C253" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D253" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E253" s="9">
+      <c r="D253" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E253" s="10">
         <v>50.1</v>
       </c>
-      <c r="F253" s="9">
+      <c r="F253" s="10">
         <v>49.2</v>
       </c>
-      <c r="G253" s="9">
+      <c r="G253" s="10">
         <v>49.2</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A254" s="4">
+      <c r="A254" s="7">
         <v>46023</v>
       </c>
-      <c r="B254" s="4">
+      <c r="B254" s="7">
         <v>46053</v>
       </c>
-      <c r="C254" s="7">
+      <c r="C254" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D254" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E254" s="9">
+      <c r="D254" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E254" s="10">
         <v>49.3</v>
       </c>
-      <c r="F254" s="9">
+      <c r="F254" s="10">
         <v>50.1</v>
       </c>
-      <c r="G254" s="9">
+      <c r="G254" s="10">
         <v>50.1</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A255" s="4">
+      <c r="A255" s="7">
         <v>46054</v>
       </c>
-      <c r="B255" s="4">
+      <c r="B255" s="7">
         <v>46085</v>
       </c>
-      <c r="C255" s="7">
+      <c r="C255" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D255" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E255" s="9">
+      <c r="D255" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E255" s="10">
         <v>49</v>
       </c>
-      <c r="F255" s="9">
+      <c r="F255" s="10">
         <v>49.1</v>
       </c>
-      <c r="G255" s="9">
+      <c r="G255" s="10">
         <v>49.3</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A256" s="4">
+      <c r="A256" s="7">
         <v>46082</v>
       </c>
-      <c r="B256" s="4">
+      <c r="B256" s="7">
         <v>46112</v>
       </c>
-      <c r="C256" s="7">
+      <c r="C256" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D256" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E256" s="9">
+      <c r="D256" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E256" s="10">
         <v>50.4</v>
       </c>
-      <c r="F256" s="9">
+      <c r="F256" s="10">
         <v>50.1</v>
       </c>
-      <c r="G256" s="9">
+      <c r="G256" s="10">
         <v>49</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A257" s="4">
+      <c r="A257" s="7">
         <v>46113</v>
       </c>
-      <c r="B257" s="4">
+      <c r="B257" s="7">
         <v>46142</v>
       </c>
-      <c r="C257" s="7">
+      <c r="C257" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D257" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E257" s="9">
+      <c r="D257" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E257" s="10">
         <v>50.3</v>
       </c>
-      <c r="F257" s="9">
+      <c r="F257" s="10">
         <v>50.1</v>
       </c>
-      <c r="G257" s="9">
+      <c r="G257" s="10">
         <v>50.4</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A258" s="7">
+        <v>46143</v>
+      </c>
+      <c r="B258" s="7">
+        <v>46173</v>
+      </c>
+      <c r="C258" s="8">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="D258" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E258" s="10">
+        <v>50</v>
+      </c>
+      <c r="F258" s="10">
+        <v>50.2</v>
+      </c>
+      <c r="G258" s="10">
+        <v>50.3</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A259" s="7">
+        <v>46174</v>
+      </c>
+      <c r="B259" s="7">
+        <v>46203</v>
+      </c>
+      <c r="C259" s="8">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="D259" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F259" s="10">
+        <v>50.2</v>
+      </c>
+      <c r="G259" s="10">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -6449,17 +6492,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4443F9EE-BDA7-42C7-BB47-C54379F4610C}">
   <dimension ref="B2:C3"/>
-  <sheetFormatPr defaultRowHeight="19.2" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
         <v>9</v>
       </c>

--- a/data/macro/China/China PMI.xlsx
+++ b/data/macro/China/China PMI.xlsx
@@ -1,32 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data/macro/China/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\macro\China\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDA48D33-F23E-A04D-AB4B-20FAE145924F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA1F1A69-C7E2-495D-A7F8-71F64C3F863E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22160" yWindow="600" windowWidth="29040" windowHeight="15720" xr2:uid="{4C7AFA9F-A9F7-4D4A-8224-91102ADA8910}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{4C7AFA9F-A9F7-4D4A-8224-91102ADA8910}"/>
   </bookViews>
   <sheets>
     <sheet name="CPMINDX" sheetId="1" r:id="rId1"/>
-    <sheet name="info" sheetId="2" r:id="rId2"/>
+    <sheet name="CPMINMNS" sheetId="3" r:id="rId2"/>
+    <sheet name="info" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="14">
   <si>
     <t>Release Date</t>
   </si>
@@ -70,16 +80,21 @@
     <t>https://cn.investing.com/economic-calendar/chinese-manufacturing-pmi-594</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>https://kr.investing.com/economic-calendar/chinese-non-manufacturing-pmi-831</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="6">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
     <numFmt numFmtId="167" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -142,14 +157,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -178,11 +194,29 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="3">
-    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="4">
+    <cellStyle name="쉼표" xfId="3" builtinId="3"/>
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -515,17 +549,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8641136A-8358-754A-BFC1-48B8F9996351}">
   <dimension ref="A1:G259"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.33203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.6640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5" style="11"/>
-    <col min="5" max="7" width="11.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.296875" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.296875" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.59765625" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.8984375" style="10" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="11.5" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>6</v>
       </c>
@@ -548,7 +584,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="7">
         <v>38353</v>
       </c>
@@ -571,7 +607,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="7">
         <v>38384</v>
       </c>
@@ -594,7 +630,7 @@
         <v>54.7</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="7">
         <v>38412</v>
       </c>
@@ -617,7 +653,7 @@
         <v>54.5</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="7">
         <v>38443</v>
       </c>
@@ -640,7 +676,7 @@
         <v>57.9</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="7">
         <v>38473</v>
       </c>
@@ -663,7 +699,7 @@
         <v>56.7</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
         <v>38504</v>
       </c>
@@ -686,7 +722,7 @@
         <v>52.9</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="7">
         <v>38534</v>
       </c>
@@ -709,7 +745,7 @@
         <v>51.7</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="7">
         <v>38565</v>
       </c>
@@ -732,7 +768,7 @@
         <v>51.1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="7">
         <v>38596</v>
       </c>
@@ -755,7 +791,7 @@
         <v>52.6</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="7">
         <v>38626</v>
       </c>
@@ -778,7 +814,7 @@
         <v>55.1</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="7">
         <v>38657</v>
       </c>
@@ -801,7 +837,7 @@
         <v>54.1</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="7">
         <v>38687</v>
       </c>
@@ -824,7 +860,7 @@
         <v>54.1</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="7">
         <v>38718</v>
       </c>
@@ -847,7 +883,7 @@
         <v>54.3</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="7">
         <v>38749</v>
       </c>
@@ -870,7 +906,7 @@
         <v>52.1</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="7">
         <v>38777</v>
       </c>
@@ -893,7 +929,7 @@
         <v>52.1</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="7">
         <v>38808</v>
       </c>
@@ -916,7 +952,7 @@
         <v>55.3</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="7">
         <v>38838</v>
       </c>
@@ -939,7 +975,7 @@
         <v>58.1</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="7">
         <v>38869</v>
       </c>
@@ -962,7 +998,7 @@
         <v>54.8</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="7">
         <v>38899</v>
       </c>
@@ -985,7 +1021,7 @@
         <v>54.1</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="7">
         <v>38930</v>
       </c>
@@ -1008,7 +1044,7 @@
         <v>52.4</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="7">
         <v>38961</v>
       </c>
@@ -1031,7 +1067,7 @@
         <v>53.1</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="7">
         <v>38991</v>
       </c>
@@ -1054,7 +1090,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="7">
         <v>39022</v>
       </c>
@@ -1077,7 +1113,7 @@
         <v>54.7</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="7">
         <v>39052</v>
       </c>
@@ -1100,7 +1136,7 @@
         <v>55.3</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="7">
         <v>39083</v>
       </c>
@@ -1123,7 +1159,7 @@
         <v>54.8</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="7">
         <v>39114</v>
       </c>
@@ -1146,7 +1182,7 @@
         <v>55.1</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="7">
         <v>39142</v>
       </c>
@@ -1169,7 +1205,7 @@
         <v>53.1</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="7">
         <v>39173</v>
       </c>
@@ -1192,7 +1228,7 @@
         <v>56.1</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="7">
         <v>39203</v>
       </c>
@@ -1215,7 +1251,7 @@
         <v>58.6</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="7">
         <v>39234</v>
       </c>
@@ -1238,7 +1274,7 @@
         <v>55.7</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="7">
         <v>39264</v>
       </c>
@@ -1261,7 +1297,7 @@
         <v>54.5</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="7">
         <v>39295</v>
       </c>
@@ -1284,7 +1320,7 @@
         <v>53.3</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="7">
         <v>39326</v>
       </c>
@@ -1307,7 +1343,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="7">
         <v>39356</v>
       </c>
@@ -1330,7 +1366,7 @@
         <v>56.1</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="7">
         <v>39387</v>
       </c>
@@ -1353,7 +1389,7 @@
         <v>53.2</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="7">
         <v>39417</v>
       </c>
@@ -1376,7 +1412,7 @@
         <v>55.4</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="7">
         <v>39448</v>
       </c>
@@ -1399,7 +1435,7 @@
         <v>55.3</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="7">
         <v>39479</v>
       </c>
@@ -1422,7 +1458,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="7">
         <v>39508</v>
       </c>
@@ -1445,7 +1481,7 @@
         <v>53.4</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="7">
         <v>39539</v>
       </c>
@@ -1468,7 +1504,7 @@
         <v>58.4</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="7">
         <v>39569</v>
       </c>
@@ -1491,7 +1527,7 @@
         <v>59.2</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="7">
         <v>39600</v>
       </c>
@@ -1514,7 +1550,7 @@
         <v>53.3</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="7">
         <v>39630</v>
       </c>
@@ -1537,7 +1573,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="7">
         <v>39661</v>
       </c>
@@ -1560,7 +1596,7 @@
         <v>48.4</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="7">
         <v>39692</v>
       </c>
@@ -1583,7 +1619,7 @@
         <v>48.4</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="7">
         <v>39722</v>
       </c>
@@ -1606,7 +1642,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="7">
         <v>39753</v>
       </c>
@@ -1629,7 +1665,7 @@
         <v>44.6</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="7">
         <v>39783</v>
       </c>
@@ -1652,7 +1688,7 @@
         <v>38.799999999999997</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="7">
         <v>39814</v>
       </c>
@@ -1675,7 +1711,7 @@
         <v>41.2</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="7">
         <v>39845</v>
       </c>
@@ -1698,7 +1734,7 @@
         <v>45.3</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="7">
         <v>39873</v>
       </c>
@@ -1721,7 +1757,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="7">
         <v>39904</v>
       </c>
@@ -1744,7 +1780,7 @@
         <v>52.4</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="7">
         <v>39934</v>
       </c>
@@ -1767,7 +1803,7 @@
         <v>53.5</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="7">
         <v>39965</v>
       </c>
@@ -1790,7 +1826,7 @@
         <v>53.1</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="7">
         <v>39995</v>
       </c>
@@ -1813,7 +1849,7 @@
         <v>53.2</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="7">
         <v>40026</v>
       </c>
@@ -1836,7 +1872,7 @@
         <v>53.3</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="7">
         <v>40057</v>
       </c>
@@ -1859,7 +1895,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="7">
         <v>40087</v>
       </c>
@@ -1882,7 +1918,7 @@
         <v>54.3</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="7">
         <v>40118</v>
       </c>
@@ -1905,7 +1941,7 @@
         <v>55.2</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="7">
         <v>40148</v>
       </c>
@@ -1928,7 +1964,7 @@
         <v>55.2</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="7">
         <v>40179</v>
       </c>
@@ -1951,7 +1987,7 @@
         <v>56.6</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="7">
         <v>40210</v>
       </c>
@@ -1974,7 +2010,7 @@
         <v>55.8</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="7">
         <v>40238</v>
       </c>
@@ -1997,7 +2033,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" s="7">
         <v>40269</v>
       </c>
@@ -2020,7 +2056,7 @@
         <v>55.1</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" s="7">
         <v>40299</v>
       </c>
@@ -2043,7 +2079,7 @@
         <v>55.7</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" s="7">
         <v>40330</v>
       </c>
@@ -2066,7 +2102,7 @@
         <v>53.9</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" s="7">
         <v>40360</v>
       </c>
@@ -2089,7 +2125,7 @@
         <v>52.1</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" s="7">
         <v>40391</v>
       </c>
@@ -2112,7 +2148,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" s="7">
         <v>40422</v>
       </c>
@@ -2135,7 +2171,7 @@
         <v>51.7</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" s="7">
         <v>40452</v>
       </c>
@@ -2158,7 +2194,7 @@
         <v>53.8</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" s="7">
         <v>40483</v>
       </c>
@@ -2181,7 +2217,7 @@
         <v>54.7</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" s="7">
         <v>40513</v>
       </c>
@@ -2204,7 +2240,7 @@
         <v>55.2</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" s="7">
         <v>40544</v>
       </c>
@@ -2227,7 +2263,7 @@
         <v>53.9</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" s="7">
         <v>40575</v>
       </c>
@@ -2250,7 +2286,7 @@
         <v>52.9</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" s="7">
         <v>40603</v>
       </c>
@@ -2273,7 +2309,7 @@
         <v>52.2</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" s="7">
         <v>40634</v>
       </c>
@@ -2296,7 +2332,7 @@
         <v>53.4</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" s="7">
         <v>40664</v>
       </c>
@@ -2319,7 +2355,7 @@
         <v>52.9</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" s="7">
         <v>40695</v>
       </c>
@@ -2342,7 +2378,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" s="7">
         <v>40725</v>
       </c>
@@ -2365,7 +2401,7 @@
         <v>50.9</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" s="7">
         <v>40756</v>
       </c>
@@ -2388,7 +2424,7 @@
         <v>50.7</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" s="7">
         <v>40787</v>
       </c>
@@ -2411,7 +2447,7 @@
         <v>50.9</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" s="7">
         <v>40817</v>
       </c>
@@ -2434,7 +2470,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" s="7">
         <v>40848</v>
       </c>
@@ -2457,7 +2493,7 @@
         <v>50.4</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" s="7">
         <v>40878</v>
       </c>
@@ -2480,7 +2516,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" s="7">
         <v>40909</v>
       </c>
@@ -2503,7 +2539,7 @@
         <v>50.3</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" s="7">
         <v>40940</v>
       </c>
@@ -2526,7 +2562,7 @@
         <v>50.5</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" s="7">
         <v>40969</v>
       </c>
@@ -2549,7 +2585,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" s="7">
         <v>41000</v>
       </c>
@@ -2572,7 +2608,7 @@
         <v>53.1</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" s="7">
         <v>41030</v>
       </c>
@@ -2595,7 +2631,7 @@
         <v>53.3</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" s="7">
         <v>41061</v>
       </c>
@@ -2618,7 +2654,7 @@
         <v>50.4</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" s="7">
         <v>41091</v>
       </c>
@@ -2641,7 +2677,7 @@
         <v>50.2</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" s="7">
         <v>41122</v>
       </c>
@@ -2664,7 +2700,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" s="7">
         <v>41153</v>
       </c>
@@ -2687,7 +2723,7 @@
         <v>49.2</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" s="7">
         <v>41183</v>
       </c>
@@ -2710,7 +2746,7 @@
         <v>49.8</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" s="7">
         <v>41214</v>
       </c>
@@ -2733,7 +2769,7 @@
         <v>50.2</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" s="7">
         <v>41244</v>
       </c>
@@ -2756,7 +2792,7 @@
         <v>50.6</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" s="7">
         <v>41275</v>
       </c>
@@ -2779,7 +2815,7 @@
         <v>50.6</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" s="7">
         <v>41306</v>
       </c>
@@ -2802,7 +2838,7 @@
         <v>50.4</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" s="7">
         <v>41334</v>
       </c>
@@ -2825,7 +2861,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" s="7">
         <v>41365</v>
       </c>
@@ -2848,7 +2884,7 @@
         <v>50.9</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" s="7">
         <v>41395</v>
       </c>
@@ -2871,7 +2907,7 @@
         <v>50.6</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" s="7">
         <v>41426</v>
       </c>
@@ -2894,7 +2930,7 @@
         <v>50.8</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" s="7">
         <v>41456</v>
       </c>
@@ -2917,7 +2953,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" s="7">
         <v>41487</v>
       </c>
@@ -2940,7 +2976,7 @@
         <v>50.3</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" s="7">
         <v>41518</v>
       </c>
@@ -2963,7 +2999,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" s="7">
         <v>41548</v>
       </c>
@@ -2986,7 +3022,7 @@
         <v>51.1</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" s="7">
         <v>41579</v>
       </c>
@@ -3009,7 +3045,7 @@
         <v>51.4</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" s="7">
         <v>41609</v>
       </c>
@@ -3032,7 +3068,7 @@
         <v>51.4</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" s="7">
         <v>41640</v>
       </c>
@@ -3055,7 +3091,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" s="7">
         <v>41671</v>
       </c>
@@ -3078,7 +3114,7 @@
         <v>50.5</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" s="7">
         <v>41699</v>
       </c>
@@ -3101,7 +3137,7 @@
         <v>50.2</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" s="7">
         <v>41730</v>
       </c>
@@ -3124,7 +3160,7 @@
         <v>50.3</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" s="7">
         <v>41760</v>
       </c>
@@ -3147,7 +3183,7 @@
         <v>50.4</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" s="7">
         <v>41791</v>
       </c>
@@ -3170,7 +3206,7 @@
         <v>50.8</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" s="7">
         <v>41821</v>
       </c>
@@ -3193,7 +3229,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" s="7">
         <v>41852</v>
       </c>
@@ -3216,7 +3252,7 @@
         <v>51.7</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" s="7">
         <v>41883</v>
       </c>
@@ -3239,7 +3275,7 @@
         <v>51.1</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" s="7">
         <v>41913</v>
       </c>
@@ -3262,7 +3298,7 @@
         <v>51.1</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" s="7">
         <v>41944</v>
       </c>
@@ -3285,7 +3321,7 @@
         <v>50.8</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" s="7">
         <v>41974</v>
       </c>
@@ -3308,7 +3344,7 @@
         <v>50.3</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" s="7">
         <v>42005</v>
       </c>
@@ -3331,7 +3367,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" s="7">
         <v>42036</v>
       </c>
@@ -3354,7 +3390,7 @@
         <v>49.8</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" s="7">
         <v>42064</v>
       </c>
@@ -3377,7 +3413,7 @@
         <v>49.9</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" s="7">
         <v>42095</v>
       </c>
@@ -3400,7 +3436,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" s="7">
         <v>42125</v>
       </c>
@@ -3423,7 +3459,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" s="7">
         <v>42156</v>
       </c>
@@ -3446,7 +3482,7 @@
         <v>50.2</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" s="7">
         <v>42186</v>
       </c>
@@ -3469,7 +3505,7 @@
         <v>50.2</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" s="7">
         <v>42217</v>
       </c>
@@ -3492,7 +3528,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" s="7">
         <v>42248</v>
       </c>
@@ -3515,7 +3551,7 @@
         <v>49.7</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" s="7">
         <v>42278</v>
       </c>
@@ -3538,7 +3574,7 @@
         <v>49.8</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" s="7">
         <v>42309</v>
       </c>
@@ -3561,7 +3597,7 @@
         <v>49.8</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" s="7">
         <v>42339</v>
       </c>
@@ -3584,7 +3620,7 @@
         <v>49.6</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" s="7">
         <v>42370</v>
       </c>
@@ -3607,7 +3643,7 @@
         <v>49.7</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" s="7">
         <v>42401</v>
       </c>
@@ -3630,7 +3666,7 @@
         <v>49.4</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" s="7">
         <v>42430</v>
       </c>
@@ -3653,7 +3689,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137" s="7">
         <v>42461</v>
       </c>
@@ -3676,7 +3712,7 @@
         <v>50.2</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" s="7">
         <v>42491</v>
       </c>
@@ -3699,7 +3735,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" s="7">
         <v>42522</v>
       </c>
@@ -3722,7 +3758,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" s="7">
         <v>42552</v>
       </c>
@@ -3745,7 +3781,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" s="7">
         <v>42583</v>
       </c>
@@ -3768,7 +3804,7 @@
         <v>49.9</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" s="7">
         <v>42614</v>
       </c>
@@ -3791,7 +3827,7 @@
         <v>50.4</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" s="7">
         <v>42644</v>
       </c>
@@ -3814,7 +3850,7 @@
         <v>50.4</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" s="7">
         <v>42675</v>
       </c>
@@ -3837,7 +3873,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" s="7">
         <v>42705</v>
       </c>
@@ -3860,7 +3896,7 @@
         <v>51.7</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146" s="7">
         <v>42736</v>
       </c>
@@ -3883,7 +3919,7 @@
         <v>51.4</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" s="7">
         <v>42767</v>
       </c>
@@ -3906,7 +3942,7 @@
         <v>51.3</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148" s="7">
         <v>42795</v>
       </c>
@@ -3929,7 +3965,7 @@
         <v>51.6</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149" s="7">
         <v>42826</v>
       </c>
@@ -3952,7 +3988,7 @@
         <v>51.8</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150" s="7">
         <v>42856</v>
       </c>
@@ -3975,7 +4011,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A151" s="7">
         <v>42887</v>
       </c>
@@ -3998,7 +4034,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" s="7">
         <v>42917</v>
       </c>
@@ -4021,7 +4057,7 @@
         <v>51.7</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153" s="7">
         <v>42948</v>
       </c>
@@ -4044,7 +4080,7 @@
         <v>51.4</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A154" s="7">
         <v>42979</v>
       </c>
@@ -4067,7 +4103,7 @@
         <v>51.7</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A155" s="7">
         <v>43009</v>
       </c>
@@ -4090,7 +4126,7 @@
         <v>52.4</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A156" s="7">
         <v>43040</v>
       </c>
@@ -4113,7 +4149,7 @@
         <v>51.6</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A157" s="7">
         <v>43070</v>
       </c>
@@ -4136,7 +4172,7 @@
         <v>51.8</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158" s="7">
         <v>43101</v>
       </c>
@@ -4159,7 +4195,7 @@
         <v>51.6</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159" s="7">
         <v>43132</v>
       </c>
@@ -4182,7 +4218,7 @@
         <v>51.3</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A160" s="7">
         <v>43160</v>
       </c>
@@ -4205,7 +4241,7 @@
         <v>50.3</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A161" s="7">
         <v>43191</v>
       </c>
@@ -4228,7 +4264,7 @@
         <v>51.5</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A162" s="7">
         <v>43221</v>
       </c>
@@ -4251,7 +4287,7 @@
         <v>51.4</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A163" s="7">
         <v>43252</v>
       </c>
@@ -4274,7 +4310,7 @@
         <v>51.9</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A164" s="7">
         <v>43282</v>
       </c>
@@ -4297,7 +4333,7 @@
         <v>51.5</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A165" s="7">
         <v>43313</v>
       </c>
@@ -4320,7 +4356,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A166" s="7">
         <v>43344</v>
       </c>
@@ -4343,7 +4379,7 @@
         <v>51.3</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A167" s="7">
         <v>43374</v>
       </c>
@@ -4366,7 +4402,7 @@
         <v>50.8</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A168" s="7">
         <v>43405</v>
       </c>
@@ -4389,7 +4425,7 @@
         <v>50.2</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A169" s="7">
         <v>43435</v>
       </c>
@@ -4412,7 +4448,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A170" s="7">
         <v>43466</v>
       </c>
@@ -4435,7 +4471,7 @@
         <v>49.4</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A171" s="7">
         <v>43497</v>
       </c>
@@ -4458,7 +4494,7 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A172" s="7">
         <v>43525</v>
       </c>
@@ -4481,7 +4517,7 @@
         <v>49.2</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A173" s="7">
         <v>43556</v>
       </c>
@@ -4504,7 +4540,7 @@
         <v>50.5</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A174" s="7">
         <v>43586</v>
       </c>
@@ -4527,7 +4563,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A175" s="7">
         <v>43617</v>
       </c>
@@ -4550,7 +4586,7 @@
         <v>49.4</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A176" s="7">
         <v>43647</v>
       </c>
@@ -4573,7 +4609,7 @@
         <v>49.4</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A177" s="7">
         <v>43678</v>
       </c>
@@ -4596,7 +4632,7 @@
         <v>49.7</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A178" s="7">
         <v>43709</v>
       </c>
@@ -4619,7 +4655,7 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A179" s="7">
         <v>43739</v>
       </c>
@@ -4642,7 +4678,7 @@
         <v>49.8</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A180" s="7">
         <v>43770</v>
       </c>
@@ -4665,7 +4701,7 @@
         <v>49.3</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A181" s="7">
         <v>43800</v>
       </c>
@@ -4688,7 +4724,7 @@
         <v>50.2</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A182" s="7">
         <v>43831</v>
       </c>
@@ -4711,7 +4747,7 @@
         <v>50.2</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A183" s="7">
         <v>43862</v>
       </c>
@@ -4734,7 +4770,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A184" s="7">
         <v>43891</v>
       </c>
@@ -4757,7 +4793,7 @@
         <v>35.700000000000003</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A185" s="7">
         <v>43922</v>
       </c>
@@ -4780,7 +4816,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A186" s="7">
         <v>43952</v>
       </c>
@@ -4803,7 +4839,7 @@
         <v>50.8</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A187" s="7">
         <v>43983</v>
       </c>
@@ -4826,7 +4862,7 @@
         <v>50.6</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A188" s="7">
         <v>44013</v>
       </c>
@@ -4849,7 +4885,7 @@
         <v>50.9</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A189" s="7">
         <v>44044</v>
       </c>
@@ -4872,7 +4908,7 @@
         <v>51.1</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A190" s="7">
         <v>44075</v>
       </c>
@@ -4895,7 +4931,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A191" s="7">
         <v>44105</v>
       </c>
@@ -4918,7 +4954,7 @@
         <v>51.5</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A192" s="7">
         <v>44136</v>
       </c>
@@ -4941,7 +4977,7 @@
         <v>51.4</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A193" s="7">
         <v>44166</v>
       </c>
@@ -4964,7 +5000,7 @@
         <v>52.1</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A194" s="7">
         <v>44197</v>
       </c>
@@ -4987,7 +5023,7 @@
         <v>51.9</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A195" s="7">
         <v>44228</v>
       </c>
@@ -5010,7 +5046,7 @@
         <v>51.3</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A196" s="7">
         <v>44256</v>
       </c>
@@ -5033,7 +5069,7 @@
         <v>50.6</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A197" s="7">
         <v>44287</v>
       </c>
@@ -5056,7 +5092,7 @@
         <v>51.9</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A198" s="7">
         <v>44317</v>
       </c>
@@ -5079,7 +5115,7 @@
         <v>51.1</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A199" s="7">
         <v>44348</v>
       </c>
@@ -5102,7 +5138,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A200" s="7">
         <v>44378</v>
       </c>
@@ -5125,7 +5161,7 @@
         <v>50.9</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A201" s="7">
         <v>44409</v>
       </c>
@@ -5148,7 +5184,7 @@
         <v>50.4</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A202" s="7">
         <v>44440</v>
       </c>
@@ -5171,7 +5207,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A203" s="7">
         <v>44470</v>
       </c>
@@ -5194,7 +5230,7 @@
         <v>49.6</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A204" s="7">
         <v>44501</v>
       </c>
@@ -5217,7 +5253,7 @@
         <v>49.2</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A205" s="7">
         <v>44531</v>
       </c>
@@ -5240,7 +5276,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A206" s="7">
         <v>44562</v>
       </c>
@@ -5263,7 +5299,7 @@
         <v>50.3</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A207" s="7">
         <v>44593</v>
       </c>
@@ -5286,7 +5322,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A208" s="7">
         <v>44621</v>
       </c>
@@ -5309,7 +5345,7 @@
         <v>50.2</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A209" s="7">
         <v>44652</v>
       </c>
@@ -5332,7 +5368,7 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A210" s="7">
         <v>44682</v>
       </c>
@@ -5355,7 +5391,7 @@
         <v>47.4</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A211" s="7">
         <v>44713</v>
       </c>
@@ -5378,7 +5414,7 @@
         <v>49.6</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A212" s="7">
         <v>44743</v>
       </c>
@@ -5401,7 +5437,7 @@
         <v>50.2</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A213" s="7">
         <v>44774</v>
       </c>
@@ -5424,7 +5460,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A214" s="7">
         <v>44805</v>
       </c>
@@ -5447,7 +5483,7 @@
         <v>49.4</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A215" s="7">
         <v>44835</v>
       </c>
@@ -5470,7 +5506,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A216" s="7">
         <v>44866</v>
       </c>
@@ -5493,7 +5529,7 @@
         <v>49.2</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A217" s="7">
         <v>44896</v>
       </c>
@@ -5516,7 +5552,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A218" s="7">
         <v>44927</v>
       </c>
@@ -5539,7 +5575,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A219" s="7">
         <v>44958</v>
       </c>
@@ -5562,7 +5598,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A220" s="7">
         <v>44986</v>
       </c>
@@ -5585,7 +5621,7 @@
         <v>52.6</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A221" s="7">
         <v>45017</v>
       </c>
@@ -5608,7 +5644,7 @@
         <v>51.9</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A222" s="7">
         <v>45047</v>
       </c>
@@ -5631,7 +5667,7 @@
         <v>49.2</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A223" s="7">
         <v>45078</v>
       </c>
@@ -5654,7 +5690,7 @@
         <v>48.8</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A224" s="7">
         <v>45108</v>
       </c>
@@ -5677,7 +5713,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A225" s="7">
         <v>45139</v>
       </c>
@@ -5700,7 +5736,7 @@
         <v>49.3</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A226" s="7">
         <v>45170</v>
       </c>
@@ -5723,7 +5759,7 @@
         <v>49.7</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A227" s="7">
         <v>45200</v>
       </c>
@@ -5746,7 +5782,7 @@
         <v>50.2</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A228" s="7">
         <v>45231</v>
       </c>
@@ -5769,7 +5805,7 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A229" s="7">
         <v>45261</v>
       </c>
@@ -5792,7 +5828,7 @@
         <v>49.4</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A230" s="7">
         <v>45292</v>
       </c>
@@ -5815,7 +5851,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A231" s="7">
         <v>45323</v>
       </c>
@@ -5838,7 +5874,7 @@
         <v>49.2</v>
       </c>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A232" s="7">
         <v>45352</v>
       </c>
@@ -5861,7 +5897,7 @@
         <v>49.1</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A233" s="7">
         <v>45383</v>
       </c>
@@ -5884,7 +5920,7 @@
         <v>50.8</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A234" s="7">
         <v>45413</v>
       </c>
@@ -5907,7 +5943,7 @@
         <v>50.4</v>
       </c>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A235" s="7">
         <v>45444</v>
       </c>
@@ -5930,7 +5966,7 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A236" s="7">
         <v>45474</v>
       </c>
@@ -5953,7 +5989,7 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A237" s="7">
         <v>45505</v>
       </c>
@@ -5976,7 +6012,7 @@
         <v>49.4</v>
       </c>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A238" s="7">
         <v>45536</v>
       </c>
@@ -5999,7 +6035,7 @@
         <v>49.1</v>
       </c>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A239" s="7">
         <v>45566</v>
       </c>
@@ -6022,7 +6058,7 @@
         <v>49.8</v>
       </c>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A240" s="7">
         <v>45597</v>
       </c>
@@ -6045,7 +6081,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A241" s="7">
         <v>45627</v>
       </c>
@@ -6068,7 +6104,7 @@
         <v>50.3</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A242" s="7">
         <v>45658</v>
       </c>
@@ -6091,7 +6127,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A243" s="7">
         <v>45689</v>
       </c>
@@ -6114,7 +6150,7 @@
         <v>49.1</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A244" s="7">
         <v>45717</v>
       </c>
@@ -6137,7 +6173,7 @@
         <v>50.2</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A245" s="7">
         <v>45748</v>
       </c>
@@ -6160,7 +6196,7 @@
         <v>50.5</v>
       </c>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A246" s="7">
         <v>45778</v>
       </c>
@@ -6183,7 +6219,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A247" s="7">
         <v>45809</v>
       </c>
@@ -6206,7 +6242,7 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A248" s="7">
         <v>45839</v>
       </c>
@@ -6229,7 +6265,7 @@
         <v>49.7</v>
       </c>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A249" s="7">
         <v>45870</v>
       </c>
@@ -6252,7 +6288,7 @@
         <v>49.3</v>
       </c>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A250" s="7">
         <v>45901</v>
       </c>
@@ -6275,7 +6311,7 @@
         <v>49.4</v>
       </c>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A251" s="7">
         <v>45931</v>
       </c>
@@ -6298,7 +6334,7 @@
         <v>49.8</v>
       </c>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A252" s="7">
         <v>45962</v>
       </c>
@@ -6321,7 +6357,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A253" s="7">
         <v>45992</v>
       </c>
@@ -6344,7 +6380,7 @@
         <v>49.2</v>
       </c>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A254" s="7">
         <v>46023</v>
       </c>
@@ -6367,7 +6403,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A255" s="7">
         <v>46054</v>
       </c>
@@ -6390,7 +6426,7 @@
         <v>49.3</v>
       </c>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A256" s="7">
         <v>46082</v>
       </c>
@@ -6413,7 +6449,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A257" s="7">
         <v>46113</v>
       </c>
@@ -6436,7 +6472,7 @@
         <v>50.4</v>
       </c>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A258" s="7">
         <v>46143</v>
       </c>
@@ -6459,7 +6495,7 @@
         <v>50.3</v>
       </c>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A259" s="7">
         <v>46174</v>
       </c>
@@ -6490,11 +6526,5162 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{317C4CC0-835B-4324-B0A5-C9431E0655E3}">
+  <dimension ref="A1:H235"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.09765625" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.69921875" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.8984375" style="18" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.19921875" style="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="8.796875" style="16"/>
+    <col min="8" max="8" width="9.09765625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="12"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="13">
+        <v>39083</v>
+      </c>
+      <c r="B2" s="13">
+        <v>39114</v>
+      </c>
+      <c r="C2" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="16">
+        <v>60.4</v>
+      </c>
+      <c r="H2" s="12"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="13">
+        <v>39114</v>
+      </c>
+      <c r="B3" s="13">
+        <v>39142</v>
+      </c>
+      <c r="C3" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="16">
+        <v>60.6</v>
+      </c>
+      <c r="G3" s="16">
+        <v>60.4</v>
+      </c>
+      <c r="H3" s="12"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="13">
+        <v>39142</v>
+      </c>
+      <c r="B4" s="13">
+        <v>39173</v>
+      </c>
+      <c r="C4" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="16">
+        <v>58.2</v>
+      </c>
+      <c r="G4" s="16">
+        <v>60.6</v>
+      </c>
+      <c r="H4" s="12"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="13">
+        <v>39173</v>
+      </c>
+      <c r="B5" s="13">
+        <v>39203</v>
+      </c>
+      <c r="C5" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="16">
+        <v>60.4</v>
+      </c>
+      <c r="G5" s="16">
+        <v>58.2</v>
+      </c>
+      <c r="H5" s="12"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="13">
+        <v>39203</v>
+      </c>
+      <c r="B6" s="13">
+        <v>39234</v>
+      </c>
+      <c r="C6" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="16">
+        <v>62.2</v>
+      </c>
+      <c r="G6" s="16">
+        <v>60.4</v>
+      </c>
+      <c r="H6" s="12"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="13">
+        <v>39234</v>
+      </c>
+      <c r="B7" s="13">
+        <v>39264</v>
+      </c>
+      <c r="C7" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="16">
+        <v>60</v>
+      </c>
+      <c r="G7" s="16">
+        <v>62.2</v>
+      </c>
+      <c r="H7" s="12"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="13">
+        <v>39264</v>
+      </c>
+      <c r="B8" s="13">
+        <v>39295</v>
+      </c>
+      <c r="C8" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="16">
+        <v>59.4</v>
+      </c>
+      <c r="G8" s="16">
+        <v>60</v>
+      </c>
+      <c r="H8" s="12"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="13">
+        <v>39295</v>
+      </c>
+      <c r="B9" s="13">
+        <v>39326</v>
+      </c>
+      <c r="C9" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="16">
+        <v>61.7</v>
+      </c>
+      <c r="G9" s="16">
+        <v>59.4</v>
+      </c>
+      <c r="H9" s="12"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="13">
+        <v>39326</v>
+      </c>
+      <c r="B10" s="13">
+        <v>39356</v>
+      </c>
+      <c r="C10" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="16">
+        <v>61.9</v>
+      </c>
+      <c r="G10" s="16">
+        <v>61.7</v>
+      </c>
+      <c r="H10" s="12"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="13">
+        <v>39356</v>
+      </c>
+      <c r="B11" s="13">
+        <v>39387</v>
+      </c>
+      <c r="C11" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="16">
+        <v>61.4</v>
+      </c>
+      <c r="G11" s="16">
+        <v>61.9</v>
+      </c>
+      <c r="H11" s="12"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="13">
+        <v>39387</v>
+      </c>
+      <c r="B12" s="13">
+        <v>39417</v>
+      </c>
+      <c r="C12" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="16">
+        <v>60.6</v>
+      </c>
+      <c r="G12" s="16">
+        <v>61.4</v>
+      </c>
+      <c r="H12" s="12"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="13">
+        <v>39417</v>
+      </c>
+      <c r="B13" s="13">
+        <v>39448</v>
+      </c>
+      <c r="C13" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="16">
+        <v>60.2</v>
+      </c>
+      <c r="G13" s="16">
+        <v>60.6</v>
+      </c>
+      <c r="H13" s="12"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="13">
+        <v>39448</v>
+      </c>
+      <c r="B14" s="13">
+        <v>39479</v>
+      </c>
+      <c r="C14" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="16">
+        <v>60.2</v>
+      </c>
+      <c r="G14" s="16">
+        <v>60.2</v>
+      </c>
+      <c r="H14" s="12"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="13">
+        <v>39479</v>
+      </c>
+      <c r="B15" s="13">
+        <v>39508</v>
+      </c>
+      <c r="C15" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="16">
+        <v>59.3</v>
+      </c>
+      <c r="G15" s="16">
+        <v>60.2</v>
+      </c>
+      <c r="H15" s="12"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="13">
+        <v>39508</v>
+      </c>
+      <c r="B16" s="13">
+        <v>39539</v>
+      </c>
+      <c r="C16" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="16">
+        <v>58.9</v>
+      </c>
+      <c r="G16" s="16">
+        <v>59.3</v>
+      </c>
+      <c r="H16" s="12"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="13">
+        <v>39539</v>
+      </c>
+      <c r="B17" s="13">
+        <v>39569</v>
+      </c>
+      <c r="C17" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" s="16">
+        <v>58.4</v>
+      </c>
+      <c r="G17" s="16">
+        <v>58.9</v>
+      </c>
+      <c r="H17" s="12"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="13">
+        <v>39569</v>
+      </c>
+      <c r="B18" s="13">
+        <v>39600</v>
+      </c>
+      <c r="C18" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="16">
+        <v>57.4</v>
+      </c>
+      <c r="G18" s="16">
+        <v>58.4</v>
+      </c>
+      <c r="H18" s="12"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="13">
+        <v>39600</v>
+      </c>
+      <c r="B19" s="13">
+        <v>39630</v>
+      </c>
+      <c r="C19" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" s="16">
+        <v>57.4</v>
+      </c>
+      <c r="G19" s="16">
+        <v>57.4</v>
+      </c>
+      <c r="H19" s="12"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" s="13">
+        <v>39630</v>
+      </c>
+      <c r="B20" s="13">
+        <v>39661</v>
+      </c>
+      <c r="C20" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" s="16">
+        <v>55.7</v>
+      </c>
+      <c r="G20" s="16">
+        <v>57.4</v>
+      </c>
+      <c r="H20" s="12"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" s="13">
+        <v>39661</v>
+      </c>
+      <c r="B21" s="13">
+        <v>39692</v>
+      </c>
+      <c r="C21" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" s="16">
+        <v>52.9</v>
+      </c>
+      <c r="G21" s="16">
+        <v>55.7</v>
+      </c>
+      <c r="H21" s="12"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" s="13">
+        <v>39692</v>
+      </c>
+      <c r="B22" s="13">
+        <v>39722</v>
+      </c>
+      <c r="C22" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" s="16">
+        <v>55</v>
+      </c>
+      <c r="G22" s="16">
+        <v>52.9</v>
+      </c>
+      <c r="H22" s="12"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" s="13">
+        <v>39722</v>
+      </c>
+      <c r="B23" s="13">
+        <v>39753</v>
+      </c>
+      <c r="C23" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" s="16">
+        <v>53.1</v>
+      </c>
+      <c r="G23" s="16">
+        <v>55</v>
+      </c>
+      <c r="H23" s="12"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" s="13">
+        <v>39753</v>
+      </c>
+      <c r="B24" s="13">
+        <v>39783</v>
+      </c>
+      <c r="C24" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D24" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" s="16">
+        <v>51.2</v>
+      </c>
+      <c r="G24" s="16">
+        <v>53.1</v>
+      </c>
+      <c r="H24" s="12"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" s="13">
+        <v>39783</v>
+      </c>
+      <c r="B25" s="13">
+        <v>39814</v>
+      </c>
+      <c r="C25" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D25" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" s="16">
+        <v>50.8</v>
+      </c>
+      <c r="G25" s="16">
+        <v>51.2</v>
+      </c>
+      <c r="H25" s="12"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" s="13">
+        <v>39814</v>
+      </c>
+      <c r="B26" s="13">
+        <v>39845</v>
+      </c>
+      <c r="C26" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D26" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" s="16">
+        <v>53.7</v>
+      </c>
+      <c r="G26" s="16">
+        <v>50.8</v>
+      </c>
+      <c r="H26" s="12"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" s="13">
+        <v>39845</v>
+      </c>
+      <c r="B27" s="13">
+        <v>39873</v>
+      </c>
+      <c r="C27" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D27" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" s="16">
+        <v>55.1</v>
+      </c>
+      <c r="G27" s="16">
+        <v>53.7</v>
+      </c>
+      <c r="H27" s="12"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" s="13">
+        <v>39873</v>
+      </c>
+      <c r="B28" s="13">
+        <v>39904</v>
+      </c>
+      <c r="C28" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D28" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" s="16">
+        <v>54.4</v>
+      </c>
+      <c r="G28" s="16">
+        <v>55.1</v>
+      </c>
+      <c r="H28" s="12"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" s="13">
+        <v>39904</v>
+      </c>
+      <c r="B29" s="13">
+        <v>39934</v>
+      </c>
+      <c r="C29" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D29" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" s="16">
+        <v>53.5</v>
+      </c>
+      <c r="G29" s="16">
+        <v>54.4</v>
+      </c>
+      <c r="H29" s="12"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" s="13">
+        <v>39934</v>
+      </c>
+      <c r="B30" s="13">
+        <v>39965</v>
+      </c>
+      <c r="C30" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" s="16">
+        <v>54.9</v>
+      </c>
+      <c r="G30" s="16">
+        <v>53.5</v>
+      </c>
+      <c r="H30" s="12"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" s="13">
+        <v>39965</v>
+      </c>
+      <c r="B31" s="13">
+        <v>39995</v>
+      </c>
+      <c r="C31" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D31" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E31" s="16">
+        <v>55.4</v>
+      </c>
+      <c r="G31" s="16">
+        <v>54.9</v>
+      </c>
+      <c r="H31" s="12"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" s="13">
+        <v>39995</v>
+      </c>
+      <c r="B32" s="13">
+        <v>40026</v>
+      </c>
+      <c r="C32" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D32" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E32" s="16">
+        <v>57.3</v>
+      </c>
+      <c r="G32" s="16">
+        <v>55.4</v>
+      </c>
+      <c r="H32" s="12"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33" s="13">
+        <v>40026</v>
+      </c>
+      <c r="B33" s="13">
+        <v>40057</v>
+      </c>
+      <c r="C33" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D33" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" s="16">
+        <v>57.3</v>
+      </c>
+      <c r="G33" s="16">
+        <v>57.3</v>
+      </c>
+      <c r="H33" s="12"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34" s="13">
+        <v>40057</v>
+      </c>
+      <c r="B34" s="13">
+        <v>40087</v>
+      </c>
+      <c r="C34" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D34" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" s="16">
+        <v>57.9</v>
+      </c>
+      <c r="G34" s="16">
+        <v>57.3</v>
+      </c>
+      <c r="H34" s="12"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A35" s="13">
+        <v>40087</v>
+      </c>
+      <c r="B35" s="13">
+        <v>40118</v>
+      </c>
+      <c r="C35" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D35" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" s="16">
+        <v>59.5</v>
+      </c>
+      <c r="G35" s="16">
+        <v>57.9</v>
+      </c>
+      <c r="H35" s="12"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A36" s="13">
+        <v>40118</v>
+      </c>
+      <c r="B36" s="13">
+        <v>40148</v>
+      </c>
+      <c r="C36" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D36" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" s="16">
+        <v>58.4</v>
+      </c>
+      <c r="G36" s="16">
+        <v>59.5</v>
+      </c>
+      <c r="H36" s="12"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A37" s="13">
+        <v>40148</v>
+      </c>
+      <c r="B37" s="13">
+        <v>40179</v>
+      </c>
+      <c r="C37" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D37" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E37" s="16">
+        <v>58.8</v>
+      </c>
+      <c r="G37" s="16">
+        <v>58.4</v>
+      </c>
+      <c r="H37" s="12"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A38" s="13">
+        <v>40179</v>
+      </c>
+      <c r="B38" s="13">
+        <v>40210</v>
+      </c>
+      <c r="C38" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D38" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E38" s="16">
+        <v>58.1</v>
+      </c>
+      <c r="G38" s="16">
+        <v>58.8</v>
+      </c>
+      <c r="H38" s="12"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A39" s="13">
+        <v>40210</v>
+      </c>
+      <c r="B39" s="13">
+        <v>40238</v>
+      </c>
+      <c r="C39" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D39" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E39" s="16">
+        <v>57</v>
+      </c>
+      <c r="G39" s="16">
+        <v>58.1</v>
+      </c>
+      <c r="H39" s="12"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A40" s="13">
+        <v>40238</v>
+      </c>
+      <c r="B40" s="13">
+        <v>40269</v>
+      </c>
+      <c r="C40" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D40" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E40" s="16">
+        <v>57.3</v>
+      </c>
+      <c r="G40" s="16">
+        <v>57</v>
+      </c>
+      <c r="H40" s="12"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A41" s="13">
+        <v>40269</v>
+      </c>
+      <c r="B41" s="13">
+        <v>40299</v>
+      </c>
+      <c r="C41" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D41" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E41" s="16">
+        <v>57.8</v>
+      </c>
+      <c r="G41" s="16">
+        <v>57.3</v>
+      </c>
+      <c r="H41" s="12"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A42" s="13">
+        <v>40299</v>
+      </c>
+      <c r="B42" s="13">
+        <v>40330</v>
+      </c>
+      <c r="C42" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D42" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" s="16">
+        <v>58.1</v>
+      </c>
+      <c r="G42" s="16">
+        <v>57.8</v>
+      </c>
+      <c r="H42" s="12"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A43" s="13">
+        <v>40330</v>
+      </c>
+      <c r="B43" s="13">
+        <v>40360</v>
+      </c>
+      <c r="C43" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D43" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E43" s="16">
+        <v>58.8</v>
+      </c>
+      <c r="G43" s="16">
+        <v>58.1</v>
+      </c>
+      <c r="H43" s="12"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A44" s="13">
+        <v>40360</v>
+      </c>
+      <c r="B44" s="13">
+        <v>40391</v>
+      </c>
+      <c r="C44" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D44" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E44" s="16">
+        <v>57.1</v>
+      </c>
+      <c r="G44" s="16">
+        <v>58.8</v>
+      </c>
+      <c r="H44" s="12"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A45" s="13">
+        <v>40391</v>
+      </c>
+      <c r="B45" s="13">
+        <v>40422</v>
+      </c>
+      <c r="C45" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D45" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E45" s="16">
+        <v>58</v>
+      </c>
+      <c r="G45" s="16">
+        <v>57.1</v>
+      </c>
+      <c r="H45" s="12"/>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A46" s="13">
+        <v>40422</v>
+      </c>
+      <c r="B46" s="13">
+        <v>40452</v>
+      </c>
+      <c r="C46" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D46" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E46" s="16">
+        <v>57.9</v>
+      </c>
+      <c r="G46" s="16">
+        <v>58</v>
+      </c>
+      <c r="H46" s="12"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A47" s="13">
+        <v>40452</v>
+      </c>
+      <c r="B47" s="13">
+        <v>40483</v>
+      </c>
+      <c r="C47" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D47" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E47" s="16">
+        <v>57.4</v>
+      </c>
+      <c r="G47" s="16">
+        <v>57.9</v>
+      </c>
+      <c r="H47" s="12"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A48" s="13">
+        <v>40483</v>
+      </c>
+      <c r="B48" s="13">
+        <v>40513</v>
+      </c>
+      <c r="C48" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D48" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E48" s="16">
+        <v>58.9</v>
+      </c>
+      <c r="G48" s="16">
+        <v>57.4</v>
+      </c>
+      <c r="H48" s="12"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A49" s="13">
+        <v>40513</v>
+      </c>
+      <c r="B49" s="13">
+        <v>40544</v>
+      </c>
+      <c r="C49" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D49" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E49" s="16">
+        <v>58.8</v>
+      </c>
+      <c r="G49" s="16">
+        <v>58.9</v>
+      </c>
+      <c r="H49" s="12"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A50" s="13">
+        <v>40544</v>
+      </c>
+      <c r="B50" s="13">
+        <v>40575</v>
+      </c>
+      <c r="C50" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D50" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E50" s="16">
+        <v>57.2</v>
+      </c>
+      <c r="G50" s="16">
+        <v>58.8</v>
+      </c>
+      <c r="H50" s="12"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A51" s="13">
+        <v>40575</v>
+      </c>
+      <c r="B51" s="13">
+        <v>40603</v>
+      </c>
+      <c r="C51" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D51" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E51" s="16">
+        <v>57</v>
+      </c>
+      <c r="G51" s="16">
+        <v>57.2</v>
+      </c>
+      <c r="H51" s="12"/>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A52" s="13">
+        <v>40603</v>
+      </c>
+      <c r="B52" s="13">
+        <v>40634</v>
+      </c>
+      <c r="C52" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D52" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E52" s="16">
+        <v>59.2</v>
+      </c>
+      <c r="G52" s="16">
+        <v>57</v>
+      </c>
+      <c r="H52" s="12"/>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A53" s="13">
+        <v>40634</v>
+      </c>
+      <c r="B53" s="13">
+        <v>40664</v>
+      </c>
+      <c r="C53" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D53" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E53" s="16">
+        <v>58.2</v>
+      </c>
+      <c r="G53" s="16">
+        <v>59.2</v>
+      </c>
+      <c r="H53" s="12"/>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A54" s="13">
+        <v>40664</v>
+      </c>
+      <c r="B54" s="13">
+        <v>40695</v>
+      </c>
+      <c r="C54" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D54" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E54" s="16">
+        <v>58.7</v>
+      </c>
+      <c r="G54" s="16">
+        <v>58.2</v>
+      </c>
+      <c r="H54" s="12"/>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A55" s="13">
+        <v>40695</v>
+      </c>
+      <c r="B55" s="13">
+        <v>40725</v>
+      </c>
+      <c r="C55" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D55" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E55" s="16">
+        <v>56.6</v>
+      </c>
+      <c r="G55" s="16">
+        <v>58.7</v>
+      </c>
+      <c r="H55" s="12"/>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A56" s="13">
+        <v>40725</v>
+      </c>
+      <c r="B56" s="13">
+        <v>40756</v>
+      </c>
+      <c r="C56" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D56" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E56" s="16">
+        <v>57.3</v>
+      </c>
+      <c r="G56" s="16">
+        <v>56.6</v>
+      </c>
+      <c r="H56" s="12"/>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A57" s="13">
+        <v>40756</v>
+      </c>
+      <c r="B57" s="13">
+        <v>40787</v>
+      </c>
+      <c r="C57" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D57" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E57" s="16">
+        <v>57.1</v>
+      </c>
+      <c r="G57" s="16">
+        <v>57.3</v>
+      </c>
+      <c r="H57" s="12"/>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A58" s="13">
+        <v>40787</v>
+      </c>
+      <c r="B58" s="13">
+        <v>40817</v>
+      </c>
+      <c r="C58" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D58" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E58" s="16">
+        <v>55.8</v>
+      </c>
+      <c r="G58" s="16">
+        <v>57.1</v>
+      </c>
+      <c r="H58" s="12"/>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A59" s="13">
+        <v>40817</v>
+      </c>
+      <c r="B59" s="13">
+        <v>40848</v>
+      </c>
+      <c r="C59" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D59" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E59" s="16">
+        <v>55.5</v>
+      </c>
+      <c r="G59" s="16">
+        <v>55.8</v>
+      </c>
+      <c r="H59" s="12"/>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A60" s="13">
+        <v>40848</v>
+      </c>
+      <c r="B60" s="13">
+        <v>40878</v>
+      </c>
+      <c r="C60" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D60" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E60" s="16">
+        <v>55.9</v>
+      </c>
+      <c r="G60" s="16">
+        <v>55.5</v>
+      </c>
+      <c r="H60" s="12"/>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A61" s="13">
+        <v>40878</v>
+      </c>
+      <c r="B61" s="13">
+        <v>40909</v>
+      </c>
+      <c r="C61" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D61" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E61" s="16">
+        <v>56.3</v>
+      </c>
+      <c r="G61" s="16">
+        <v>55.9</v>
+      </c>
+      <c r="H61" s="12"/>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A62" s="13">
+        <v>40909</v>
+      </c>
+      <c r="B62" s="13">
+        <v>40940</v>
+      </c>
+      <c r="C62" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D62" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E62" s="16">
+        <v>55.7</v>
+      </c>
+      <c r="G62" s="16">
+        <v>56.3</v>
+      </c>
+      <c r="H62" s="12"/>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A63" s="13">
+        <v>40940</v>
+      </c>
+      <c r="B63" s="13">
+        <v>40969</v>
+      </c>
+      <c r="C63" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D63" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E63" s="16">
+        <v>57.3</v>
+      </c>
+      <c r="G63" s="16">
+        <v>55.7</v>
+      </c>
+      <c r="H63" s="12"/>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A64" s="13">
+        <v>40969</v>
+      </c>
+      <c r="B64" s="13">
+        <v>41000</v>
+      </c>
+      <c r="C64" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D64" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E64" s="16">
+        <v>58</v>
+      </c>
+      <c r="G64" s="16">
+        <v>57.3</v>
+      </c>
+      <c r="H64" s="12"/>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A65" s="13">
+        <v>41000</v>
+      </c>
+      <c r="B65" s="13">
+        <v>41030</v>
+      </c>
+      <c r="C65" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D65" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E65" s="16">
+        <v>56.1</v>
+      </c>
+      <c r="G65" s="16">
+        <v>58</v>
+      </c>
+      <c r="H65" s="12"/>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A66" s="13">
+        <v>41030</v>
+      </c>
+      <c r="B66" s="13">
+        <v>41061</v>
+      </c>
+      <c r="C66" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D66" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E66" s="16">
+        <v>55.2</v>
+      </c>
+      <c r="G66" s="16">
+        <v>56.1</v>
+      </c>
+      <c r="H66" s="12"/>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A67" s="13">
+        <v>41061</v>
+      </c>
+      <c r="B67" s="13">
+        <v>41091</v>
+      </c>
+      <c r="C67" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D67" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E67" s="16">
+        <v>56.7</v>
+      </c>
+      <c r="G67" s="16">
+        <v>55.2</v>
+      </c>
+      <c r="H67" s="12"/>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A68" s="13">
+        <v>41091</v>
+      </c>
+      <c r="B68" s="13">
+        <v>41124</v>
+      </c>
+      <c r="C68" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D68" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E68" s="16">
+        <v>55.6</v>
+      </c>
+      <c r="G68" s="16">
+        <v>56.7</v>
+      </c>
+      <c r="H68" s="12"/>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A69" s="13">
+        <v>41122</v>
+      </c>
+      <c r="B69" s="13">
+        <v>41155</v>
+      </c>
+      <c r="C69" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D69" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E69" s="16">
+        <v>56.3</v>
+      </c>
+      <c r="G69" s="16">
+        <v>55.6</v>
+      </c>
+      <c r="H69" s="12"/>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A70" s="13">
+        <v>41153</v>
+      </c>
+      <c r="B70" s="13">
+        <v>41185</v>
+      </c>
+      <c r="C70" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D70" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E70" s="16">
+        <v>53.7</v>
+      </c>
+      <c r="G70" s="16">
+        <v>56.3</v>
+      </c>
+      <c r="H70" s="12"/>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A71" s="13">
+        <v>41183</v>
+      </c>
+      <c r="B71" s="13">
+        <v>41216</v>
+      </c>
+      <c r="C71" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D71" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E71" s="16">
+        <v>55.5</v>
+      </c>
+      <c r="G71" s="16">
+        <v>53.7</v>
+      </c>
+      <c r="H71" s="12"/>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A72" s="13">
+        <v>41214</v>
+      </c>
+      <c r="B72" s="13">
+        <v>41246</v>
+      </c>
+      <c r="C72" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D72" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E72" s="16">
+        <v>55.6</v>
+      </c>
+      <c r="G72" s="16">
+        <v>55.5</v>
+      </c>
+      <c r="H72" s="12"/>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A73" s="13">
+        <v>41244</v>
+      </c>
+      <c r="B73" s="13">
+        <v>41277</v>
+      </c>
+      <c r="C73" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D73" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E73" s="16">
+        <v>56.1</v>
+      </c>
+      <c r="G73" s="16">
+        <v>55.6</v>
+      </c>
+      <c r="H73" s="12"/>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A74" s="13">
+        <v>41275</v>
+      </c>
+      <c r="B74" s="13">
+        <v>41308</v>
+      </c>
+      <c r="C74" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D74" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E74" s="16">
+        <v>56.2</v>
+      </c>
+      <c r="G74" s="16">
+        <v>56.1</v>
+      </c>
+      <c r="H74" s="12"/>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A75" s="13">
+        <v>41306</v>
+      </c>
+      <c r="B75" s="13">
+        <v>41336</v>
+      </c>
+      <c r="C75" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D75" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E75" s="16">
+        <v>54.5</v>
+      </c>
+      <c r="G75" s="16">
+        <v>56.2</v>
+      </c>
+      <c r="H75" s="12"/>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A76" s="13">
+        <v>41334</v>
+      </c>
+      <c r="B76" s="13">
+        <v>41367</v>
+      </c>
+      <c r="C76" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D76" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E76" s="16">
+        <v>55.6</v>
+      </c>
+      <c r="G76" s="16">
+        <v>54.5</v>
+      </c>
+      <c r="H76" s="12"/>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A77" s="13">
+        <v>41365</v>
+      </c>
+      <c r="B77" s="13">
+        <v>41397</v>
+      </c>
+      <c r="C77" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D77" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E77" s="16">
+        <v>54.5</v>
+      </c>
+      <c r="G77" s="16">
+        <v>55.6</v>
+      </c>
+      <c r="H77" s="12"/>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A78" s="13">
+        <v>41395</v>
+      </c>
+      <c r="B78" s="13">
+        <v>41428</v>
+      </c>
+      <c r="C78" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D78" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E78" s="16">
+        <v>54.3</v>
+      </c>
+      <c r="G78" s="16">
+        <v>54.5</v>
+      </c>
+      <c r="H78" s="12"/>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A79" s="13">
+        <v>41426</v>
+      </c>
+      <c r="B79" s="13">
+        <v>41458</v>
+      </c>
+      <c r="C79" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D79" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E79" s="16">
+        <v>53.9</v>
+      </c>
+      <c r="G79" s="16">
+        <v>54.3</v>
+      </c>
+      <c r="H79" s="12"/>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A80" s="13">
+        <v>41456</v>
+      </c>
+      <c r="B80" s="13">
+        <v>41489</v>
+      </c>
+      <c r="C80" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D80" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E80" s="16">
+        <v>54.1</v>
+      </c>
+      <c r="G80" s="16">
+        <v>53.9</v>
+      </c>
+      <c r="H80" s="12"/>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A81" s="13">
+        <v>41487</v>
+      </c>
+      <c r="B81" s="13">
+        <v>41520</v>
+      </c>
+      <c r="C81" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D81" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E81" s="16">
+        <v>53.9</v>
+      </c>
+      <c r="G81" s="16">
+        <v>54.1</v>
+      </c>
+      <c r="H81" s="12"/>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A82" s="13">
+        <v>41518</v>
+      </c>
+      <c r="B82" s="13">
+        <v>41550</v>
+      </c>
+      <c r="C82" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D82" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E82" s="16">
+        <v>55.4</v>
+      </c>
+      <c r="G82" s="16">
+        <v>53.9</v>
+      </c>
+      <c r="H82" s="12"/>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A83" s="13">
+        <v>41548</v>
+      </c>
+      <c r="B83" s="13">
+        <v>41581</v>
+      </c>
+      <c r="C83" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D83" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E83" s="16">
+        <v>56.3</v>
+      </c>
+      <c r="G83" s="16">
+        <v>55.4</v>
+      </c>
+      <c r="H83" s="12"/>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A84" s="13">
+        <v>41579</v>
+      </c>
+      <c r="B84" s="13">
+        <v>41611</v>
+      </c>
+      <c r="C84" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D84" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E84" s="16">
+        <v>56</v>
+      </c>
+      <c r="G84" s="16">
+        <v>56.3</v>
+      </c>
+      <c r="H84" s="12"/>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A85" s="13">
+        <v>41609</v>
+      </c>
+      <c r="B85" s="13">
+        <v>41642</v>
+      </c>
+      <c r="C85" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D85" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E85" s="16">
+        <v>54.6</v>
+      </c>
+      <c r="G85" s="16">
+        <v>56</v>
+      </c>
+      <c r="H85" s="12"/>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A86" s="13">
+        <v>41640</v>
+      </c>
+      <c r="B86" s="13">
+        <v>41673</v>
+      </c>
+      <c r="C86" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D86" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E86" s="16">
+        <v>53.4</v>
+      </c>
+      <c r="G86" s="16">
+        <v>54.6</v>
+      </c>
+      <c r="H86" s="12"/>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A87" s="13">
+        <v>41671</v>
+      </c>
+      <c r="B87" s="13">
+        <v>41701</v>
+      </c>
+      <c r="C87" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D87" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E87" s="16">
+        <v>55</v>
+      </c>
+      <c r="G87" s="16">
+        <v>53.4</v>
+      </c>
+      <c r="H87" s="12"/>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A88" s="13">
+        <v>41699</v>
+      </c>
+      <c r="B88" s="13">
+        <v>41732</v>
+      </c>
+      <c r="C88" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D88" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E88" s="16">
+        <v>54.5</v>
+      </c>
+      <c r="G88" s="16">
+        <v>55</v>
+      </c>
+      <c r="H88" s="12"/>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A89" s="13">
+        <v>41730</v>
+      </c>
+      <c r="B89" s="13">
+        <v>41762</v>
+      </c>
+      <c r="C89" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D89" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E89" s="16">
+        <v>54.8</v>
+      </c>
+      <c r="G89" s="16">
+        <v>54.5</v>
+      </c>
+      <c r="H89" s="12"/>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A90" s="13">
+        <v>41760</v>
+      </c>
+      <c r="B90" s="13">
+        <v>41793</v>
+      </c>
+      <c r="C90" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D90" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E90" s="16">
+        <v>55.5</v>
+      </c>
+      <c r="G90" s="16">
+        <v>54.8</v>
+      </c>
+      <c r="H90" s="12"/>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A91" s="13">
+        <v>41791</v>
+      </c>
+      <c r="B91" s="13">
+        <v>41823</v>
+      </c>
+      <c r="C91" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D91" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E91" s="16">
+        <v>55</v>
+      </c>
+      <c r="G91" s="16">
+        <v>55.5</v>
+      </c>
+      <c r="H91" s="12"/>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A92" s="13">
+        <v>41821</v>
+      </c>
+      <c r="B92" s="13">
+        <v>41854</v>
+      </c>
+      <c r="C92" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D92" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E92" s="16">
+        <v>54.2</v>
+      </c>
+      <c r="G92" s="16">
+        <v>55</v>
+      </c>
+      <c r="H92" s="12"/>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A93" s="13">
+        <v>41852</v>
+      </c>
+      <c r="B93" s="13">
+        <v>41885</v>
+      </c>
+      <c r="C93" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D93" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E93" s="16">
+        <v>54.4</v>
+      </c>
+      <c r="G93" s="16">
+        <v>54.2</v>
+      </c>
+      <c r="H93" s="12"/>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A94" s="13">
+        <v>41883</v>
+      </c>
+      <c r="B94" s="13">
+        <v>41915</v>
+      </c>
+      <c r="C94" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D94" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E94" s="16">
+        <v>54</v>
+      </c>
+      <c r="G94" s="16">
+        <v>54.4</v>
+      </c>
+      <c r="H94" s="12"/>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A95" s="13">
+        <v>41913</v>
+      </c>
+      <c r="B95" s="13">
+        <v>41946</v>
+      </c>
+      <c r="C95" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D95" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E95" s="16">
+        <v>53.8</v>
+      </c>
+      <c r="G95" s="16">
+        <v>54</v>
+      </c>
+      <c r="H95" s="12"/>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A96" s="13">
+        <v>41944</v>
+      </c>
+      <c r="B96" s="13">
+        <v>41976</v>
+      </c>
+      <c r="C96" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D96" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E96" s="16">
+        <v>53.9</v>
+      </c>
+      <c r="G96" s="16">
+        <v>53.8</v>
+      </c>
+      <c r="H96" s="12"/>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A97" s="13">
+        <v>41974</v>
+      </c>
+      <c r="B97" s="13">
+        <v>42005</v>
+      </c>
+      <c r="C97" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D97" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E97" s="16">
+        <v>54.1</v>
+      </c>
+      <c r="G97" s="16">
+        <v>53.9</v>
+      </c>
+      <c r="H97" s="12"/>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A98" s="13">
+        <v>42005</v>
+      </c>
+      <c r="B98" s="13">
+        <v>42036</v>
+      </c>
+      <c r="C98" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D98" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E98" s="16">
+        <v>53.7</v>
+      </c>
+      <c r="G98" s="16">
+        <v>54.1</v>
+      </c>
+      <c r="H98" s="12"/>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A99" s="13">
+        <v>42036</v>
+      </c>
+      <c r="B99" s="13">
+        <v>42064</v>
+      </c>
+      <c r="C99" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D99" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E99" s="16">
+        <v>53.9</v>
+      </c>
+      <c r="G99" s="16">
+        <v>53.7</v>
+      </c>
+      <c r="H99" s="12"/>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A100" s="13">
+        <v>42064</v>
+      </c>
+      <c r="B100" s="13">
+        <v>42095</v>
+      </c>
+      <c r="C100" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D100" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E100" s="16">
+        <v>53.7</v>
+      </c>
+      <c r="G100" s="16">
+        <v>53.9</v>
+      </c>
+      <c r="H100" s="12"/>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A101" s="13">
+        <v>42095</v>
+      </c>
+      <c r="B101" s="13">
+        <v>42125</v>
+      </c>
+      <c r="C101" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D101" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E101" s="16">
+        <v>53.4</v>
+      </c>
+      <c r="G101" s="16">
+        <v>53.7</v>
+      </c>
+      <c r="H101" s="12"/>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A102" s="13">
+        <v>42125</v>
+      </c>
+      <c r="B102" s="13">
+        <v>42156</v>
+      </c>
+      <c r="C102" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D102" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E102" s="16">
+        <v>53.2</v>
+      </c>
+      <c r="G102" s="16">
+        <v>53.4</v>
+      </c>
+      <c r="H102" s="12"/>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A103" s="13">
+        <v>42156</v>
+      </c>
+      <c r="B103" s="13">
+        <v>42186</v>
+      </c>
+      <c r="C103" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D103" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E103" s="16">
+        <v>53.8</v>
+      </c>
+      <c r="G103" s="16">
+        <v>53.2</v>
+      </c>
+      <c r="H103" s="12"/>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A104" s="13">
+        <v>42186</v>
+      </c>
+      <c r="B104" s="13">
+        <v>42217</v>
+      </c>
+      <c r="C104" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D104" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E104" s="16">
+        <v>53.9</v>
+      </c>
+      <c r="G104" s="16">
+        <v>53.8</v>
+      </c>
+      <c r="H104" s="12"/>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A105" s="13">
+        <v>42217</v>
+      </c>
+      <c r="B105" s="13">
+        <v>42248</v>
+      </c>
+      <c r="C105" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D105" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E105" s="16">
+        <v>53.4</v>
+      </c>
+      <c r="G105" s="16">
+        <v>53.9</v>
+      </c>
+      <c r="H105" s="12"/>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A106" s="13">
+        <v>42248</v>
+      </c>
+      <c r="B106" s="13">
+        <v>42278</v>
+      </c>
+      <c r="C106" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D106" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E106" s="16">
+        <v>53.4</v>
+      </c>
+      <c r="G106" s="16">
+        <v>53.4</v>
+      </c>
+      <c r="H106" s="12"/>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A107" s="13">
+        <v>42278</v>
+      </c>
+      <c r="B107" s="13">
+        <v>42309</v>
+      </c>
+      <c r="C107" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D107" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E107" s="16">
+        <v>53.1</v>
+      </c>
+      <c r="G107" s="16">
+        <v>53.4</v>
+      </c>
+      <c r="H107" s="12"/>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A108" s="13">
+        <v>42309</v>
+      </c>
+      <c r="B108" s="13">
+        <v>42339</v>
+      </c>
+      <c r="C108" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D108" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E108" s="16">
+        <v>53.6</v>
+      </c>
+      <c r="G108" s="16">
+        <v>53.1</v>
+      </c>
+      <c r="H108" s="12"/>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A109" s="13">
+        <v>42339</v>
+      </c>
+      <c r="B109" s="13">
+        <v>42370</v>
+      </c>
+      <c r="C109" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D109" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E109" s="16">
+        <v>54.4</v>
+      </c>
+      <c r="G109" s="16">
+        <v>53.6</v>
+      </c>
+      <c r="H109" s="12"/>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A110" s="13">
+        <v>42370</v>
+      </c>
+      <c r="B110" s="13">
+        <v>42401</v>
+      </c>
+      <c r="C110" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D110" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E110" s="16">
+        <v>53.5</v>
+      </c>
+      <c r="G110" s="16">
+        <v>54.4</v>
+      </c>
+      <c r="H110" s="12"/>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A111" s="13">
+        <v>42401</v>
+      </c>
+      <c r="B111" s="13">
+        <v>42430</v>
+      </c>
+      <c r="C111" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D111" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E111" s="16">
+        <v>52.7</v>
+      </c>
+      <c r="G111" s="16">
+        <v>53.5</v>
+      </c>
+      <c r="H111" s="12"/>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A112" s="13">
+        <v>42430</v>
+      </c>
+      <c r="B112" s="13">
+        <v>42461</v>
+      </c>
+      <c r="C112" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D112" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E112" s="16">
+        <v>53.8</v>
+      </c>
+      <c r="G112" s="16">
+        <v>52.7</v>
+      </c>
+      <c r="H112" s="12"/>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A113" s="13">
+        <v>42461</v>
+      </c>
+      <c r="B113" s="13">
+        <v>42491</v>
+      </c>
+      <c r="C113" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D113" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E113" s="16">
+        <v>53.5</v>
+      </c>
+      <c r="G113" s="16">
+        <v>53.8</v>
+      </c>
+      <c r="H113" s="12"/>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A114" s="13">
+        <v>42491</v>
+      </c>
+      <c r="B114" s="13">
+        <v>42522</v>
+      </c>
+      <c r="C114" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D114" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E114" s="16">
+        <v>53.1</v>
+      </c>
+      <c r="G114" s="16">
+        <v>53.5</v>
+      </c>
+      <c r="H114" s="12"/>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A115" s="13">
+        <v>42522</v>
+      </c>
+      <c r="B115" s="13">
+        <v>42552</v>
+      </c>
+      <c r="C115" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D115" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E115" s="16">
+        <v>53.7</v>
+      </c>
+      <c r="G115" s="16">
+        <v>53.1</v>
+      </c>
+      <c r="H115" s="12"/>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A116" s="13">
+        <v>42552</v>
+      </c>
+      <c r="B116" s="13">
+        <v>42583</v>
+      </c>
+      <c r="C116" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D116" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E116" s="16">
+        <v>53.9</v>
+      </c>
+      <c r="G116" s="16">
+        <v>53.7</v>
+      </c>
+      <c r="H116" s="12"/>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A117" s="13">
+        <v>42583</v>
+      </c>
+      <c r="B117" s="13">
+        <v>42614</v>
+      </c>
+      <c r="C117" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D117" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E117" s="16">
+        <v>53.5</v>
+      </c>
+      <c r="G117" s="16">
+        <v>53.9</v>
+      </c>
+      <c r="H117" s="12"/>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A118" s="13">
+        <v>42614</v>
+      </c>
+      <c r="B118" s="13">
+        <v>42644</v>
+      </c>
+      <c r="C118" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D118" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E118" s="16">
+        <v>53.7</v>
+      </c>
+      <c r="G118" s="16">
+        <v>53.5</v>
+      </c>
+      <c r="H118" s="12"/>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A119" s="13">
+        <v>42644</v>
+      </c>
+      <c r="B119" s="13">
+        <v>42675</v>
+      </c>
+      <c r="C119" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D119" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E119" s="16">
+        <v>54</v>
+      </c>
+      <c r="G119" s="16">
+        <v>53.7</v>
+      </c>
+      <c r="H119" s="12"/>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A120" s="13">
+        <v>42675</v>
+      </c>
+      <c r="B120" s="13">
+        <v>42705</v>
+      </c>
+      <c r="C120" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D120" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E120" s="16">
+        <v>54.7</v>
+      </c>
+      <c r="G120" s="16">
+        <v>54</v>
+      </c>
+      <c r="H120" s="12"/>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A121" s="13">
+        <v>42705</v>
+      </c>
+      <c r="B121" s="13">
+        <v>42736</v>
+      </c>
+      <c r="C121" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D121" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E121" s="16">
+        <v>54.5</v>
+      </c>
+      <c r="G121" s="16">
+        <v>54.7</v>
+      </c>
+      <c r="H121" s="12"/>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A122" s="13">
+        <v>42736</v>
+      </c>
+      <c r="B122" s="13">
+        <v>42767</v>
+      </c>
+      <c r="C122" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D122" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E122" s="16">
+        <v>54.6</v>
+      </c>
+      <c r="G122" s="16">
+        <v>54.5</v>
+      </c>
+      <c r="H122" s="12"/>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A123" s="13">
+        <v>42767</v>
+      </c>
+      <c r="B123" s="13">
+        <v>42795</v>
+      </c>
+      <c r="C123" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D123" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E123" s="16">
+        <v>54.2</v>
+      </c>
+      <c r="G123" s="16">
+        <v>54.6</v>
+      </c>
+      <c r="H123" s="12"/>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A124" s="13">
+        <v>42795</v>
+      </c>
+      <c r="B124" s="13">
+        <v>42825</v>
+      </c>
+      <c r="C124" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D124" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E124" s="16">
+        <v>55.1</v>
+      </c>
+      <c r="G124" s="16">
+        <v>54.2</v>
+      </c>
+      <c r="H124" s="12"/>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A125" s="13">
+        <v>42826</v>
+      </c>
+      <c r="B125" s="13">
+        <v>42855</v>
+      </c>
+      <c r="C125" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D125" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E125" s="16">
+        <v>54</v>
+      </c>
+      <c r="G125" s="16">
+        <v>55.1</v>
+      </c>
+      <c r="H125" s="12"/>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A126" s="13">
+        <v>42856</v>
+      </c>
+      <c r="B126" s="13">
+        <v>42886</v>
+      </c>
+      <c r="C126" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D126" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E126" s="16">
+        <v>54.5</v>
+      </c>
+      <c r="G126" s="16">
+        <v>54</v>
+      </c>
+      <c r="H126" s="12"/>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A127" s="13">
+        <v>42887</v>
+      </c>
+      <c r="B127" s="13">
+        <v>42916</v>
+      </c>
+      <c r="C127" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D127" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E127" s="16">
+        <v>54.9</v>
+      </c>
+      <c r="G127" s="16">
+        <v>54.5</v>
+      </c>
+      <c r="H127" s="12"/>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A128" s="13">
+        <v>42917</v>
+      </c>
+      <c r="B128" s="13">
+        <v>42947</v>
+      </c>
+      <c r="C128" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D128" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E128" s="16">
+        <v>54.5</v>
+      </c>
+      <c r="G128" s="16">
+        <v>54.9</v>
+      </c>
+      <c r="H128" s="12"/>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A129" s="13">
+        <v>42948</v>
+      </c>
+      <c r="B129" s="13">
+        <v>42978</v>
+      </c>
+      <c r="C129" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D129" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E129" s="16">
+        <v>53.4</v>
+      </c>
+      <c r="G129" s="16">
+        <v>54.5</v>
+      </c>
+      <c r="H129" s="12"/>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A130" s="13">
+        <v>42979</v>
+      </c>
+      <c r="B130" s="13">
+        <v>43008</v>
+      </c>
+      <c r="C130" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D130" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E130" s="16">
+        <v>55.4</v>
+      </c>
+      <c r="G130" s="16">
+        <v>53.4</v>
+      </c>
+      <c r="H130" s="12"/>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A131" s="13">
+        <v>43009</v>
+      </c>
+      <c r="B131" s="13">
+        <v>43039</v>
+      </c>
+      <c r="C131" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D131" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E131" s="16">
+        <v>54.3</v>
+      </c>
+      <c r="G131" s="16">
+        <v>55.4</v>
+      </c>
+      <c r="H131" s="12"/>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A132" s="13">
+        <v>43040</v>
+      </c>
+      <c r="B132" s="13">
+        <v>43069</v>
+      </c>
+      <c r="C132" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D132" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E132" s="16">
+        <v>54.8</v>
+      </c>
+      <c r="G132" s="16">
+        <v>54.3</v>
+      </c>
+      <c r="H132" s="12"/>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A133" s="13">
+        <v>43070</v>
+      </c>
+      <c r="B133" s="13">
+        <v>43100</v>
+      </c>
+      <c r="C133" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D133" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E133" s="16">
+        <v>55</v>
+      </c>
+      <c r="G133" s="16">
+        <v>54.8</v>
+      </c>
+      <c r="H133" s="12"/>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A134" s="13">
+        <v>43101</v>
+      </c>
+      <c r="B134" s="13">
+        <v>43131</v>
+      </c>
+      <c r="C134" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D134" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E134" s="16">
+        <v>55.3</v>
+      </c>
+      <c r="F134" s="16">
+        <v>55</v>
+      </c>
+      <c r="G134" s="16">
+        <v>55</v>
+      </c>
+      <c r="H134" s="12"/>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A135" s="13">
+        <v>43132</v>
+      </c>
+      <c r="B135" s="13">
+        <v>43159</v>
+      </c>
+      <c r="C135" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D135" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E135" s="16">
+        <v>54.4</v>
+      </c>
+      <c r="F135" s="16">
+        <v>55</v>
+      </c>
+      <c r="G135" s="16">
+        <v>55.3</v>
+      </c>
+      <c r="H135" s="12"/>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A136" s="13">
+        <v>43160</v>
+      </c>
+      <c r="B136" s="13">
+        <v>43190</v>
+      </c>
+      <c r="C136" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D136" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E136" s="16">
+        <v>54.6</v>
+      </c>
+      <c r="G136" s="16">
+        <v>54.4</v>
+      </c>
+      <c r="H136" s="12"/>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A137" s="13">
+        <v>43191</v>
+      </c>
+      <c r="B137" s="13">
+        <v>43220</v>
+      </c>
+      <c r="C137" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D137" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E137" s="16">
+        <v>54.8</v>
+      </c>
+      <c r="F137" s="16">
+        <v>54.6</v>
+      </c>
+      <c r="G137" s="16">
+        <v>54.6</v>
+      </c>
+      <c r="H137" s="12"/>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A138" s="13">
+        <v>43221</v>
+      </c>
+      <c r="B138" s="13">
+        <v>43251</v>
+      </c>
+      <c r="C138" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D138" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E138" s="16">
+        <v>54.9</v>
+      </c>
+      <c r="F138" s="16">
+        <v>54.8</v>
+      </c>
+      <c r="G138" s="16">
+        <v>54.8</v>
+      </c>
+      <c r="H138" s="12"/>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A139" s="13">
+        <v>43252</v>
+      </c>
+      <c r="B139" s="13">
+        <v>43281</v>
+      </c>
+      <c r="C139" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D139" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E139" s="16">
+        <v>55</v>
+      </c>
+      <c r="F139" s="16">
+        <v>54.7</v>
+      </c>
+      <c r="G139" s="16">
+        <v>54.9</v>
+      </c>
+      <c r="H139" s="12"/>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A140" s="13">
+        <v>43282</v>
+      </c>
+      <c r="B140" s="13">
+        <v>43312</v>
+      </c>
+      <c r="C140" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D140" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E140" s="16">
+        <v>54</v>
+      </c>
+      <c r="F140" s="16">
+        <v>55</v>
+      </c>
+      <c r="G140" s="16">
+        <v>55</v>
+      </c>
+      <c r="H140" s="12"/>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A141" s="13">
+        <v>43313</v>
+      </c>
+      <c r="B141" s="13">
+        <v>43343</v>
+      </c>
+      <c r="C141" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D141" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E141" s="16">
+        <v>54.2</v>
+      </c>
+      <c r="F141" s="16">
+        <v>53.8</v>
+      </c>
+      <c r="G141" s="16">
+        <v>54</v>
+      </c>
+      <c r="H141" s="12"/>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A142" s="13">
+        <v>43344</v>
+      </c>
+      <c r="B142" s="13">
+        <v>43373</v>
+      </c>
+      <c r="C142" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D142" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E142" s="16">
+        <v>54.9</v>
+      </c>
+      <c r="G142" s="16">
+        <v>54.2</v>
+      </c>
+      <c r="H142" s="12"/>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A143" s="13">
+        <v>43374</v>
+      </c>
+      <c r="B143" s="13">
+        <v>43404</v>
+      </c>
+      <c r="C143" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D143" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E143" s="16">
+        <v>53.9</v>
+      </c>
+      <c r="F143" s="16">
+        <v>54.9</v>
+      </c>
+      <c r="G143" s="16">
+        <v>54.9</v>
+      </c>
+      <c r="H143" s="12"/>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A144" s="13">
+        <v>43405</v>
+      </c>
+      <c r="B144" s="13">
+        <v>43434</v>
+      </c>
+      <c r="C144" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D144" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E144" s="16">
+        <v>53.4</v>
+      </c>
+      <c r="F144" s="16">
+        <v>53.8</v>
+      </c>
+      <c r="G144" s="16">
+        <v>53.9</v>
+      </c>
+      <c r="H144" s="12"/>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A145" s="13">
+        <v>43435</v>
+      </c>
+      <c r="B145" s="13">
+        <v>43465</v>
+      </c>
+      <c r="C145" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D145" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E145" s="16">
+        <v>53.8</v>
+      </c>
+      <c r="F145" s="16">
+        <v>53.2</v>
+      </c>
+      <c r="G145" s="16">
+        <v>53.4</v>
+      </c>
+      <c r="H145" s="12"/>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A146" s="13">
+        <v>43466</v>
+      </c>
+      <c r="B146" s="13">
+        <v>43496</v>
+      </c>
+      <c r="C146" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D146" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E146" s="16">
+        <v>54.7</v>
+      </c>
+      <c r="F146" s="16">
+        <v>53.9</v>
+      </c>
+      <c r="G146" s="16">
+        <v>53.8</v>
+      </c>
+      <c r="H146" s="12"/>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A147" s="13">
+        <v>43497</v>
+      </c>
+      <c r="B147" s="13">
+        <v>43524</v>
+      </c>
+      <c r="C147" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D147" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E147" s="16">
+        <v>54.3</v>
+      </c>
+      <c r="F147" s="16">
+        <v>54.5</v>
+      </c>
+      <c r="G147" s="16">
+        <v>54.7</v>
+      </c>
+      <c r="H147" s="12"/>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A148" s="13">
+        <v>43525</v>
+      </c>
+      <c r="B148" s="13">
+        <v>43555</v>
+      </c>
+      <c r="C148" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D148" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E148" s="16">
+        <v>54.8</v>
+      </c>
+      <c r="F148" s="16">
+        <v>54.5</v>
+      </c>
+      <c r="G148" s="16">
+        <v>54.3</v>
+      </c>
+      <c r="H148" s="12"/>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A149" s="13">
+        <v>43556</v>
+      </c>
+      <c r="B149" s="13">
+        <v>43585</v>
+      </c>
+      <c r="C149" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D149" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E149" s="16">
+        <v>54.3</v>
+      </c>
+      <c r="F149" s="16">
+        <v>55</v>
+      </c>
+      <c r="G149" s="16">
+        <v>54.8</v>
+      </c>
+      <c r="H149" s="12"/>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A150" s="13">
+        <v>43586</v>
+      </c>
+      <c r="B150" s="13">
+        <v>43616</v>
+      </c>
+      <c r="C150" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D150" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E150" s="16">
+        <v>54.3</v>
+      </c>
+      <c r="F150" s="16">
+        <v>54.3</v>
+      </c>
+      <c r="G150" s="16">
+        <v>54.3</v>
+      </c>
+      <c r="H150" s="12"/>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A151" s="13">
+        <v>43617</v>
+      </c>
+      <c r="B151" s="13">
+        <v>43646</v>
+      </c>
+      <c r="C151" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D151" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E151" s="16">
+        <v>54.2</v>
+      </c>
+      <c r="F151" s="16">
+        <v>54.1</v>
+      </c>
+      <c r="G151" s="16">
+        <v>54.3</v>
+      </c>
+      <c r="H151" s="12"/>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A152" s="13">
+        <v>43647</v>
+      </c>
+      <c r="B152" s="13">
+        <v>43677</v>
+      </c>
+      <c r="C152" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D152" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E152" s="16">
+        <v>53.7</v>
+      </c>
+      <c r="F152" s="16">
+        <v>54</v>
+      </c>
+      <c r="G152" s="16">
+        <v>54.2</v>
+      </c>
+      <c r="H152" s="12"/>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A153" s="13">
+        <v>43678</v>
+      </c>
+      <c r="B153" s="13">
+        <v>43708</v>
+      </c>
+      <c r="C153" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D153" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E153" s="16">
+        <v>53.8</v>
+      </c>
+      <c r="F153" s="16">
+        <v>53.6</v>
+      </c>
+      <c r="G153" s="16">
+        <v>53.7</v>
+      </c>
+      <c r="H153" s="12"/>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A154" s="13">
+        <v>43709</v>
+      </c>
+      <c r="B154" s="13">
+        <v>43738</v>
+      </c>
+      <c r="C154" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D154" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E154" s="16">
+        <v>53.7</v>
+      </c>
+      <c r="F154" s="16">
+        <v>54.2</v>
+      </c>
+      <c r="G154" s="16">
+        <v>53.8</v>
+      </c>
+      <c r="H154" s="12"/>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A155" s="13">
+        <v>43739</v>
+      </c>
+      <c r="B155" s="13">
+        <v>43769</v>
+      </c>
+      <c r="C155" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D155" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E155" s="16">
+        <v>52.8</v>
+      </c>
+      <c r="F155" s="16">
+        <v>53.7</v>
+      </c>
+      <c r="G155" s="16">
+        <v>53.7</v>
+      </c>
+      <c r="H155" s="12"/>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A156" s="13">
+        <v>43770</v>
+      </c>
+      <c r="B156" s="13">
+        <v>43799</v>
+      </c>
+      <c r="C156" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D156" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E156" s="16">
+        <v>54.4</v>
+      </c>
+      <c r="G156" s="16">
+        <v>52.8</v>
+      </c>
+      <c r="H156" s="12"/>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A157" s="13">
+        <v>43800</v>
+      </c>
+      <c r="B157" s="13">
+        <v>43830</v>
+      </c>
+      <c r="C157" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D157" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E157" s="16">
+        <v>53.5</v>
+      </c>
+      <c r="G157" s="16">
+        <v>54.4</v>
+      </c>
+      <c r="H157" s="12"/>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A158" s="13">
+        <v>43831</v>
+      </c>
+      <c r="B158" s="13">
+        <v>43861</v>
+      </c>
+      <c r="C158" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D158" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E158" s="16">
+        <v>54.1</v>
+      </c>
+      <c r="G158" s="16">
+        <v>53.5</v>
+      </c>
+      <c r="H158" s="12"/>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A159" s="13">
+        <v>43862</v>
+      </c>
+      <c r="B159" s="13">
+        <v>43890</v>
+      </c>
+      <c r="C159" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D159" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E159" s="16">
+        <v>29.6</v>
+      </c>
+      <c r="G159" s="16">
+        <v>54.1</v>
+      </c>
+      <c r="H159" s="12"/>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A160" s="13">
+        <v>43891</v>
+      </c>
+      <c r="B160" s="13">
+        <v>43921</v>
+      </c>
+      <c r="C160" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D160" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E160" s="16">
+        <v>52.3</v>
+      </c>
+      <c r="G160" s="16">
+        <v>29.6</v>
+      </c>
+      <c r="H160" s="12"/>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A161" s="13">
+        <v>43922</v>
+      </c>
+      <c r="B161" s="13">
+        <v>43951</v>
+      </c>
+      <c r="C161" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D161" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E161" s="16">
+        <v>53.2</v>
+      </c>
+      <c r="G161" s="16">
+        <v>52.3</v>
+      </c>
+      <c r="H161" s="12"/>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A162" s="13">
+        <v>43952</v>
+      </c>
+      <c r="B162" s="13">
+        <v>43982</v>
+      </c>
+      <c r="C162" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D162" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E162" s="16">
+        <v>53.6</v>
+      </c>
+      <c r="G162" s="16">
+        <v>53.2</v>
+      </c>
+      <c r="H162" s="12"/>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A163" s="13">
+        <v>43983</v>
+      </c>
+      <c r="B163" s="13">
+        <v>44012</v>
+      </c>
+      <c r="C163" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D163" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E163" s="16">
+        <v>54.4</v>
+      </c>
+      <c r="G163" s="16">
+        <v>53.6</v>
+      </c>
+      <c r="H163" s="12"/>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A164" s="13">
+        <v>44013</v>
+      </c>
+      <c r="B164" s="13">
+        <v>44043</v>
+      </c>
+      <c r="C164" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D164" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E164" s="16">
+        <v>54.2</v>
+      </c>
+      <c r="G164" s="16">
+        <v>54.4</v>
+      </c>
+      <c r="H164" s="12"/>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A165" s="13">
+        <v>44044</v>
+      </c>
+      <c r="B165" s="13">
+        <v>44074</v>
+      </c>
+      <c r="C165" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D165" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E165" s="16">
+        <v>55.2</v>
+      </c>
+      <c r="G165" s="16">
+        <v>54.2</v>
+      </c>
+      <c r="H165" s="12"/>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A166" s="13">
+        <v>44075</v>
+      </c>
+      <c r="B166" s="13">
+        <v>44104</v>
+      </c>
+      <c r="C166" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D166" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E166" s="16">
+        <v>55.9</v>
+      </c>
+      <c r="G166" s="16">
+        <v>55.2</v>
+      </c>
+      <c r="H166" s="12"/>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A167" s="13">
+        <v>44105</v>
+      </c>
+      <c r="B167" s="13">
+        <v>44135</v>
+      </c>
+      <c r="C167" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D167" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E167" s="16">
+        <v>56.2</v>
+      </c>
+      <c r="G167" s="16">
+        <v>55.9</v>
+      </c>
+      <c r="H167" s="12"/>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A168" s="13">
+        <v>44136</v>
+      </c>
+      <c r="B168" s="13">
+        <v>44165</v>
+      </c>
+      <c r="C168" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D168" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E168" s="16">
+        <v>56.4</v>
+      </c>
+      <c r="F168" s="16">
+        <v>56</v>
+      </c>
+      <c r="G168" s="16">
+        <v>56.2</v>
+      </c>
+      <c r="H168" s="12"/>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A169" s="13">
+        <v>44166</v>
+      </c>
+      <c r="B169" s="13">
+        <v>44196</v>
+      </c>
+      <c r="C169" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D169" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E169" s="16">
+        <v>55.7</v>
+      </c>
+      <c r="G169" s="16">
+        <v>56.4</v>
+      </c>
+      <c r="H169" s="12"/>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A170" s="13">
+        <v>44197</v>
+      </c>
+      <c r="B170" s="13">
+        <v>44227</v>
+      </c>
+      <c r="C170" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D170" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E170" s="16">
+        <v>52.4</v>
+      </c>
+      <c r="G170" s="16">
+        <v>55.7</v>
+      </c>
+      <c r="H170" s="12"/>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A171" s="13">
+        <v>44228</v>
+      </c>
+      <c r="B171" s="13">
+        <v>44255</v>
+      </c>
+      <c r="C171" s="18">
+        <v>0.625</v>
+      </c>
+      <c r="D171" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E171" s="16">
+        <v>51.4</v>
+      </c>
+      <c r="G171" s="16">
+        <v>52.4</v>
+      </c>
+      <c r="H171" s="12"/>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A172" s="13">
+        <v>44256</v>
+      </c>
+      <c r="B172" s="13">
+        <v>44286</v>
+      </c>
+      <c r="C172" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D172" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E172" s="16">
+        <v>56.3</v>
+      </c>
+      <c r="G172" s="16">
+        <v>51.4</v>
+      </c>
+      <c r="H172" s="12"/>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A173" s="13">
+        <v>44287</v>
+      </c>
+      <c r="B173" s="13">
+        <v>44316</v>
+      </c>
+      <c r="C173" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D173" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E173" s="16">
+        <v>54.9</v>
+      </c>
+      <c r="G173" s="16">
+        <v>56.3</v>
+      </c>
+      <c r="H173" s="12"/>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A174" s="13">
+        <v>44317</v>
+      </c>
+      <c r="B174" s="13">
+        <v>44347</v>
+      </c>
+      <c r="C174" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D174" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E174" s="16">
+        <v>55.2</v>
+      </c>
+      <c r="G174" s="16">
+        <v>54.9</v>
+      </c>
+      <c r="H174" s="12"/>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A175" s="13">
+        <v>44348</v>
+      </c>
+      <c r="B175" s="13">
+        <v>44377</v>
+      </c>
+      <c r="C175" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D175" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E175" s="16">
+        <v>53.5</v>
+      </c>
+      <c r="G175" s="16">
+        <v>55.2</v>
+      </c>
+      <c r="H175" s="12"/>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A176" s="13">
+        <v>44378</v>
+      </c>
+      <c r="B176" s="13">
+        <v>44408</v>
+      </c>
+      <c r="C176" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D176" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E176" s="16">
+        <v>53.3</v>
+      </c>
+      <c r="G176" s="16">
+        <v>53.5</v>
+      </c>
+      <c r="H176" s="12"/>
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A177" s="13">
+        <v>44409</v>
+      </c>
+      <c r="B177" s="13">
+        <v>44439</v>
+      </c>
+      <c r="C177" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D177" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E177" s="16">
+        <v>47.5</v>
+      </c>
+      <c r="G177" s="16">
+        <v>53.3</v>
+      </c>
+      <c r="H177" s="12"/>
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A178" s="13">
+        <v>44440</v>
+      </c>
+      <c r="B178" s="13">
+        <v>44469</v>
+      </c>
+      <c r="C178" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D178" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E178" s="16">
+        <v>53.2</v>
+      </c>
+      <c r="G178" s="16">
+        <v>47.5</v>
+      </c>
+      <c r="H178" s="12"/>
+    </row>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A179" s="13">
+        <v>44470</v>
+      </c>
+      <c r="B179" s="13">
+        <v>44500</v>
+      </c>
+      <c r="C179" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D179" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E179" s="16">
+        <v>52.4</v>
+      </c>
+      <c r="G179" s="16">
+        <v>53.2</v>
+      </c>
+      <c r="H179" s="12"/>
+    </row>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A180" s="13">
+        <v>44501</v>
+      </c>
+      <c r="B180" s="13">
+        <v>44530</v>
+      </c>
+      <c r="C180" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D180" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E180" s="16">
+        <v>52.3</v>
+      </c>
+      <c r="G180" s="16">
+        <v>52.4</v>
+      </c>
+      <c r="H180" s="12"/>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A181" s="13">
+        <v>44531</v>
+      </c>
+      <c r="B181" s="13">
+        <v>44561</v>
+      </c>
+      <c r="C181" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="D181" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E181" s="16">
+        <v>52.7</v>
+      </c>
+      <c r="F181" s="16">
+        <v>52</v>
+      </c>
+      <c r="G181" s="16">
+        <v>52.3</v>
+      </c>
+      <c r="H181" s="12"/>
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A182" s="13">
+        <v>44562</v>
+      </c>
+      <c r="B182" s="13">
+        <v>44591</v>
+      </c>
+      <c r="C182" s="18">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D182" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E182" s="16">
+        <v>51.1</v>
+      </c>
+      <c r="G182" s="16">
+        <v>52.7</v>
+      </c>
+      <c r="H182" s="12"/>
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A183" s="13">
+        <v>44593</v>
+      </c>
+      <c r="B183" s="13">
+        <v>44621</v>
+      </c>
+      <c r="C183" s="18">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D183" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E183" s="16">
+        <v>51.6</v>
+      </c>
+      <c r="G183" s="16">
+        <v>51.1</v>
+      </c>
+      <c r="H183" s="12"/>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A184" s="13">
+        <v>44621</v>
+      </c>
+      <c r="B184" s="13">
+        <v>44651</v>
+      </c>
+      <c r="C184" s="18">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D184" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E184" s="16">
+        <v>48.4</v>
+      </c>
+      <c r="G184" s="16">
+        <v>51.6</v>
+      </c>
+      <c r="H184" s="12"/>
+    </row>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A185" s="13">
+        <v>44652</v>
+      </c>
+      <c r="B185" s="13">
+        <v>44681</v>
+      </c>
+      <c r="C185" s="18">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D185" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E185" s="16">
+        <v>41.9</v>
+      </c>
+      <c r="G185" s="16">
+        <v>48.4</v>
+      </c>
+      <c r="H185" s="12"/>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A186" s="13">
+        <v>44682</v>
+      </c>
+      <c r="B186" s="13">
+        <v>44712</v>
+      </c>
+      <c r="C186" s="18">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D186" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E186" s="16">
+        <v>47.8</v>
+      </c>
+      <c r="G186" s="16">
+        <v>41.9</v>
+      </c>
+      <c r="H186" s="12"/>
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A187" s="13">
+        <v>44713</v>
+      </c>
+      <c r="B187" s="13">
+        <v>44742</v>
+      </c>
+      <c r="C187" s="18">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D187" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E187" s="16">
+        <v>54.7</v>
+      </c>
+      <c r="G187" s="16">
+        <v>47.8</v>
+      </c>
+      <c r="H187" s="12"/>
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A188" s="13">
+        <v>44743</v>
+      </c>
+      <c r="B188" s="13">
+        <v>44773</v>
+      </c>
+      <c r="C188" s="18">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D188" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E188" s="16">
+        <v>53.8</v>
+      </c>
+      <c r="F188" s="16">
+        <v>53.9</v>
+      </c>
+      <c r="G188" s="16">
+        <v>54.7</v>
+      </c>
+      <c r="H188" s="12"/>
+    </row>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A189" s="13">
+        <v>44774</v>
+      </c>
+      <c r="B189" s="13">
+        <v>44804</v>
+      </c>
+      <c r="C189" s="18">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D189" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E189" s="16">
+        <v>52.6</v>
+      </c>
+      <c r="G189" s="16">
+        <v>53.8</v>
+      </c>
+      <c r="H189" s="12"/>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A190" s="13">
+        <v>44805</v>
+      </c>
+      <c r="B190" s="13">
+        <v>44834</v>
+      </c>
+      <c r="C190" s="18">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D190" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E190" s="16">
+        <v>50.6</v>
+      </c>
+      <c r="G190" s="16">
+        <v>52.6</v>
+      </c>
+      <c r="H190" s="12"/>
+    </row>
+    <row r="191" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A191" s="13">
+        <v>44835</v>
+      </c>
+      <c r="B191" s="13">
+        <v>44865</v>
+      </c>
+      <c r="C191" s="18">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D191" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E191" s="16">
+        <v>48.7</v>
+      </c>
+      <c r="F191" s="16">
+        <v>50.2</v>
+      </c>
+      <c r="G191" s="16">
+        <v>50.6</v>
+      </c>
+      <c r="H191" s="12"/>
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A192" s="13">
+        <v>44866</v>
+      </c>
+      <c r="B192" s="13">
+        <v>44895</v>
+      </c>
+      <c r="C192" s="18">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D192" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E192" s="16">
+        <v>46.7</v>
+      </c>
+      <c r="F192" s="16">
+        <v>48</v>
+      </c>
+      <c r="G192" s="16">
+        <v>48.7</v>
+      </c>
+      <c r="H192" s="12"/>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A193" s="13">
+        <v>44896</v>
+      </c>
+      <c r="B193" s="13">
+        <v>44926</v>
+      </c>
+      <c r="C193" s="18">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D193" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E193" s="16">
+        <v>41.6</v>
+      </c>
+      <c r="G193" s="16">
+        <v>46.7</v>
+      </c>
+      <c r="H193" s="12"/>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A194" s="13">
+        <v>44927</v>
+      </c>
+      <c r="B194" s="13">
+        <v>44957</v>
+      </c>
+      <c r="C194" s="18">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D194" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E194" s="16">
+        <v>54.4</v>
+      </c>
+      <c r="F194" s="16">
+        <v>52</v>
+      </c>
+      <c r="G194" s="16">
+        <v>41.6</v>
+      </c>
+      <c r="H194" s="12"/>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A195" s="13">
+        <v>44958</v>
+      </c>
+      <c r="B195" s="13">
+        <v>44986</v>
+      </c>
+      <c r="C195" s="18">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D195" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E195" s="16">
+        <v>56.3</v>
+      </c>
+      <c r="F195" s="16">
+        <v>55</v>
+      </c>
+      <c r="G195" s="16">
+        <v>54.4</v>
+      </c>
+      <c r="H195" s="12"/>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A196" s="13">
+        <v>44986</v>
+      </c>
+      <c r="B196" s="13">
+        <v>45016</v>
+      </c>
+      <c r="C196" s="18">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D196" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E196" s="16">
+        <v>58.2</v>
+      </c>
+      <c r="F196" s="16">
+        <v>54.3</v>
+      </c>
+      <c r="G196" s="16">
+        <v>56.3</v>
+      </c>
+      <c r="H196" s="12"/>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A197" s="13">
+        <v>45017</v>
+      </c>
+      <c r="B197" s="13">
+        <v>45046</v>
+      </c>
+      <c r="C197" s="18">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D197" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E197" s="16">
+        <v>56.4</v>
+      </c>
+      <c r="F197" s="16">
+        <v>57</v>
+      </c>
+      <c r="G197" s="16">
+        <v>58.2</v>
+      </c>
+      <c r="H197" s="12"/>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A198" s="13">
+        <v>45047</v>
+      </c>
+      <c r="B198" s="13">
+        <v>45077</v>
+      </c>
+      <c r="C198" s="18">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D198" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E198" s="16">
+        <v>54.5</v>
+      </c>
+      <c r="F198" s="16">
+        <v>54.9</v>
+      </c>
+      <c r="G198" s="16">
+        <v>56.4</v>
+      </c>
+      <c r="H198" s="12"/>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A199" s="13">
+        <v>45078</v>
+      </c>
+      <c r="B199" s="13">
+        <v>45107</v>
+      </c>
+      <c r="C199" s="18">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D199" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E199" s="16">
+        <v>53.2</v>
+      </c>
+      <c r="F199" s="16">
+        <v>53.7</v>
+      </c>
+      <c r="G199" s="16">
+        <v>54.5</v>
+      </c>
+      <c r="H199" s="12"/>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A200" s="13">
+        <v>45108</v>
+      </c>
+      <c r="B200" s="13">
+        <v>45138</v>
+      </c>
+      <c r="C200" s="18">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D200" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E200" s="16">
+        <v>51.5</v>
+      </c>
+      <c r="F200" s="16">
+        <v>52.9</v>
+      </c>
+      <c r="G200" s="16">
+        <v>53.2</v>
+      </c>
+      <c r="H200" s="12"/>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A201" s="13">
+        <v>45139</v>
+      </c>
+      <c r="B201" s="13">
+        <v>45169</v>
+      </c>
+      <c r="C201" s="18">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D201" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E201" s="16">
+        <v>51</v>
+      </c>
+      <c r="F201" s="16">
+        <v>51.1</v>
+      </c>
+      <c r="G201" s="16">
+        <v>51.5</v>
+      </c>
+      <c r="H201" s="12"/>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A202" s="13">
+        <v>45170</v>
+      </c>
+      <c r="B202" s="13">
+        <v>45199</v>
+      </c>
+      <c r="C202" s="18">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D202" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E202" s="16">
+        <v>51.7</v>
+      </c>
+      <c r="F202" s="16">
+        <v>51.5</v>
+      </c>
+      <c r="G202" s="16">
+        <v>51</v>
+      </c>
+      <c r="H202" s="12"/>
+    </row>
+    <row r="203" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A203" s="13">
+        <v>45200</v>
+      </c>
+      <c r="B203" s="13">
+        <v>45230</v>
+      </c>
+      <c r="C203" s="18">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D203" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E203" s="16">
+        <v>50.6</v>
+      </c>
+      <c r="F203" s="16">
+        <v>51.8</v>
+      </c>
+      <c r="G203" s="16">
+        <v>51.7</v>
+      </c>
+      <c r="H203" s="12"/>
+    </row>
+    <row r="204" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A204" s="13">
+        <v>45231</v>
+      </c>
+      <c r="B204" s="13">
+        <v>45260</v>
+      </c>
+      <c r="C204" s="18">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D204" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E204" s="16">
+        <v>50.2</v>
+      </c>
+      <c r="F204" s="16">
+        <v>51.1</v>
+      </c>
+      <c r="G204" s="16">
+        <v>50.6</v>
+      </c>
+      <c r="H204" s="12"/>
+    </row>
+    <row r="205" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A205" s="13">
+        <v>45261</v>
+      </c>
+      <c r="B205" s="13">
+        <v>45291</v>
+      </c>
+      <c r="C205" s="18">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D205" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E205" s="16">
+        <v>50.4</v>
+      </c>
+      <c r="F205" s="16">
+        <v>50.5</v>
+      </c>
+      <c r="G205" s="16">
+        <v>50.2</v>
+      </c>
+      <c r="H205" s="12"/>
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A206" s="13">
+        <v>45292</v>
+      </c>
+      <c r="B206" s="13">
+        <v>45322</v>
+      </c>
+      <c r="C206" s="18">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D206" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E206" s="16">
+        <v>50.7</v>
+      </c>
+      <c r="F206" s="16">
+        <v>50.6</v>
+      </c>
+      <c r="G206" s="16">
+        <v>50.4</v>
+      </c>
+      <c r="H206" s="12"/>
+    </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A207" s="13">
+        <v>45323</v>
+      </c>
+      <c r="B207" s="13">
+        <v>45352</v>
+      </c>
+      <c r="C207" s="18">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D207" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E207" s="16">
+        <v>51.4</v>
+      </c>
+      <c r="F207" s="16">
+        <v>50.9</v>
+      </c>
+      <c r="G207" s="16">
+        <v>50.7</v>
+      </c>
+      <c r="H207" s="12"/>
+    </row>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A208" s="13">
+        <v>45352</v>
+      </c>
+      <c r="B208" s="13">
+        <v>45382</v>
+      </c>
+      <c r="C208" s="18">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D208" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E208" s="16">
+        <v>53</v>
+      </c>
+      <c r="F208" s="16">
+        <v>51.3</v>
+      </c>
+      <c r="G208" s="16">
+        <v>51.4</v>
+      </c>
+      <c r="H208" s="12"/>
+    </row>
+    <row r="209" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A209" s="13">
+        <v>45383</v>
+      </c>
+      <c r="B209" s="13">
+        <v>45412</v>
+      </c>
+      <c r="C209" s="18">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D209" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E209" s="16">
+        <v>51.2</v>
+      </c>
+      <c r="F209" s="16">
+        <v>52.3</v>
+      </c>
+      <c r="G209" s="16">
+        <v>53</v>
+      </c>
+      <c r="H209" s="12"/>
+    </row>
+    <row r="210" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A210" s="13">
+        <v>45413</v>
+      </c>
+      <c r="B210" s="13">
+        <v>45443</v>
+      </c>
+      <c r="C210" s="18">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D210" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E210" s="16">
+        <v>51.1</v>
+      </c>
+      <c r="F210" s="16">
+        <v>51.5</v>
+      </c>
+      <c r="G210" s="16">
+        <v>51.2</v>
+      </c>
+      <c r="H210" s="12"/>
+    </row>
+    <row r="211" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A211" s="13">
+        <v>45444</v>
+      </c>
+      <c r="B211" s="13">
+        <v>45473</v>
+      </c>
+      <c r="C211" s="18">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D211" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E211" s="16">
+        <v>50.5</v>
+      </c>
+      <c r="F211" s="16">
+        <v>51.1</v>
+      </c>
+      <c r="G211" s="16">
+        <v>51.1</v>
+      </c>
+      <c r="H211" s="12"/>
+    </row>
+    <row r="212" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A212" s="13">
+        <v>45474</v>
+      </c>
+      <c r="B212" s="13">
+        <v>45504</v>
+      </c>
+      <c r="C212" s="18">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D212" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E212" s="16">
+        <v>50.2</v>
+      </c>
+      <c r="F212" s="16">
+        <v>50.3</v>
+      </c>
+      <c r="G212" s="16">
+        <v>50.5</v>
+      </c>
+      <c r="H212" s="12"/>
+    </row>
+    <row r="213" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A213" s="13">
+        <v>45505</v>
+      </c>
+      <c r="B213" s="13">
+        <v>45535</v>
+      </c>
+      <c r="C213" s="18">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D213" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E213" s="16">
+        <v>50.3</v>
+      </c>
+      <c r="F213" s="16">
+        <v>50</v>
+      </c>
+      <c r="G213" s="16">
+        <v>50.2</v>
+      </c>
+      <c r="H213" s="12"/>
+    </row>
+    <row r="214" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A214" s="13">
+        <v>45536</v>
+      </c>
+      <c r="B214" s="13">
+        <v>45565</v>
+      </c>
+      <c r="C214" s="18">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D214" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E214" s="16">
+        <v>50</v>
+      </c>
+      <c r="F214" s="16">
+        <v>50.4</v>
+      </c>
+      <c r="G214" s="16">
+        <v>50.3</v>
+      </c>
+      <c r="H214" s="12"/>
+    </row>
+    <row r="215" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A215" s="13">
+        <v>45566</v>
+      </c>
+      <c r="B215" s="13">
+        <v>45596</v>
+      </c>
+      <c r="C215" s="18">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D215" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E215" s="16">
+        <v>50.2</v>
+      </c>
+      <c r="F215" s="16">
+        <v>50.4</v>
+      </c>
+      <c r="G215" s="16">
+        <v>50</v>
+      </c>
+      <c r="H215" s="12"/>
+    </row>
+    <row r="216" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A216" s="13">
+        <v>45597</v>
+      </c>
+      <c r="B216" s="13">
+        <v>45626</v>
+      </c>
+      <c r="C216" s="18">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D216" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E216" s="16">
+        <v>50</v>
+      </c>
+      <c r="F216" s="16">
+        <v>50.4</v>
+      </c>
+      <c r="G216" s="16">
+        <v>50.2</v>
+      </c>
+      <c r="H216" s="12"/>
+    </row>
+    <row r="217" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A217" s="13">
+        <v>45627</v>
+      </c>
+      <c r="B217" s="13">
+        <v>45657</v>
+      </c>
+      <c r="C217" s="18">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D217" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E217" s="16">
+        <v>52.2</v>
+      </c>
+      <c r="F217" s="16">
+        <v>50.2</v>
+      </c>
+      <c r="G217" s="16">
+        <v>50</v>
+      </c>
+      <c r="H217" s="12"/>
+    </row>
+    <row r="218" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A218" s="13">
+        <v>45658</v>
+      </c>
+      <c r="B218" s="13">
+        <v>45684</v>
+      </c>
+      <c r="C218" s="18">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D218" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E218" s="16">
+        <v>50.2</v>
+      </c>
+      <c r="G218" s="16">
+        <v>52.2</v>
+      </c>
+      <c r="H218" s="12"/>
+    </row>
+    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A219" s="13">
+        <v>45689</v>
+      </c>
+      <c r="B219" s="13">
+        <v>45717</v>
+      </c>
+      <c r="C219" s="18">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D219" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E219" s="16">
+        <v>50.4</v>
+      </c>
+      <c r="F219" s="16">
+        <v>50.3</v>
+      </c>
+      <c r="G219" s="16">
+        <v>50.2</v>
+      </c>
+      <c r="H219" s="12"/>
+    </row>
+    <row r="220" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A220" s="13">
+        <v>45717</v>
+      </c>
+      <c r="B220" s="13">
+        <v>45747</v>
+      </c>
+      <c r="C220" s="18">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D220" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E220" s="16">
+        <v>50.8</v>
+      </c>
+      <c r="F220" s="16">
+        <v>50.5</v>
+      </c>
+      <c r="G220" s="16">
+        <v>50.4</v>
+      </c>
+      <c r="H220" s="12"/>
+    </row>
+    <row r="221" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A221" s="13">
+        <v>45748</v>
+      </c>
+      <c r="B221" s="13">
+        <v>45777</v>
+      </c>
+      <c r="C221" s="18">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D221" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E221" s="16">
+        <v>50.4</v>
+      </c>
+      <c r="F221" s="16">
+        <v>50.6</v>
+      </c>
+      <c r="G221" s="16">
+        <v>50.8</v>
+      </c>
+      <c r="H221" s="12"/>
+    </row>
+    <row r="222" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A222" s="13">
+        <v>45778</v>
+      </c>
+      <c r="B222" s="13">
+        <v>45808</v>
+      </c>
+      <c r="C222" s="18">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D222" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E222" s="16">
+        <v>50.3</v>
+      </c>
+      <c r="F222" s="16">
+        <v>50.6</v>
+      </c>
+      <c r="G222" s="16">
+        <v>50.4</v>
+      </c>
+      <c r="H222" s="12"/>
+    </row>
+    <row r="223" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A223" s="13">
+        <v>45809</v>
+      </c>
+      <c r="B223" s="13">
+        <v>45838</v>
+      </c>
+      <c r="C223" s="18">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D223" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E223" s="16">
+        <v>50.5</v>
+      </c>
+      <c r="F223" s="16">
+        <v>50.3</v>
+      </c>
+      <c r="G223" s="16">
+        <v>50.3</v>
+      </c>
+      <c r="H223" s="12"/>
+    </row>
+    <row r="224" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A224" s="13">
+        <v>45839</v>
+      </c>
+      <c r="B224" s="13">
+        <v>45869</v>
+      </c>
+      <c r="C224" s="18">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D224" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E224" s="16">
+        <v>50.1</v>
+      </c>
+      <c r="F224" s="16">
+        <v>50.3</v>
+      </c>
+      <c r="G224" s="16">
+        <v>50.5</v>
+      </c>
+      <c r="H224" s="12"/>
+    </row>
+    <row r="225" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A225" s="13">
+        <v>45870</v>
+      </c>
+      <c r="B225" s="13">
+        <v>45900</v>
+      </c>
+      <c r="C225" s="18">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D225" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E225" s="16">
+        <v>50.3</v>
+      </c>
+      <c r="F225" s="16">
+        <v>50.3</v>
+      </c>
+      <c r="G225" s="16">
+        <v>50.1</v>
+      </c>
+      <c r="H225" s="12"/>
+    </row>
+    <row r="226" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A226" s="13">
+        <v>45901</v>
+      </c>
+      <c r="B226" s="13">
+        <v>45930</v>
+      </c>
+      <c r="C226" s="18">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D226" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E226" s="16">
+        <v>50</v>
+      </c>
+      <c r="F226" s="16">
+        <v>50.3</v>
+      </c>
+      <c r="G226" s="16">
+        <v>50.3</v>
+      </c>
+      <c r="H226" s="12"/>
+    </row>
+    <row r="227" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A227" s="13">
+        <v>45931</v>
+      </c>
+      <c r="B227" s="13">
+        <v>45961</v>
+      </c>
+      <c r="C227" s="18">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D227" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E227" s="16">
+        <v>50.1</v>
+      </c>
+      <c r="F227" s="16">
+        <v>50.1</v>
+      </c>
+      <c r="G227" s="16">
+        <v>50</v>
+      </c>
+      <c r="H227" s="12"/>
+    </row>
+    <row r="228" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A228" s="13">
+        <v>45962</v>
+      </c>
+      <c r="B228" s="13">
+        <v>45991</v>
+      </c>
+      <c r="C228" s="18">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D228" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E228" s="16">
+        <v>49.5</v>
+      </c>
+      <c r="F228" s="16">
+        <v>50</v>
+      </c>
+      <c r="G228" s="16">
+        <v>50.1</v>
+      </c>
+      <c r="H228" s="12"/>
+    </row>
+    <row r="229" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A229" s="13">
+        <v>45992</v>
+      </c>
+      <c r="B229" s="13">
+        <v>46022</v>
+      </c>
+      <c r="C229" s="18">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D229" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E229" s="16">
+        <v>50.2</v>
+      </c>
+      <c r="F229" s="16">
+        <v>49.6</v>
+      </c>
+      <c r="G229" s="16">
+        <v>49.5</v>
+      </c>
+      <c r="H229" s="12"/>
+    </row>
+    <row r="230" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A230" s="13">
+        <v>46023</v>
+      </c>
+      <c r="B230" s="13">
+        <v>46053</v>
+      </c>
+      <c r="C230" s="18">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D230" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E230" s="16">
+        <v>49.4</v>
+      </c>
+      <c r="F230" s="16">
+        <v>50.3</v>
+      </c>
+      <c r="G230" s="16">
+        <v>50.2</v>
+      </c>
+      <c r="H230" s="12"/>
+    </row>
+    <row r="231" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A231" s="13">
+        <v>46054</v>
+      </c>
+      <c r="B231" s="13">
+        <v>46085</v>
+      </c>
+      <c r="C231" s="18">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D231" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E231" s="16">
+        <v>49.5</v>
+      </c>
+      <c r="F231" s="16">
+        <v>49.8</v>
+      </c>
+      <c r="G231" s="16">
+        <v>49.4</v>
+      </c>
+      <c r="H231" s="12"/>
+    </row>
+    <row r="232" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A232" s="13">
+        <v>46082</v>
+      </c>
+      <c r="B232" s="13">
+        <v>46112</v>
+      </c>
+      <c r="C232" s="18">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D232" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E232" s="16">
+        <v>50.1</v>
+      </c>
+      <c r="F232" s="16">
+        <v>49.9</v>
+      </c>
+      <c r="G232" s="16">
+        <v>49.5</v>
+      </c>
+      <c r="H232" s="12"/>
+    </row>
+    <row r="233" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A233" s="13">
+        <v>46113</v>
+      </c>
+      <c r="B233" s="13">
+        <v>46142</v>
+      </c>
+      <c r="C233" s="18">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D233" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E233" s="16">
+        <v>49.4</v>
+      </c>
+      <c r="F233" s="16">
+        <v>49.9</v>
+      </c>
+      <c r="G233" s="16">
+        <v>50.1</v>
+      </c>
+      <c r="H233" s="12"/>
+    </row>
+    <row r="234" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A234" s="13">
+        <v>46143</v>
+      </c>
+      <c r="B234" s="13">
+        <v>46173</v>
+      </c>
+      <c r="C234" s="18">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D234" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E234" s="16">
+        <v>50.1</v>
+      </c>
+      <c r="F234" s="16">
+        <v>49.5</v>
+      </c>
+      <c r="G234" s="16">
+        <v>49.4</v>
+      </c>
+      <c r="H234" s="12"/>
+    </row>
+    <row r="235" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A235" s="13">
+        <v>46174</v>
+      </c>
+      <c r="B235" s="13">
+        <v>46203</v>
+      </c>
+      <c r="C235" s="18">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D235" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="F235" s="16">
+        <v>49.9</v>
+      </c>
+      <c r="G235" s="16">
+        <v>50.1</v>
+      </c>
+      <c r="H235" s="12"/>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G235">
+    <sortCondition ref="B2:B235"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4443F9EE-BDA7-42C7-BB47-C54379F4610C}">
-  <dimension ref="B2:C3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="B2:C4"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>8</v>
       </c>
@@ -6502,11 +11689,16 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B3" t="s">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C3" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
         <v>9</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C4" t="s">
         <v>10</v>
       </c>
     </row>
@@ -6514,6 +11706,7 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{A5969E77-C348-41B1-9D81-78C2305BD7F6}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{56341EB3-C711-4691-A83B-E868000986BA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
